--- a/research/traditional_assets/database/data/kuwait/kuwait_entertainment.xlsx
+++ b/research/traditional_assets/database/data/kuwait/kuwait_entertainment.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="kwse_kcin" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,46 +590,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.249</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="E2">
-        <v>-0.375</v>
+        <v>-0.04269999999999999</v>
       </c>
       <c r="G2">
-        <v>-0.1871621621621622</v>
+        <v>0.1222585924713584</v>
       </c>
       <c r="H2">
-        <v>-0.1871621621621622</v>
+        <v>0.1222585924713584</v>
       </c>
       <c r="I2">
-        <v>-0.4466216216216216</v>
+        <v>0.1882160392798691</v>
       </c>
       <c r="J2">
-        <v>-0.4466216216216216</v>
+        <v>0.1877589431844751</v>
       </c>
       <c r="K2">
-        <v>2.91</v>
+        <v>27.9</v>
       </c>
       <c r="L2">
-        <v>0.1966216216216216</v>
+        <v>0.4566284779050736</v>
       </c>
       <c r="M2">
-        <v>0.169</v>
+        <v>8.98</v>
       </c>
       <c r="N2">
-        <v>0.0006263899184581172</v>
+        <v>0.0313001045660509</v>
       </c>
       <c r="O2">
-        <v>0.05807560137457045</v>
+        <v>0.3218637992831542</v>
       </c>
       <c r="P2">
-        <v>0.169</v>
+        <v>8.98</v>
       </c>
       <c r="Q2">
-        <v>0.0006263899184581172</v>
+        <v>0.0313001045660509</v>
       </c>
       <c r="R2">
-        <v>0.05807560137457045</v>
+        <v>0.3218637992831542</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +638,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.133</v>
+        <v>1.23</v>
       </c>
       <c r="V2">
-        <v>0.0004929577464788732</v>
+        <v>0.004287208086441269</v>
       </c>
       <c r="W2">
-        <v>0.01308453237410072</v>
+        <v>0.1185720356991075</v>
       </c>
       <c r="X2">
-        <v>0.09714128611922769</v>
+        <v>0.1849125310958142</v>
       </c>
       <c r="Y2">
-        <v>-0.08405675374512697</v>
+        <v>-0.06634049539670672</v>
       </c>
       <c r="Z2">
-        <v>0.04580681902592419</v>
+        <v>0.1460091237779801</v>
       </c>
       <c r="AA2">
-        <v>-0.02045831579468641</v>
+        <v>0.02741451877584476</v>
       </c>
       <c r="AB2">
-        <v>0.06792987146507082</v>
+        <v>0.1209580695853921</v>
       </c>
       <c r="AC2">
-        <v>-0.08838818725975722</v>
+        <v>-0.09354355080954735</v>
       </c>
       <c r="AD2">
-        <v>183.3</v>
+        <v>288.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>183.3</v>
+        <v>288.3</v>
       </c>
       <c r="AG2">
-        <v>183.167</v>
+        <v>287.07</v>
       </c>
       <c r="AH2">
-        <v>0.4045464577355992</v>
+        <v>0.5012169680111266</v>
       </c>
       <c r="AI2">
-        <v>0.4377836159541438</v>
+        <v>0.5346810089020771</v>
       </c>
       <c r="AJ2">
-        <v>0.4043716208907051</v>
+        <v>0.5001480913636601</v>
       </c>
       <c r="AK2">
-        <v>0.437604971247136</v>
+        <v>0.5336171161960703</v>
       </c>
       <c r="AL2">
-        <v>2.86</v>
+        <v>4.06</v>
       </c>
       <c r="AM2">
-        <v>2.86</v>
+        <v>3.393</v>
       </c>
       <c r="AN2">
-        <v>7969.565217391305</v>
+        <v>17.36746987951807</v>
       </c>
       <c r="AO2">
-        <v>-2.311188811188811</v>
+        <v>2.832512315270936</v>
       </c>
       <c r="AP2">
-        <v>7963.782608695652</v>
+        <v>17.2933734939759</v>
       </c>
       <c r="AQ2">
-        <v>-2.311188811188811</v>
+        <v>3.389330975537872</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +724,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.249</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="E3">
-        <v>-0.375</v>
+        <v>-0.04269999999999999</v>
       </c>
       <c r="G3">
-        <v>-0.1871621621621622</v>
+        <v>0.1222585924713584</v>
       </c>
       <c r="H3">
-        <v>-0.1871621621621622</v>
+        <v>0.1222585924713584</v>
       </c>
       <c r="I3">
-        <v>-0.4466216216216216</v>
+        <v>0.1882160392798691</v>
       </c>
       <c r="J3">
-        <v>-0.4466216216216216</v>
+        <v>0.1877589431844751</v>
       </c>
       <c r="K3">
-        <v>2.91</v>
+        <v>27.9</v>
       </c>
       <c r="L3">
-        <v>0.1966216216216216</v>
+        <v>0.4566284779050736</v>
       </c>
       <c r="M3">
-        <v>0.169</v>
+        <v>8.98</v>
       </c>
       <c r="N3">
-        <v>0.0006263899184581172</v>
+        <v>0.0313001045660509</v>
       </c>
       <c r="O3">
-        <v>0.05807560137457045</v>
+        <v>0.3218637992831542</v>
       </c>
       <c r="P3">
-        <v>0.169</v>
+        <v>8.98</v>
       </c>
       <c r="Q3">
-        <v>0.0006263899184581172</v>
+        <v>0.0313001045660509</v>
       </c>
       <c r="R3">
-        <v>0.05807560137457045</v>
+        <v>0.3218637992831542</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +772,8785 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.133</v>
+        <v>1.23</v>
       </c>
       <c r="V3">
-        <v>0.0004929577464788732</v>
+        <v>0.004287208086441269</v>
       </c>
       <c r="W3">
-        <v>0.01308453237410072</v>
+        <v>0.1185720356991075</v>
       </c>
       <c r="X3">
-        <v>0.09714128611922769</v>
+        <v>0.1849125310958142</v>
       </c>
       <c r="Y3">
-        <v>-0.08405675374512697</v>
+        <v>-0.06634049539670672</v>
       </c>
       <c r="Z3">
-        <v>0.04580681902592419</v>
+        <v>0.1460091237779801</v>
       </c>
       <c r="AA3">
-        <v>-0.02045831579468641</v>
+        <v>0.02741451877584476</v>
       </c>
       <c r="AB3">
-        <v>0.06792987146507082</v>
+        <v>0.1209580695853921</v>
       </c>
       <c r="AC3">
-        <v>-0.08838818725975722</v>
+        <v>-0.09354355080954735</v>
       </c>
       <c r="AD3">
-        <v>183.3</v>
+        <v>288.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>183.3</v>
+        <v>288.3</v>
       </c>
       <c r="AG3">
-        <v>183.167</v>
+        <v>287.07</v>
       </c>
       <c r="AH3">
-        <v>0.4045464577355992</v>
+        <v>0.5012169680111266</v>
       </c>
       <c r="AI3">
-        <v>0.4377836159541438</v>
+        <v>0.5346810089020771</v>
       </c>
       <c r="AJ3">
-        <v>0.4043716208907051</v>
+        <v>0.5001480913636601</v>
       </c>
       <c r="AK3">
-        <v>0.437604971247136</v>
+        <v>0.5336171161960703</v>
       </c>
       <c r="AL3">
-        <v>2.86</v>
+        <v>4.06</v>
       </c>
       <c r="AM3">
-        <v>2.86</v>
+        <v>3.393</v>
       </c>
       <c r="AN3">
-        <v>7969.565217391305</v>
+        <v>17.36746987951807</v>
       </c>
       <c r="AO3">
-        <v>-2.311188811188811</v>
+        <v>2.832512315270936</v>
       </c>
       <c r="AP3">
-        <v>7963.782608695652</v>
+        <v>17.2933734939759</v>
       </c>
       <c r="AQ3">
-        <v>-2.311188811188811</v>
+        <v>3.389330975537872</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Kuwait National Cinema Company (K.P.S.C) (KWSE:KCIN)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>KWSE:KCIN</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Entertainment</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Kuwait</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.501216968011127</v>
+      </c>
+      <c r="F2">
+        <v>0.04</v>
+      </c>
+      <c r="G2">
+        <v>286.9</v>
+      </c>
+      <c r="H2">
+        <v>579.808988816001</v>
+      </c>
+      <c r="I2">
+        <v>573.97</v>
+      </c>
+      <c r="J2">
+        <v>601.5869888160011</v>
+      </c>
+      <c r="K2">
+        <v>288.3</v>
+      </c>
+      <c r="L2">
+        <v>23.008</v>
+      </c>
+      <c r="M2">
+        <v>0.120958069585392</v>
+      </c>
+      <c r="N2">
+        <v>0.117186447972781</v>
+      </c>
+      <c r="O2">
+        <v>0.0573141743119266</v>
+      </c>
+      <c r="P2">
+        <v>0.040205</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.184912531095814</v>
+      </c>
+      <c r="T2">
+        <v>0.12039400830498</v>
+      </c>
+      <c r="U2">
+        <v>2.0488648739444</v>
+      </c>
+      <c r="V2">
+        <v>1.14415304619407</v>
+      </c>
+      <c r="W2">
+        <v>10.56714899422795</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>286.9</v>
+      </c>
+      <c r="AB2">
+        <v>0.07131389334354851</v>
+      </c>
+      <c r="AC2">
+        <v>0.06742844036697249</v>
+      </c>
+      <c r="AD2">
+        <v>0.15</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>16.6</v>
+      </c>
+      <c r="AH2">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="AI2">
+        <v>33.1</v>
+      </c>
+      <c r="AJ2">
+        <v>288.3</v>
+      </c>
+      <c r="AK2">
+        <v>288.3</v>
+      </c>
+      <c r="AL2">
+        <v>4.06</v>
+      </c>
+      <c r="AM2">
+        <v>288.3</v>
+      </c>
+      <c r="AN2">
+        <v>1.23</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1176030663710071</v>
+      </c>
+      <c r="C2">
+        <v>599.6365008068902</v>
+      </c>
+      <c r="D2">
+        <v>598.4065008068902</v>
+      </c>
+      <c r="E2">
+        <v>-288.3</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1.23</v>
+      </c>
+      <c r="H2">
+        <v>286.9</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>16.6</v>
+      </c>
+      <c r="K2">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L2">
+        <v>11.5</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>11.5</v>
+      </c>
+      <c r="O2">
+        <v>1.725</v>
+      </c>
+      <c r="P2">
+        <v>9.775</v>
+      </c>
+      <c r="Q2">
+        <v>14.875</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1176030663710071</v>
+      </c>
+      <c r="T2">
+        <v>1.105017026505343</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.15</v>
+      </c>
+      <c r="W2">
+        <v>0.038845</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1174853117714506</v>
+      </c>
+      <c r="C3">
+        <v>594.7800315773499</v>
+      </c>
+      <c r="D3">
+        <v>599.3020315773498</v>
+      </c>
+      <c r="E3">
+        <v>-282.548</v>
+      </c>
+      <c r="F3">
+        <v>5.752000000000001</v>
+      </c>
+      <c r="G3">
+        <v>1.23</v>
+      </c>
+      <c r="H3">
+        <v>286.9</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>16.6</v>
+      </c>
+      <c r="K3">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L3">
+        <v>11.5</v>
+      </c>
+      <c r="M3">
+        <v>0.2628664000000001</v>
+      </c>
+      <c r="N3">
+        <v>11.2371336</v>
+      </c>
+      <c r="O3">
+        <v>1.68557004</v>
+      </c>
+      <c r="P3">
+        <v>9.55156356</v>
+      </c>
+      <c r="Q3">
+        <v>14.65156356</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1182796583550006</v>
+      </c>
+      <c r="T3">
+        <v>1.114504546429884</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.15</v>
+      </c>
+      <c r="W3">
+        <v>0.038845</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>43.74845929339009</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1173675571718941</v>
+      </c>
+      <c r="C4">
+        <v>589.9262467348784</v>
+      </c>
+      <c r="D4">
+        <v>600.2002467348784</v>
+      </c>
+      <c r="E4">
+        <v>-276.796</v>
+      </c>
+      <c r="F4">
+        <v>11.504</v>
+      </c>
+      <c r="G4">
+        <v>1.23</v>
+      </c>
+      <c r="H4">
+        <v>286.9</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>16.6</v>
+      </c>
+      <c r="K4">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L4">
+        <v>11.5</v>
+      </c>
+      <c r="M4">
+        <v>0.5257328000000001</v>
+      </c>
+      <c r="N4">
+        <v>10.9742672</v>
+      </c>
+      <c r="O4">
+        <v>1.64614008</v>
+      </c>
+      <c r="P4">
+        <v>9.32812712</v>
+      </c>
+      <c r="Q4">
+        <v>14.42812712</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1189700583386675</v>
+      </c>
+      <c r="T4">
+        <v>1.124185689210027</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.15</v>
+      </c>
+      <c r="W4">
+        <v>0.038845</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>21.87422964669505</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1172498025723376</v>
+      </c>
+      <c r="C5">
+        <v>585.0751583674198</v>
+      </c>
+      <c r="D5">
+        <v>601.1011583674198</v>
+      </c>
+      <c r="E5">
+        <v>-271.044</v>
+      </c>
+      <c r="F5">
+        <v>17.256</v>
+      </c>
+      <c r="G5">
+        <v>1.23</v>
+      </c>
+      <c r="H5">
+        <v>286.9</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>16.6</v>
+      </c>
+      <c r="K5">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L5">
+        <v>11.5</v>
+      </c>
+      <c r="M5">
+        <v>0.7885992000000001</v>
+      </c>
+      <c r="N5">
+        <v>10.7114008</v>
+      </c>
+      <c r="O5">
+        <v>1.60671012</v>
+      </c>
+      <c r="P5">
+        <v>9.104690679999999</v>
+      </c>
+      <c r="Q5">
+        <v>14.20469068</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1196746933735439</v>
+      </c>
+      <c r="T5">
+        <v>1.134066443181514</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.15</v>
+      </c>
+      <c r="W5">
+        <v>0.038845</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>14.58281976446337</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1171864479727811</v>
+      </c>
+      <c r="C6">
+        <v>579.8089888160011</v>
+      </c>
+      <c r="D6">
+        <v>601.5869888160012</v>
+      </c>
+      <c r="E6">
+        <v>-265.292</v>
+      </c>
+      <c r="F6">
+        <v>23.008</v>
+      </c>
+      <c r="G6">
+        <v>1.23</v>
+      </c>
+      <c r="H6">
+        <v>286.9</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>16.6</v>
+      </c>
+      <c r="K6">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L6">
+        <v>11.5</v>
+      </c>
+      <c r="M6">
+        <v>1.0882784</v>
+      </c>
+      <c r="N6">
+        <v>10.4117216</v>
+      </c>
+      <c r="O6">
+        <v>1.56175824</v>
+      </c>
+      <c r="P6">
+        <v>8.84996336</v>
+      </c>
+      <c r="Q6">
+        <v>13.94996336</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1203940083049803</v>
+      </c>
+      <c r="T6">
+        <v>1.144153046194074</v>
+      </c>
+      <c r="U6">
+        <v>0.0473</v>
+      </c>
+      <c r="V6">
+        <v>0.15</v>
+      </c>
+      <c r="W6">
+        <v>0.040205</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>10.56714899422795</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1172437933732246</v>
+      </c>
+      <c r="C7">
+        <v>573.6172058160754</v>
+      </c>
+      <c r="D7">
+        <v>601.1472058160754</v>
+      </c>
+      <c r="E7">
+        <v>-259.54</v>
+      </c>
+      <c r="F7">
+        <v>28.76000000000001</v>
+      </c>
+      <c r="G7">
+        <v>1.23</v>
+      </c>
+      <c r="H7">
+        <v>286.9</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>16.6</v>
+      </c>
+      <c r="K7">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L7">
+        <v>11.5</v>
+      </c>
+      <c r="M7">
+        <v>1.469636</v>
+      </c>
+      <c r="N7">
+        <v>10.030364</v>
+      </c>
+      <c r="O7">
+        <v>1.5045546</v>
+      </c>
+      <c r="P7">
+        <v>8.5258094</v>
+      </c>
+      <c r="Q7">
+        <v>13.6258094</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1211284667086574</v>
+      </c>
+      <c r="T7">
+        <v>1.15445199874374</v>
+      </c>
+      <c r="U7">
+        <v>0.0511</v>
+      </c>
+      <c r="V7">
+        <v>0.15</v>
+      </c>
+      <c r="W7">
+        <v>0.043435</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>7.825066887310872</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.117268838773668</v>
+      </c>
+      <c r="C8">
+        <v>567.6733338229319</v>
+      </c>
+      <c r="D8">
+        <v>600.9553338229319</v>
+      </c>
+      <c r="E8">
+        <v>-253.788</v>
+      </c>
+      <c r="F8">
+        <v>34.512</v>
+      </c>
+      <c r="G8">
+        <v>1.23</v>
+      </c>
+      <c r="H8">
+        <v>286.9</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>16.6</v>
+      </c>
+      <c r="K8">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L8">
+        <v>11.5</v>
+      </c>
+      <c r="M8">
+        <v>1.829136</v>
+      </c>
+      <c r="N8">
+        <v>9.670864</v>
+      </c>
+      <c r="O8">
+        <v>1.4506296</v>
+      </c>
+      <c r="P8">
+        <v>8.220234399999999</v>
+      </c>
+      <c r="Q8">
+        <v>13.3202344</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1218785518868809</v>
+      </c>
+      <c r="T8">
+        <v>1.164970077943398</v>
+      </c>
+      <c r="U8">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V8">
+        <v>0.15</v>
+      </c>
+      <c r="W8">
+        <v>0.04505000000000001</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>6.28712135128279</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1173321341741115</v>
+      </c>
+      <c r="C9">
+        <v>561.4369753001057</v>
+      </c>
+      <c r="D9">
+        <v>600.4709753001057</v>
+      </c>
+      <c r="E9">
+        <v>-248.036</v>
+      </c>
+      <c r="F9">
+        <v>40.26400000000001</v>
+      </c>
+      <c r="G9">
+        <v>1.23</v>
+      </c>
+      <c r="H9">
+        <v>286.9</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>16.6</v>
+      </c>
+      <c r="K9">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L9">
+        <v>11.5</v>
+      </c>
+      <c r="M9">
+        <v>2.214520000000001</v>
+      </c>
+      <c r="N9">
+        <v>9.28548</v>
+      </c>
+      <c r="O9">
+        <v>1.392822</v>
+      </c>
+      <c r="P9">
+        <v>7.892657999999999</v>
+      </c>
+      <c r="Q9">
+        <v>12.992658</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1226447679291522</v>
+      </c>
+      <c r="T9">
+        <v>1.175714352394663</v>
+      </c>
+      <c r="U9">
+        <v>0.055</v>
+      </c>
+      <c r="V9">
+        <v>0.15</v>
+      </c>
+      <c r="W9">
+        <v>0.04675</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>5.192998934306305</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.117293429574555</v>
+      </c>
+      <c r="C10">
+        <v>555.9810636322152</v>
+      </c>
+      <c r="D10">
+        <v>600.7670636322151</v>
+      </c>
+      <c r="E10">
+        <v>-242.284</v>
+      </c>
+      <c r="F10">
+        <v>46.01600000000001</v>
+      </c>
+      <c r="G10">
+        <v>1.23</v>
+      </c>
+      <c r="H10">
+        <v>286.9</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>16.6</v>
+      </c>
+      <c r="K10">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L10">
+        <v>11.5</v>
+      </c>
+      <c r="M10">
+        <v>2.53088</v>
+      </c>
+      <c r="N10">
+        <v>8.96912</v>
+      </c>
+      <c r="O10">
+        <v>1.345368</v>
+      </c>
+      <c r="P10">
+        <v>7.623752</v>
+      </c>
+      <c r="Q10">
+        <v>12.723752</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1234276408419077</v>
+      </c>
+      <c r="T10">
+        <v>1.186692198029651</v>
+      </c>
+      <c r="U10">
+        <v>0.055</v>
+      </c>
+      <c r="V10">
+        <v>0.15</v>
+      </c>
+      <c r="W10">
+        <v>0.04675</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>4.543874067518017</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1178667249749985</v>
+      </c>
+      <c r="C11">
+        <v>545.8730340328203</v>
+      </c>
+      <c r="D11">
+        <v>596.4110340328203</v>
+      </c>
+      <c r="E11">
+        <v>-236.532</v>
+      </c>
+      <c r="F11">
+        <v>51.768</v>
+      </c>
+      <c r="G11">
+        <v>1.23</v>
+      </c>
+      <c r="H11">
+        <v>286.9</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>16.6</v>
+      </c>
+      <c r="K11">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L11">
+        <v>11.5</v>
+      </c>
+      <c r="M11">
+        <v>3.261384</v>
+      </c>
+      <c r="N11">
+        <v>8.238616</v>
+      </c>
+      <c r="O11">
+        <v>1.2357924</v>
+      </c>
+      <c r="P11">
+        <v>7.0028236</v>
+      </c>
+      <c r="Q11">
+        <v>12.1028236</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1242277197527456</v>
+      </c>
+      <c r="T11">
+        <v>1.197911314997275</v>
+      </c>
+      <c r="U11">
+        <v>0.063</v>
+      </c>
+      <c r="V11">
+        <v>0.15</v>
+      </c>
+      <c r="W11">
+        <v>0.05355</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>3.526110387491936</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1203100203754421</v>
+      </c>
+      <c r="C12">
+        <v>522.2433751938934</v>
+      </c>
+      <c r="D12">
+        <v>578.5333751938933</v>
+      </c>
+      <c r="E12">
+        <v>-230.78</v>
+      </c>
+      <c r="F12">
+        <v>57.52000000000001</v>
+      </c>
+      <c r="G12">
+        <v>1.23</v>
+      </c>
+      <c r="H12">
+        <v>286.9</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>16.6</v>
+      </c>
+      <c r="K12">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L12">
+        <v>11.5</v>
+      </c>
+      <c r="M12">
+        <v>5.257328000000001</v>
+      </c>
+      <c r="N12">
+        <v>6.242671999999999</v>
+      </c>
+      <c r="O12">
+        <v>0.9364007999999999</v>
+      </c>
+      <c r="P12">
+        <v>5.306271199999999</v>
+      </c>
+      <c r="Q12">
+        <v>10.4062712</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1250455781949356</v>
+      </c>
+      <c r="T12">
+        <v>1.209379745675292</v>
+      </c>
+      <c r="U12">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V12">
+        <v>0.15</v>
+      </c>
+      <c r="W12">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>2.187422964669505</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1225535657758855</v>
+      </c>
+      <c r="C13">
+        <v>500.9939348055941</v>
+      </c>
+      <c r="D13">
+        <v>563.035934805594</v>
+      </c>
+      <c r="E13">
+        <v>-225.028</v>
+      </c>
+      <c r="F13">
+        <v>63.27200000000001</v>
+      </c>
+      <c r="G13">
+        <v>1.23</v>
+      </c>
+      <c r="H13">
+        <v>286.9</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>16.6</v>
+      </c>
+      <c r="K13">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L13">
+        <v>11.5</v>
+      </c>
+      <c r="M13">
+        <v>7.118100000000001</v>
+      </c>
+      <c r="N13">
+        <v>4.381899999999999</v>
+      </c>
+      <c r="O13">
+        <v>0.6572849999999999</v>
+      </c>
+      <c r="P13">
+        <v>3.724614999999999</v>
+      </c>
+      <c r="Q13">
+        <v>8.824615000000001</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1258818154785231</v>
+      </c>
+      <c r="T13">
+        <v>1.221105893896634</v>
+      </c>
+      <c r="U13">
+        <v>0.1125</v>
+      </c>
+      <c r="V13">
+        <v>0.15</v>
+      </c>
+      <c r="W13">
+        <v>0.095625</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>1.61559966845085</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1323380393012066</v>
+      </c>
+      <c r="C14">
+        <v>436.3460007121938</v>
+      </c>
+      <c r="D14">
+        <v>504.1400007121938</v>
+      </c>
+      <c r="E14">
+        <v>-219.276</v>
+      </c>
+      <c r="F14">
+        <v>69.024</v>
+      </c>
+      <c r="G14">
+        <v>1.23</v>
+      </c>
+      <c r="H14">
+        <v>286.9</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>16.6</v>
+      </c>
+      <c r="K14">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L14">
+        <v>11.5</v>
+      </c>
+      <c r="M14">
+        <v>13.5701184</v>
+      </c>
+      <c r="N14">
+        <v>-2.0701184</v>
+      </c>
+      <c r="O14">
+        <v>-0.3105177600000001</v>
+      </c>
+      <c r="P14">
+        <v>-1.75960064</v>
+      </c>
+      <c r="Q14">
+        <v>3.340399360000001</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1269829502111006</v>
+      </c>
+      <c r="T14">
+        <v>1.236546570053143</v>
+      </c>
+      <c r="U14">
+        <v>0.1966</v>
+      </c>
+      <c r="V14">
+        <v>0.127117534950911</v>
+      </c>
+      <c r="W14">
+        <v>0.1716086926286509</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>0.8474502330060731</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.136248744666904</v>
+      </c>
+      <c r="C15">
+        <v>410.362411145936</v>
+      </c>
+      <c r="D15">
+        <v>483.908411145936</v>
+      </c>
+      <c r="E15">
+        <v>-213.524</v>
+      </c>
+      <c r="F15">
+        <v>74.77600000000001</v>
+      </c>
+      <c r="G15">
+        <v>1.23</v>
+      </c>
+      <c r="H15">
+        <v>286.9</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>16.6</v>
+      </c>
+      <c r="K15">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L15">
+        <v>11.5</v>
+      </c>
+      <c r="M15">
+        <v>15.9871088</v>
+      </c>
+      <c r="N15">
+        <v>-4.487108800000001</v>
+      </c>
+      <c r="O15">
+        <v>-0.6730663200000003</v>
+      </c>
+      <c r="P15">
+        <v>-3.814042480000001</v>
+      </c>
+      <c r="Q15">
+        <v>1.28595752</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1281077029327194</v>
+      </c>
+      <c r="T15">
+        <v>1.252318429769179</v>
+      </c>
+      <c r="U15">
+        <v>0.2138</v>
+      </c>
+      <c r="V15">
+        <v>0.1078994345744366</v>
+      </c>
+      <c r="W15">
+        <v>0.1907311008879854</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>0.7193295638295774</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.137998744666904</v>
+      </c>
+      <c r="C16">
+        <v>396.0736123956195</v>
+      </c>
+      <c r="D16">
+        <v>475.3716123956195</v>
+      </c>
+      <c r="E16">
+        <v>-207.772</v>
+      </c>
+      <c r="F16">
+        <v>80.52800000000002</v>
+      </c>
+      <c r="G16">
+        <v>1.23</v>
+      </c>
+      <c r="H16">
+        <v>286.9</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>16.6</v>
+      </c>
+      <c r="K16">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L16">
+        <v>11.5</v>
+      </c>
+      <c r="M16">
+        <v>17.2168864</v>
+      </c>
+      <c r="N16">
+        <v>-5.716886400000003</v>
+      </c>
+      <c r="O16">
+        <v>-0.8575329600000007</v>
+      </c>
+      <c r="P16">
+        <v>-4.859353440000003</v>
+      </c>
+      <c r="Q16">
+        <v>0.2406465599999983</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1291461645947278</v>
+      </c>
+      <c r="T16">
+        <v>1.266880271975798</v>
+      </c>
+      <c r="U16">
+        <v>0.2138</v>
+      </c>
+      <c r="V16">
+        <v>0.100192332104834</v>
+      </c>
+      <c r="W16">
+        <v>0.1923788793959865</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>0.6679488806988932</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.139748744666904</v>
+      </c>
+      <c r="C17">
+        <v>382.0807935083981</v>
+      </c>
+      <c r="D17">
+        <v>467.130793508398</v>
+      </c>
+      <c r="E17">
+        <v>-202.02</v>
+      </c>
+      <c r="F17">
+        <v>86.28</v>
+      </c>
+      <c r="G17">
+        <v>1.23</v>
+      </c>
+      <c r="H17">
+        <v>286.9</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>16.6</v>
+      </c>
+      <c r="K17">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L17">
+        <v>11.5</v>
+      </c>
+      <c r="M17">
+        <v>18.446664</v>
+      </c>
+      <c r="N17">
+        <v>-6.946663999999998</v>
+      </c>
+      <c r="O17">
+        <v>-1.0419996</v>
+      </c>
+      <c r="P17">
+        <v>-5.904664399999999</v>
+      </c>
+      <c r="Q17">
+        <v>-0.8046643999999974</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1302090606487834</v>
+      </c>
+      <c r="T17">
+        <v>1.281784745763748</v>
+      </c>
+      <c r="U17">
+        <v>0.2138</v>
+      </c>
+      <c r="V17">
+        <v>0.09351284329784509</v>
+      </c>
+      <c r="W17">
+        <v>0.1938069541029207</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>0.6234189553189673</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.141498744666904</v>
+      </c>
+      <c r="C18">
+        <v>368.3688238778915</v>
+      </c>
+      <c r="D18">
+        <v>459.1708238778915</v>
+      </c>
+      <c r="E18">
+        <v>-196.268</v>
+      </c>
+      <c r="F18">
+        <v>92.03200000000001</v>
+      </c>
+      <c r="G18">
+        <v>1.23</v>
+      </c>
+      <c r="H18">
+        <v>286.9</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>16.6</v>
+      </c>
+      <c r="K18">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L18">
+        <v>11.5</v>
+      </c>
+      <c r="M18">
+        <v>19.6764416</v>
+      </c>
+      <c r="N18">
+        <v>-8.1764416</v>
+      </c>
+      <c r="O18">
+        <v>-1.22646624</v>
+      </c>
+      <c r="P18">
+        <v>-6.94997536</v>
+      </c>
+      <c r="Q18">
+        <v>-1.849975359999998</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1312972637517451</v>
+      </c>
+      <c r="T18">
+        <v>1.297044087975221</v>
+      </c>
+      <c r="U18">
+        <v>0.2138</v>
+      </c>
+      <c r="V18">
+        <v>0.08766829059172977</v>
+      </c>
+      <c r="W18">
+        <v>0.1950565194714882</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>0.5844552706115317</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.143248744666904</v>
+      </c>
+      <c r="C19">
+        <v>354.9235869285257</v>
+      </c>
+      <c r="D19">
+        <v>451.4775869285256</v>
+      </c>
+      <c r="E19">
+        <v>-190.516</v>
+      </c>
+      <c r="F19">
+        <v>97.78400000000002</v>
+      </c>
+      <c r="G19">
+        <v>1.23</v>
+      </c>
+      <c r="H19">
+        <v>286.9</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>16.6</v>
+      </c>
+      <c r="K19">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L19">
+        <v>11.5</v>
+      </c>
+      <c r="M19">
+        <v>20.9062192</v>
+      </c>
+      <c r="N19">
+        <v>-9.406219200000002</v>
+      </c>
+      <c r="O19">
+        <v>-1.41093288</v>
+      </c>
+      <c r="P19">
+        <v>-7.995286320000002</v>
+      </c>
+      <c r="Q19">
+        <v>-2.89528632</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1324116886162239</v>
+      </c>
+      <c r="T19">
+        <v>1.312671125179742</v>
+      </c>
+      <c r="U19">
+        <v>0.2138</v>
+      </c>
+      <c r="V19">
+        <v>0.08251133232162801</v>
+      </c>
+      <c r="W19">
+        <v>0.1961590771496359</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>0.5500755488108533</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.144998744666904</v>
+      </c>
+      <c r="C20">
+        <v>341.7318965668076</v>
+      </c>
+      <c r="D20">
+        <v>444.0378965668075</v>
+      </c>
+      <c r="E20">
+        <v>-184.764</v>
+      </c>
+      <c r="F20">
+        <v>103.536</v>
+      </c>
+      <c r="G20">
+        <v>1.23</v>
+      </c>
+      <c r="H20">
+        <v>286.9</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>16.6</v>
+      </c>
+      <c r="K20">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L20">
+        <v>11.5</v>
+      </c>
+      <c r="M20">
+        <v>22.1359968</v>
+      </c>
+      <c r="N20">
+        <v>-10.6359968</v>
+      </c>
+      <c r="O20">
+        <v>-1.59539952</v>
+      </c>
+      <c r="P20">
+        <v>-9.04059728</v>
+      </c>
+      <c r="Q20">
+        <v>-3.940597279999999</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1335532945749584</v>
+      </c>
+      <c r="T20">
+        <v>1.328679309633154</v>
+      </c>
+      <c r="U20">
+        <v>0.2138</v>
+      </c>
+      <c r="V20">
+        <v>0.0779273694148709</v>
+      </c>
+      <c r="W20">
+        <v>0.1971391284191006</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>0.5195157960991392</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.151614465439469</v>
+      </c>
+      <c r="C21">
+        <v>309.9404101881807</v>
+      </c>
+      <c r="D21">
+        <v>417.9984101881807</v>
+      </c>
+      <c r="E21">
+        <v>-179.012</v>
+      </c>
+      <c r="F21">
+        <v>109.288</v>
+      </c>
+      <c r="G21">
+        <v>1.23</v>
+      </c>
+      <c r="H21">
+        <v>286.9</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>16.6</v>
+      </c>
+      <c r="K21">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L21">
+        <v>11.5</v>
+      </c>
+      <c r="M21">
+        <v>26.09797440000001</v>
+      </c>
+      <c r="N21">
+        <v>-14.59797440000001</v>
+      </c>
+      <c r="O21">
+        <v>-2.189696160000001</v>
+      </c>
+      <c r="P21">
+        <v>-12.40827824</v>
+      </c>
+      <c r="Q21">
+        <v>-7.308278240000003</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1348659534864579</v>
+      </c>
+      <c r="T21">
+        <v>1.34708608634882</v>
+      </c>
+      <c r="U21">
+        <v>0.2388</v>
+      </c>
+      <c r="V21">
+        <v>0.0660970837644779</v>
+      </c>
+      <c r="W21">
+        <v>0.2230160163970427</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>0.4406472250965193</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1536144654394691</v>
+      </c>
+      <c r="C22">
+        <v>296.9071254025357</v>
+      </c>
+      <c r="D22">
+        <v>410.7171254025357</v>
+      </c>
+      <c r="E22">
+        <v>-173.26</v>
+      </c>
+      <c r="F22">
+        <v>115.04</v>
+      </c>
+      <c r="G22">
+        <v>1.23</v>
+      </c>
+      <c r="H22">
+        <v>286.9</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>16.6</v>
+      </c>
+      <c r="K22">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L22">
+        <v>11.5</v>
+      </c>
+      <c r="M22">
+        <v>27.47155200000001</v>
+      </c>
+      <c r="N22">
+        <v>-15.97155200000001</v>
+      </c>
+      <c r="O22">
+        <v>-2.395732800000001</v>
+      </c>
+      <c r="P22">
+        <v>-13.57581920000001</v>
+      </c>
+      <c r="Q22">
+        <v>-8.475819200000004</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1360667779050387</v>
+      </c>
+      <c r="T22">
+        <v>1.36392466242818</v>
+      </c>
+      <c r="U22">
+        <v>0.2388</v>
+      </c>
+      <c r="V22">
+        <v>0.06279222957625401</v>
+      </c>
+      <c r="W22">
+        <v>0.2238052155771906</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>0.4186148638416933</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.155614465439469</v>
+      </c>
+      <c r="C23">
+        <v>284.1231688061098</v>
+      </c>
+      <c r="D23">
+        <v>403.6851688061097</v>
+      </c>
+      <c r="E23">
+        <v>-167.508</v>
+      </c>
+      <c r="F23">
+        <v>120.792</v>
+      </c>
+      <c r="G23">
+        <v>1.23</v>
+      </c>
+      <c r="H23">
+        <v>286.9</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>16.6</v>
+      </c>
+      <c r="K23">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L23">
+        <v>11.5</v>
+      </c>
+      <c r="M23">
+        <v>28.8451296</v>
+      </c>
+      <c r="N23">
+        <v>-17.3451296</v>
+      </c>
+      <c r="O23">
+        <v>-2.601769440000001</v>
+      </c>
+      <c r="P23">
+        <v>-14.74336016</v>
+      </c>
+      <c r="Q23">
+        <v>-9.64336016</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1372980029418113</v>
+      </c>
+      <c r="T23">
+        <v>1.381189531572841</v>
+      </c>
+      <c r="U23">
+        <v>0.2388</v>
+      </c>
+      <c r="V23">
+        <v>0.0598021234059562</v>
+      </c>
+      <c r="W23">
+        <v>0.2245192529306577</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>0.3986808227063746</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.157614465439469</v>
+      </c>
+      <c r="C24">
+        <v>271.5759495992064</v>
+      </c>
+      <c r="D24">
+        <v>396.8899495992064</v>
+      </c>
+      <c r="E24">
+        <v>-161.756</v>
+      </c>
+      <c r="F24">
+        <v>126.544</v>
+      </c>
+      <c r="G24">
+        <v>1.23</v>
+      </c>
+      <c r="H24">
+        <v>286.9</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>16.6</v>
+      </c>
+      <c r="K24">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L24">
+        <v>11.5</v>
+      </c>
+      <c r="M24">
+        <v>30.2187072</v>
+      </c>
+      <c r="N24">
+        <v>-18.7187072</v>
+      </c>
+      <c r="O24">
+        <v>-2.807806080000001</v>
+      </c>
+      <c r="P24">
+        <v>-15.91090112</v>
+      </c>
+      <c r="Q24">
+        <v>-10.81090112</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1385607978513217</v>
+      </c>
+      <c r="T24">
+        <v>1.398897089669928</v>
+      </c>
+      <c r="U24">
+        <v>0.2388</v>
+      </c>
+      <c r="V24">
+        <v>0.05708384506932183</v>
+      </c>
+      <c r="W24">
+        <v>0.2251683777974459</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>0.3805589671288121</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1596144654394691</v>
+      </c>
+      <c r="C25">
+        <v>259.2537107100882</v>
+      </c>
+      <c r="D25">
+        <v>390.3197107100882</v>
+      </c>
+      <c r="E25">
+        <v>-156.004</v>
+      </c>
+      <c r="F25">
+        <v>132.296</v>
+      </c>
+      <c r="G25">
+        <v>1.23</v>
+      </c>
+      <c r="H25">
+        <v>286.9</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>16.6</v>
+      </c>
+      <c r="K25">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L25">
+        <v>11.5</v>
+      </c>
+      <c r="M25">
+        <v>31.59228480000001</v>
+      </c>
+      <c r="N25">
+        <v>-20.09228480000001</v>
+      </c>
+      <c r="O25">
+        <v>-3.013842720000001</v>
+      </c>
+      <c r="P25">
+        <v>-17.07844208</v>
+      </c>
+      <c r="Q25">
+        <v>-11.97844208</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1398563926286116</v>
+      </c>
+      <c r="T25">
+        <v>1.417064584340966</v>
+      </c>
+      <c r="U25">
+        <v>0.2388</v>
+      </c>
+      <c r="V25">
+        <v>0.05460193876196</v>
+      </c>
+      <c r="W25">
+        <v>0.225761057023644</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>0.3640129250797334</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.161614465439469</v>
+      </c>
+      <c r="C26">
+        <v>247.1454609098161</v>
+      </c>
+      <c r="D26">
+        <v>383.9634609098161</v>
+      </c>
+      <c r="E26">
+        <v>-150.252</v>
+      </c>
+      <c r="F26">
+        <v>138.048</v>
+      </c>
+      <c r="G26">
+        <v>1.23</v>
+      </c>
+      <c r="H26">
+        <v>286.9</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>16.6</v>
+      </c>
+      <c r="K26">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L26">
+        <v>11.5</v>
+      </c>
+      <c r="M26">
+        <v>32.9658624</v>
+      </c>
+      <c r="N26">
+        <v>-21.4658624</v>
+      </c>
+      <c r="O26">
+        <v>-3.21987936</v>
+      </c>
+      <c r="P26">
+        <v>-18.24598304</v>
+      </c>
+      <c r="Q26">
+        <v>-13.14598304</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1411860820053038</v>
+      </c>
+      <c r="T26">
+        <v>1.435710170977032</v>
+      </c>
+      <c r="U26">
+        <v>0.2388</v>
+      </c>
+      <c r="V26">
+        <v>0.05232685798021168</v>
+      </c>
+      <c r="W26">
+        <v>0.2263043463143255</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>0.3488457198680779</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.163614465439469</v>
+      </c>
+      <c r="C27">
+        <v>235.2409134537517</v>
+      </c>
+      <c r="D27">
+        <v>377.8109134537517</v>
+      </c>
+      <c r="E27">
+        <v>-144.5</v>
+      </c>
+      <c r="F27">
+        <v>143.8</v>
+      </c>
+      <c r="G27">
+        <v>1.23</v>
+      </c>
+      <c r="H27">
+        <v>286.9</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>16.6</v>
+      </c>
+      <c r="K27">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L27">
+        <v>11.5</v>
+      </c>
+      <c r="M27">
+        <v>34.33944</v>
+      </c>
+      <c r="N27">
+        <v>-22.83944</v>
+      </c>
+      <c r="O27">
+        <v>-3.425916000000001</v>
+      </c>
+      <c r="P27">
+        <v>-19.413524</v>
+      </c>
+      <c r="Q27">
+        <v>-14.313524</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1425512297653745</v>
+      </c>
+      <c r="T27">
+        <v>1.454852973256725</v>
+      </c>
+      <c r="U27">
+        <v>0.2388</v>
+      </c>
+      <c r="V27">
+        <v>0.05023378366100321</v>
+      </c>
+      <c r="W27">
+        <v>0.2268041724617524</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.3348918910733547</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.165614465439469</v>
+      </c>
+      <c r="C28">
+        <v>223.5304305291978</v>
+      </c>
+      <c r="D28">
+        <v>371.8524305291978</v>
+      </c>
+      <c r="E28">
+        <v>-138.748</v>
+      </c>
+      <c r="F28">
+        <v>149.552</v>
+      </c>
+      <c r="G28">
+        <v>1.23</v>
+      </c>
+      <c r="H28">
+        <v>286.9</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>16.6</v>
+      </c>
+      <c r="K28">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L28">
+        <v>11.5</v>
+      </c>
+      <c r="M28">
+        <v>35.71301760000001</v>
+      </c>
+      <c r="N28">
+        <v>-24.21301760000001</v>
+      </c>
+      <c r="O28">
+        <v>-3.631952640000002</v>
+      </c>
+      <c r="P28">
+        <v>-20.58106496000001</v>
+      </c>
+      <c r="Q28">
+        <v>-15.48106496</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1439532734108526</v>
+      </c>
+      <c r="T28">
+        <v>1.474513148571005</v>
+      </c>
+      <c r="U28">
+        <v>0.2388</v>
+      </c>
+      <c r="V28">
+        <v>0.04830171505865693</v>
+      </c>
+      <c r="W28">
+        <v>0.2272655504439927</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.3220114337243795</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.167614465439469</v>
+      </c>
+      <c r="C29">
+        <v>212.0049728781402</v>
+      </c>
+      <c r="D29">
+        <v>366.0789728781402</v>
+      </c>
+      <c r="E29">
+        <v>-132.996</v>
+      </c>
+      <c r="F29">
+        <v>155.304</v>
+      </c>
+      <c r="G29">
+        <v>1.23</v>
+      </c>
+      <c r="H29">
+        <v>286.9</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>16.6</v>
+      </c>
+      <c r="K29">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L29">
+        <v>11.5</v>
+      </c>
+      <c r="M29">
+        <v>37.08659520000001</v>
+      </c>
+      <c r="N29">
+        <v>-25.58659520000001</v>
+      </c>
+      <c r="O29">
+        <v>-3.837989280000002</v>
+      </c>
+      <c r="P29">
+        <v>-21.74860592000001</v>
+      </c>
+      <c r="Q29">
+        <v>-16.64860592000001</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1453937292110012</v>
+      </c>
+      <c r="T29">
+        <v>1.494711958825403</v>
+      </c>
+      <c r="U29">
+        <v>0.2388</v>
+      </c>
+      <c r="V29">
+        <v>0.04651276264907703</v>
+      </c>
+      <c r="W29">
+        <v>0.2276927522794004</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.3100850843271802</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.169614465439469</v>
+      </c>
+      <c r="C30">
+        <v>200.656054041247</v>
+      </c>
+      <c r="D30">
+        <v>360.482054041247</v>
+      </c>
+      <c r="E30">
+        <v>-127.244</v>
+      </c>
+      <c r="F30">
+        <v>161.056</v>
+      </c>
+      <c r="G30">
+        <v>1.23</v>
+      </c>
+      <c r="H30">
+        <v>286.9</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>16.6</v>
+      </c>
+      <c r="K30">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L30">
+        <v>11.5</v>
+      </c>
+      <c r="M30">
+        <v>38.46017280000001</v>
+      </c>
+      <c r="N30">
+        <v>-26.96017280000001</v>
+      </c>
+      <c r="O30">
+        <v>-4.044025920000002</v>
+      </c>
+      <c r="P30">
+        <v>-22.91614688000001</v>
+      </c>
+      <c r="Q30">
+        <v>-17.81614688000001</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1468741976722652</v>
+      </c>
+      <c r="T30">
+        <v>1.515471847142422</v>
+      </c>
+      <c r="U30">
+        <v>0.2388</v>
+      </c>
+      <c r="V30">
+        <v>0.04485159255446715</v>
+      </c>
+      <c r="W30">
+        <v>0.2280894396979933</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.2990106170297809</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.171614465439469</v>
+      </c>
+      <c r="C31">
+        <v>189.4756987359955</v>
+      </c>
+      <c r="D31">
+        <v>355.0536987359955</v>
+      </c>
+      <c r="E31">
+        <v>-121.492</v>
+      </c>
+      <c r="F31">
+        <v>166.808</v>
+      </c>
+      <c r="G31">
+        <v>1.23</v>
+      </c>
+      <c r="H31">
+        <v>286.9</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>16.6</v>
+      </c>
+      <c r="K31">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L31">
+        <v>11.5</v>
+      </c>
+      <c r="M31">
+        <v>39.8337504</v>
+      </c>
+      <c r="N31">
+        <v>-28.3337504</v>
+      </c>
+      <c r="O31">
+        <v>-4.250062560000001</v>
+      </c>
+      <c r="P31">
+        <v>-24.08368784</v>
+      </c>
+      <c r="Q31">
+        <v>-18.98368784</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1483963694704661</v>
+      </c>
+      <c r="T31">
+        <v>1.536816521045837</v>
+      </c>
+      <c r="U31">
+        <v>0.2388</v>
+      </c>
+      <c r="V31">
+        <v>0.04330498591465795</v>
+      </c>
+      <c r="W31">
+        <v>0.2284587693635797</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.2886999060977196</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.173614465439469</v>
+      </c>
+      <c r="C32">
+        <v>178.4564049396125</v>
+      </c>
+      <c r="D32">
+        <v>349.7864049396125</v>
+      </c>
+      <c r="E32">
+        <v>-115.74</v>
+      </c>
+      <c r="F32">
+        <v>172.56</v>
+      </c>
+      <c r="G32">
+        <v>1.23</v>
+      </c>
+      <c r="H32">
+        <v>286.9</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>16.6</v>
+      </c>
+      <c r="K32">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L32">
+        <v>11.5</v>
+      </c>
+      <c r="M32">
+        <v>41.207328</v>
+      </c>
+      <c r="N32">
+        <v>-29.707328</v>
+      </c>
+      <c r="O32">
+        <v>-4.456099200000001</v>
+      </c>
+      <c r="P32">
+        <v>-25.2512288</v>
+      </c>
+      <c r="Q32">
+        <v>-20.1512288</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1499620318914727</v>
+      </c>
+      <c r="T32">
+        <v>1.558771042775063</v>
+      </c>
+      <c r="U32">
+        <v>0.2388</v>
+      </c>
+      <c r="V32">
+        <v>0.04186148638416934</v>
+      </c>
+      <c r="W32">
+        <v>0.2288034770514604</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.2790765758944622</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.175614465439469</v>
+      </c>
+      <c r="C33">
+        <v>167.591109297722</v>
+      </c>
+      <c r="D33">
+        <v>344.673109297722</v>
+      </c>
+      <c r="E33">
+        <v>-109.988</v>
+      </c>
+      <c r="F33">
+        <v>178.312</v>
+      </c>
+      <c r="G33">
+        <v>1.23</v>
+      </c>
+      <c r="H33">
+        <v>286.9</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>16.6</v>
+      </c>
+      <c r="K33">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L33">
+        <v>11.5</v>
+      </c>
+      <c r="M33">
+        <v>42.58090560000001</v>
+      </c>
+      <c r="N33">
+        <v>-31.08090560000001</v>
+      </c>
+      <c r="O33">
+        <v>-4.662135840000002</v>
+      </c>
+      <c r="P33">
+        <v>-26.41876976000001</v>
+      </c>
+      <c r="Q33">
+        <v>-21.31876976000001</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1515730758319289</v>
+      </c>
+      <c r="T33">
+        <v>1.581361927452963</v>
+      </c>
+      <c r="U33">
+        <v>0.2388</v>
+      </c>
+      <c r="V33">
+        <v>0.04051111585564775</v>
+      </c>
+      <c r="W33">
+        <v>0.2291259455336713</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.2700741057043182</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.177614465439469</v>
+      </c>
+      <c r="C34">
+        <v>156.873155523286</v>
+      </c>
+      <c r="D34">
+        <v>339.707155523286</v>
+      </c>
+      <c r="E34">
+        <v>-104.236</v>
+      </c>
+      <c r="F34">
+        <v>184.064</v>
+      </c>
+      <c r="G34">
+        <v>1.23</v>
+      </c>
+      <c r="H34">
+        <v>286.9</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>16.6</v>
+      </c>
+      <c r="K34">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L34">
+        <v>11.5</v>
+      </c>
+      <c r="M34">
+        <v>43.95448320000001</v>
+      </c>
+      <c r="N34">
+        <v>-32.45448320000001</v>
+      </c>
+      <c r="O34">
+        <v>-4.868172480000002</v>
+      </c>
+      <c r="P34">
+        <v>-27.58631072</v>
+      </c>
+      <c r="Q34">
+        <v>-22.48631072</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1532315034176925</v>
+      </c>
+      <c r="T34">
+        <v>1.604617249915506</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.03924514348515876</v>
+      </c>
+      <c r="W34">
+        <v>0.2294282597357441</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.2616342899010583</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.179614465439469</v>
+      </c>
+      <c r="C35">
+        <v>146.2962654885429</v>
+      </c>
+      <c r="D35">
+        <v>334.8822654885429</v>
+      </c>
+      <c r="E35">
+        <v>-98.48399999999998</v>
+      </c>
+      <c r="F35">
+        <v>189.816</v>
+      </c>
+      <c r="G35">
+        <v>1.23</v>
+      </c>
+      <c r="H35">
+        <v>286.9</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>16.6</v>
+      </c>
+      <c r="K35">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L35">
+        <v>11.5</v>
+      </c>
+      <c r="M35">
+        <v>45.32806080000001</v>
+      </c>
+      <c r="N35">
+        <v>-33.82806080000001</v>
+      </c>
+      <c r="O35">
+        <v>-5.074209120000003</v>
+      </c>
+      <c r="P35">
+        <v>-28.75385168000001</v>
+      </c>
+      <c r="Q35">
+        <v>-23.65385168000001</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1549394363045238</v>
+      </c>
+      <c r="T35">
+        <v>1.628566761108275</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.03805589671288122</v>
+      </c>
+      <c r="W35">
+        <v>0.229712251864964</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.2537059780858747</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.181614465439469</v>
+      </c>
+      <c r="C36">
+        <v>135.8545127459472</v>
+      </c>
+      <c r="D36">
+        <v>330.1925127459472</v>
+      </c>
+      <c r="E36">
+        <v>-92.73199999999997</v>
+      </c>
+      <c r="F36">
+        <v>195.568</v>
+      </c>
+      <c r="G36">
+        <v>1.23</v>
+      </c>
+      <c r="H36">
+        <v>286.9</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>16.6</v>
+      </c>
+      <c r="K36">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L36">
+        <v>11.5</v>
+      </c>
+      <c r="M36">
+        <v>46.70163840000001</v>
+      </c>
+      <c r="N36">
+        <v>-35.20163840000001</v>
+      </c>
+      <c r="O36">
+        <v>-5.280245760000003</v>
+      </c>
+      <c r="P36">
+        <v>-29.92139264000001</v>
+      </c>
+      <c r="Q36">
+        <v>-24.82139264000001</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1566991247333802</v>
+      </c>
+      <c r="T36">
+        <v>1.653242015064461</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.03693660563309059</v>
+      </c>
+      <c r="W36">
+        <v>0.229979538574818</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.2462440375539372</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.183614465439469</v>
+      </c>
+      <c r="C37">
+        <v>125.542298243288</v>
+      </c>
+      <c r="D37">
+        <v>325.632298243288</v>
+      </c>
+      <c r="E37">
+        <v>-86.97999999999999</v>
+      </c>
+      <c r="F37">
+        <v>201.32</v>
+      </c>
+      <c r="G37">
+        <v>1.23</v>
+      </c>
+      <c r="H37">
+        <v>286.9</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>16.6</v>
+      </c>
+      <c r="K37">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L37">
+        <v>11.5</v>
+      </c>
+      <c r="M37">
+        <v>48.075216</v>
+      </c>
+      <c r="N37">
+        <v>-36.575216</v>
+      </c>
+      <c r="O37">
+        <v>-5.486282400000001</v>
+      </c>
+      <c r="P37">
+        <v>-31.0889336</v>
+      </c>
+      <c r="Q37">
+        <v>-25.9889336</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1585129574215861</v>
+      </c>
+      <c r="T37">
+        <v>1.678676507603914</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.03588127404357372</v>
+      </c>
+      <c r="W37">
+        <v>0.2302315517583946</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.2392084936238248</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.185614465439469</v>
+      </c>
+      <c r="C38">
+        <v>115.3543280237521</v>
+      </c>
+      <c r="D38">
+        <v>321.1963280237521</v>
+      </c>
+      <c r="E38">
+        <v>-81.22800000000001</v>
+      </c>
+      <c r="F38">
+        <v>207.072</v>
+      </c>
+      <c r="G38">
+        <v>1.23</v>
+      </c>
+      <c r="H38">
+        <v>286.9</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>16.6</v>
+      </c>
+      <c r="K38">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L38">
+        <v>11.5</v>
+      </c>
+      <c r="M38">
+        <v>49.4487936</v>
+      </c>
+      <c r="N38">
+        <v>-37.9487936</v>
+      </c>
+      <c r="O38">
+        <v>-5.692319040000001</v>
+      </c>
+      <c r="P38">
+        <v>-32.25647456</v>
+      </c>
+      <c r="Q38">
+        <v>-27.15647456</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1603834723812983</v>
+      </c>
+      <c r="T38">
+        <v>1.704905828035225</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.03488457198680779</v>
+      </c>
+      <c r="W38">
+        <v>0.2304695642095503</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.2325638132453852</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.187614465439469</v>
+      </c>
+      <c r="C39">
+        <v>105.2855927241935</v>
+      </c>
+      <c r="D39">
+        <v>316.8795927241935</v>
+      </c>
+      <c r="E39">
+        <v>-75.476</v>
+      </c>
+      <c r="F39">
+        <v>212.824</v>
+      </c>
+      <c r="G39">
+        <v>1.23</v>
+      </c>
+      <c r="H39">
+        <v>286.9</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>16.6</v>
+      </c>
+      <c r="K39">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L39">
+        <v>11.5</v>
+      </c>
+      <c r="M39">
+        <v>50.82237120000001</v>
+      </c>
+      <c r="N39">
+        <v>-39.32237120000001</v>
+      </c>
+      <c r="O39">
+        <v>-5.898355680000002</v>
+      </c>
+      <c r="P39">
+        <v>-33.42401552</v>
+      </c>
+      <c r="Q39">
+        <v>-28.32401552</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.162313368768303</v>
+      </c>
+      <c r="T39">
+        <v>1.731967825305626</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.03394174571689406</v>
+      </c>
+      <c r="W39">
+        <v>0.2306947111228057</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.2262783047792937</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1896144654394691</v>
+      </c>
+      <c r="C40">
+        <v>95.33134870468484</v>
+      </c>
+      <c r="D40">
+        <v>312.6773487046848</v>
+      </c>
+      <c r="E40">
+        <v>-69.72399999999999</v>
+      </c>
+      <c r="F40">
+        <v>218.576</v>
+      </c>
+      <c r="G40">
+        <v>1.23</v>
+      </c>
+      <c r="H40">
+        <v>286.9</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>16.6</v>
+      </c>
+      <c r="K40">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L40">
+        <v>11.5</v>
+      </c>
+      <c r="M40">
+        <v>52.19594880000001</v>
+      </c>
+      <c r="N40">
+        <v>-40.69594880000001</v>
+      </c>
+      <c r="O40">
+        <v>-6.104392320000002</v>
+      </c>
+      <c r="P40">
+        <v>-34.59155648000001</v>
+      </c>
+      <c r="Q40">
+        <v>-29.49155648000001</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1643055198774692</v>
+      </c>
+      <c r="T40">
+        <v>1.75990279022991</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.03304854188223895</v>
+      </c>
+      <c r="W40">
+        <v>0.2309080081985214</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.2203236125482596</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.191614465439469</v>
+      </c>
+      <c r="C41">
+        <v>85.48710065990099</v>
+      </c>
+      <c r="D41">
+        <v>308.585100659901</v>
+      </c>
+      <c r="E41">
+        <v>-63.97199999999998</v>
+      </c>
+      <c r="F41">
+        <v>224.328</v>
+      </c>
+      <c r="G41">
+        <v>1.23</v>
+      </c>
+      <c r="H41">
+        <v>286.9</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>16.6</v>
+      </c>
+      <c r="K41">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L41">
+        <v>11.5</v>
+      </c>
+      <c r="M41">
+        <v>53.56952640000001</v>
+      </c>
+      <c r="N41">
+        <v>-42.06952640000001</v>
+      </c>
+      <c r="O41">
+        <v>-6.310428960000002</v>
+      </c>
+      <c r="P41">
+        <v>-35.75909744000001</v>
+      </c>
+      <c r="Q41">
+        <v>-30.65909744</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1663629874164441</v>
+      </c>
+      <c r="T41">
+        <v>1.788753655643515</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.03220114337243796</v>
+      </c>
+      <c r="W41">
+        <v>0.2311103669626618</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.2146742891495863</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.193614465439469</v>
+      </c>
+      <c r="C42">
+        <v>75.74858557832988</v>
+      </c>
+      <c r="D42">
+        <v>304.5985855783299</v>
+      </c>
+      <c r="E42">
+        <v>-58.21999999999997</v>
+      </c>
+      <c r="F42">
+        <v>230.08</v>
+      </c>
+      <c r="G42">
+        <v>1.23</v>
+      </c>
+      <c r="H42">
+        <v>286.9</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>16.6</v>
+      </c>
+      <c r="K42">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L42">
+        <v>11.5</v>
+      </c>
+      <c r="M42">
+        <v>54.94310400000001</v>
+      </c>
+      <c r="N42">
+        <v>-43.44310400000001</v>
+      </c>
+      <c r="O42">
+        <v>-6.516465600000003</v>
+      </c>
+      <c r="P42">
+        <v>-36.92663840000001</v>
+      </c>
+      <c r="Q42">
+        <v>-31.82663840000001</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1684890372067182</v>
+      </c>
+      <c r="T42">
+        <v>1.818566216570907</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.031396114788127</v>
+      </c>
+      <c r="W42">
+        <v>0.2313026077885953</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.2093074319208467</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.195614465439469</v>
+      </c>
+      <c r="C43">
+        <v>66.11175792898393</v>
+      </c>
+      <c r="D43">
+        <v>300.713757928984</v>
+      </c>
+      <c r="E43">
+        <v>-52.46799999999996</v>
+      </c>
+      <c r="F43">
+        <v>235.8320000000001</v>
+      </c>
+      <c r="G43">
+        <v>1.23</v>
+      </c>
+      <c r="H43">
+        <v>286.9</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>16.6</v>
+      </c>
+      <c r="K43">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L43">
+        <v>11.5</v>
+      </c>
+      <c r="M43">
+        <v>56.31668160000002</v>
+      </c>
+      <c r="N43">
+        <v>-44.81668160000002</v>
+      </c>
+      <c r="O43">
+        <v>-6.722502240000003</v>
+      </c>
+      <c r="P43">
+        <v>-38.09417936000001</v>
+      </c>
+      <c r="Q43">
+        <v>-32.99417936000001</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1706871564814083</v>
+      </c>
+      <c r="T43">
+        <v>1.849389372783973</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.03063035589085561</v>
+      </c>
+      <c r="W43">
+        <v>0.2314854710132637</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.2042023726057041</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.197614465439469</v>
+      </c>
+      <c r="C44">
+        <v>56.57277596739937</v>
+      </c>
+      <c r="D44">
+        <v>296.9267759673994</v>
+      </c>
+      <c r="E44">
+        <v>-46.71600000000001</v>
+      </c>
+      <c r="F44">
+        <v>241.584</v>
+      </c>
+      <c r="G44">
+        <v>1.23</v>
+      </c>
+      <c r="H44">
+        <v>286.9</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>16.6</v>
+      </c>
+      <c r="K44">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L44">
+        <v>11.5</v>
+      </c>
+      <c r="M44">
+        <v>57.69025920000001</v>
+      </c>
+      <c r="N44">
+        <v>-46.19025920000001</v>
+      </c>
+      <c r="O44">
+        <v>-6.928538880000002</v>
+      </c>
+      <c r="P44">
+        <v>-39.26172032</v>
+      </c>
+      <c r="Q44">
+        <v>-34.16172032</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1729610729724671</v>
+      </c>
+      <c r="T44">
+        <v>1.881275396452662</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.0299010617029781</v>
+      </c>
+      <c r="W44">
+        <v>0.2316596264653288</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.1993404113531874</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.199614465439469</v>
+      </c>
+      <c r="C45">
+        <v>47.12798906348536</v>
+      </c>
+      <c r="D45">
+        <v>293.2339890634854</v>
+      </c>
+      <c r="E45">
+        <v>-40.964</v>
+      </c>
+      <c r="F45">
+        <v>247.336</v>
+      </c>
+      <c r="G45">
+        <v>1.23</v>
+      </c>
+      <c r="H45">
+        <v>286.9</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>16.6</v>
+      </c>
+      <c r="K45">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L45">
+        <v>11.5</v>
+      </c>
+      <c r="M45">
+        <v>59.0638368</v>
+      </c>
+      <c r="N45">
+        <v>-47.5638368</v>
+      </c>
+      <c r="O45">
+        <v>-7.134575520000002</v>
+      </c>
+      <c r="P45">
+        <v>-40.42926128000001</v>
+      </c>
+      <c r="Q45">
+        <v>-35.32926128</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1753147760070718</v>
+      </c>
+      <c r="T45">
+        <v>1.914280227969375</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.02920568817500187</v>
+      </c>
+      <c r="W45">
+        <v>0.2318256816638096</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.1947045878333458</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.201614465439469</v>
+      </c>
+      <c r="C46">
+        <v>37.773925963355</v>
+      </c>
+      <c r="D46">
+        <v>289.631925963355</v>
+      </c>
+      <c r="E46">
+        <v>-35.21199999999999</v>
+      </c>
+      <c r="F46">
+        <v>253.088</v>
+      </c>
+      <c r="G46">
+        <v>1.23</v>
+      </c>
+      <c r="H46">
+        <v>286.9</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>16.6</v>
+      </c>
+      <c r="K46">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L46">
+        <v>11.5</v>
+      </c>
+      <c r="M46">
+        <v>60.43741440000001</v>
+      </c>
+      <c r="N46">
+        <v>-48.93741440000001</v>
+      </c>
+      <c r="O46">
+        <v>-7.340612160000003</v>
+      </c>
+      <c r="P46">
+        <v>-41.59680224</v>
+      </c>
+      <c r="Q46">
+        <v>-36.49680224</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1777525398643409</v>
+      </c>
+      <c r="T46">
+        <v>1.948463803468829</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.02854192253466092</v>
+      </c>
+      <c r="W46">
+        <v>0.231984188898723</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.190279483564406</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.203614465439469</v>
+      </c>
+      <c r="C47">
+        <v>28.50728390580173</v>
+      </c>
+      <c r="D47">
+        <v>286.1172839058017</v>
+      </c>
+      <c r="E47">
+        <v>-29.45999999999998</v>
+      </c>
+      <c r="F47">
+        <v>258.84</v>
+      </c>
+      <c r="G47">
+        <v>1.23</v>
+      </c>
+      <c r="H47">
+        <v>286.9</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>16.6</v>
+      </c>
+      <c r="K47">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L47">
+        <v>11.5</v>
+      </c>
+      <c r="M47">
+        <v>61.81099200000001</v>
+      </c>
+      <c r="N47">
+        <v>-50.31099200000001</v>
+      </c>
+      <c r="O47">
+        <v>-7.546648800000003</v>
+      </c>
+      <c r="P47">
+        <v>-42.76434320000001</v>
+      </c>
+      <c r="Q47">
+        <v>-37.66434320000001</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1802789496800562</v>
+      </c>
+      <c r="T47">
+        <v>1.983890418077353</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.02790765758944622</v>
+      </c>
+      <c r="W47">
+        <v>0.2321356513676402</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.1860510505963081</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.205614465439469</v>
+      </c>
+      <c r="C48">
+        <v>19.3249185216963</v>
+      </c>
+      <c r="D48">
+        <v>282.6869185216963</v>
+      </c>
+      <c r="E48">
+        <v>-23.70799999999997</v>
+      </c>
+      <c r="F48">
+        <v>264.592</v>
+      </c>
+      <c r="G48">
+        <v>1.23</v>
+      </c>
+      <c r="H48">
+        <v>286.9</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>16.6</v>
+      </c>
+      <c r="K48">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L48">
+        <v>11.5</v>
+      </c>
+      <c r="M48">
+        <v>63.18456960000001</v>
+      </c>
+      <c r="N48">
+        <v>-51.68456960000001</v>
+      </c>
+      <c r="O48">
+        <v>-7.752685440000002</v>
+      </c>
+      <c r="P48">
+        <v>-43.93188416000001</v>
+      </c>
+      <c r="Q48">
+        <v>-38.83188416000001</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1828989302296869</v>
+      </c>
+      <c r="T48">
+        <v>2.02062912952323</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.02730096938098</v>
+      </c>
+      <c r="W48">
+        <v>0.232280528511822</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.1820064625398666</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.207614465439469</v>
+      </c>
+      <c r="C49">
+        <v>10.22383445137348</v>
+      </c>
+      <c r="D49">
+        <v>279.3378344513735</v>
+      </c>
+      <c r="E49">
+        <v>-17.95599999999996</v>
+      </c>
+      <c r="F49">
+        <v>270.3440000000001</v>
+      </c>
+      <c r="G49">
+        <v>1.23</v>
+      </c>
+      <c r="H49">
+        <v>286.9</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>16.6</v>
+      </c>
+      <c r="K49">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L49">
+        <v>11.5</v>
+      </c>
+      <c r="M49">
+        <v>64.55814720000002</v>
+      </c>
+      <c r="N49">
+        <v>-53.05814720000002</v>
+      </c>
+      <c r="O49">
+        <v>-7.958722080000005</v>
+      </c>
+      <c r="P49">
+        <v>-45.09942512000002</v>
+      </c>
+      <c r="Q49">
+        <v>-39.99942512000002</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1856177779698696</v>
+      </c>
+      <c r="T49">
+        <v>2.058754207438762</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.02672009769202298</v>
+      </c>
+      <c r="W49">
+        <v>0.2324192406711449</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.1781339846134865</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.209614465439469</v>
+      </c>
+      <c r="C50">
+        <v>1.201176621163427</v>
+      </c>
+      <c r="D50">
+        <v>276.0671766211634</v>
+      </c>
+      <c r="E50">
+        <v>-12.20400000000001</v>
+      </c>
+      <c r="F50">
+        <v>276.096</v>
+      </c>
+      <c r="G50">
+        <v>1.23</v>
+      </c>
+      <c r="H50">
+        <v>286.9</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>16.6</v>
+      </c>
+      <c r="K50">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L50">
+        <v>11.5</v>
+      </c>
+      <c r="M50">
+        <v>65.9317248</v>
+      </c>
+      <c r="N50">
+        <v>-54.4317248</v>
+      </c>
+      <c r="O50">
+        <v>-8.16475872</v>
+      </c>
+      <c r="P50">
+        <v>-46.26696608</v>
+      </c>
+      <c r="Q50">
+        <v>-41.16696607999999</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1884411967769825</v>
+      </c>
+      <c r="T50">
+        <v>2.098345634504892</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.02616342899010584</v>
+      </c>
+      <c r="W50">
+        <v>0.2325521731571628</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.1744228599340389</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.211614465439469</v>
+      </c>
+      <c r="C51">
+        <v>-7.745777874331168</v>
+      </c>
+      <c r="D51">
+        <v>272.8722221256688</v>
+      </c>
+      <c r="E51">
+        <v>-6.451999999999998</v>
+      </c>
+      <c r="F51">
+        <v>281.848</v>
+      </c>
+      <c r="G51">
+        <v>1.23</v>
+      </c>
+      <c r="H51">
+        <v>286.9</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>16.6</v>
+      </c>
+      <c r="K51">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L51">
+        <v>11.5</v>
+      </c>
+      <c r="M51">
+        <v>67.3053024</v>
+      </c>
+      <c r="N51">
+        <v>-55.8053024</v>
+      </c>
+      <c r="O51">
+        <v>-8.370795360000001</v>
+      </c>
+      <c r="P51">
+        <v>-47.43450704</v>
+      </c>
+      <c r="Q51">
+        <v>-42.33450704</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1913753378902567</v>
+      </c>
+      <c r="T51">
+        <v>2.139489666554008</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.02562948145969552</v>
+      </c>
+      <c r="W51">
+        <v>0.2326796798274247</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.1708632097313034</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.213614465439469</v>
+      </c>
+      <c r="C52">
+        <v>-16.61962733272344</v>
+      </c>
+      <c r="D52">
+        <v>269.7503726672766</v>
+      </c>
+      <c r="E52">
+        <v>-0.6999999999999886</v>
+      </c>
+      <c r="F52">
+        <v>287.6</v>
+      </c>
+      <c r="G52">
+        <v>1.23</v>
+      </c>
+      <c r="H52">
+        <v>286.9</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>16.6</v>
+      </c>
+      <c r="K52">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L52">
+        <v>11.5</v>
+      </c>
+      <c r="M52">
+        <v>68.67888000000001</v>
+      </c>
+      <c r="N52">
+        <v>-57.17888000000001</v>
+      </c>
+      <c r="O52">
+        <v>-8.576832000000003</v>
+      </c>
+      <c r="P52">
+        <v>-48.602048</v>
+      </c>
+      <c r="Q52">
+        <v>-43.502048</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1944268446480618</v>
+      </c>
+      <c r="T52">
+        <v>2.182279459885088</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.02511689183050161</v>
+      </c>
+      <c r="W52">
+        <v>0.2328020862308762</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.1674459455366774</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.215614465439469</v>
+      </c>
+      <c r="C53">
+        <v>-25.42285249121733</v>
+      </c>
+      <c r="D53">
+        <v>266.6991475087827</v>
+      </c>
+      <c r="E53">
+        <v>5.052000000000021</v>
+      </c>
+      <c r="F53">
+        <v>293.352</v>
+      </c>
+      <c r="G53">
+        <v>1.23</v>
+      </c>
+      <c r="H53">
+        <v>286.9</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>16.6</v>
+      </c>
+      <c r="K53">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L53">
+        <v>11.5</v>
+      </c>
+      <c r="M53">
+        <v>70.05245760000001</v>
+      </c>
+      <c r="N53">
+        <v>-58.55245760000001</v>
+      </c>
+      <c r="O53">
+        <v>-8.782868640000004</v>
+      </c>
+      <c r="P53">
+        <v>-49.76958896000001</v>
+      </c>
+      <c r="Q53">
+        <v>-44.66958896000001</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1976029027021039</v>
+      </c>
+      <c r="T53">
+        <v>2.226815775392947</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.02462440375539373</v>
+      </c>
+      <c r="W53">
+        <v>0.232919692383212</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.1641626917026249</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2176144654394691</v>
+      </c>
+      <c r="C54">
+        <v>-34.15782310104271</v>
+      </c>
+      <c r="D54">
+        <v>263.7161768989573</v>
+      </c>
+      <c r="E54">
+        <v>10.80400000000003</v>
+      </c>
+      <c r="F54">
+        <v>299.104</v>
+      </c>
+      <c r="G54">
+        <v>1.23</v>
+      </c>
+      <c r="H54">
+        <v>286.9</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>16.6</v>
+      </c>
+      <c r="K54">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L54">
+        <v>11.5</v>
+      </c>
+      <c r="M54">
+        <v>71.42603520000002</v>
+      </c>
+      <c r="N54">
+        <v>-59.92603520000002</v>
+      </c>
+      <c r="O54">
+        <v>-8.988905280000004</v>
+      </c>
+      <c r="P54">
+        <v>-50.93712992000001</v>
+      </c>
+      <c r="Q54">
+        <v>-45.83712992000001</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.2009112965083978</v>
+      </c>
+      <c r="T54">
+        <v>2.273207770713634</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.02415085752932846</v>
+      </c>
+      <c r="W54">
+        <v>0.2330327752219964</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.1610057168621898</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2196144654394691</v>
+      </c>
+      <c r="C55">
+        <v>-42.82680406556892</v>
+      </c>
+      <c r="D55">
+        <v>260.7991959344311</v>
+      </c>
+      <c r="E55">
+        <v>16.55600000000004</v>
+      </c>
+      <c r="F55">
+        <v>304.8560000000001</v>
+      </c>
+      <c r="G55">
+        <v>1.23</v>
+      </c>
+      <c r="H55">
+        <v>286.9</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>16.6</v>
+      </c>
+      <c r="K55">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L55">
+        <v>11.5</v>
+      </c>
+      <c r="M55">
+        <v>72.79961280000002</v>
+      </c>
+      <c r="N55">
+        <v>-61.29961280000002</v>
+      </c>
+      <c r="O55">
+        <v>-9.194941920000005</v>
+      </c>
+      <c r="P55">
+        <v>-52.10467088000001</v>
+      </c>
+      <c r="Q55">
+        <v>-47.00467088000001</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.204360473029853</v>
+      </c>
+      <c r="T55">
+        <v>2.321573893494775</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.02369518097217132</v>
+      </c>
+      <c r="W55">
+        <v>0.2331415907838455</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.1579678731478088</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2216144654394691</v>
+      </c>
+      <c r="C56">
+        <v>-51.43196117551093</v>
+      </c>
+      <c r="D56">
+        <v>257.9460388244891</v>
+      </c>
+      <c r="E56">
+        <v>22.30800000000005</v>
+      </c>
+      <c r="F56">
+        <v>310.6080000000001</v>
+      </c>
+      <c r="G56">
+        <v>1.23</v>
+      </c>
+      <c r="H56">
+        <v>286.9</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>16.6</v>
+      </c>
+      <c r="K56">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L56">
+        <v>11.5</v>
+      </c>
+      <c r="M56">
+        <v>74.17319040000002</v>
+      </c>
+      <c r="N56">
+        <v>-62.67319040000002</v>
+      </c>
+      <c r="O56">
+        <v>-9.400978560000006</v>
+      </c>
+      <c r="P56">
+        <v>-53.27221184000002</v>
+      </c>
+      <c r="Q56">
+        <v>-48.17221184000002</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2079596137478933</v>
+      </c>
+      <c r="T56">
+        <v>2.372042891179444</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.02325638132453852</v>
+      </c>
+      <c r="W56">
+        <v>0.2332463761397002</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.1550425421635901</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2236144654394691</v>
+      </c>
+      <c r="C57">
+        <v>-59.97536647174815</v>
+      </c>
+      <c r="D57">
+        <v>255.1546335282519</v>
+      </c>
+      <c r="E57">
+        <v>28.06000000000006</v>
+      </c>
+      <c r="F57">
+        <v>316.3600000000001</v>
+      </c>
+      <c r="G57">
+        <v>1.23</v>
+      </c>
+      <c r="H57">
+        <v>286.9</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>16.6</v>
+      </c>
+      <c r="K57">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L57">
+        <v>11.5</v>
+      </c>
+      <c r="M57">
+        <v>75.54676800000001</v>
+      </c>
+      <c r="N57">
+        <v>-64.04676800000001</v>
+      </c>
+      <c r="O57">
+        <v>-9.607015200000003</v>
+      </c>
+      <c r="P57">
+        <v>-54.43975280000001</v>
+      </c>
+      <c r="Q57">
+        <v>-49.33975280000001</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2117187162756243</v>
+      </c>
+      <c r="T57">
+        <v>2.424754955427876</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.02283353802772873</v>
+      </c>
+      <c r="W57">
+        <v>0.2333473511189784</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.1522235868515248</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.225614465439469</v>
+      </c>
+      <c r="C58">
+        <v>-68.45900326366376</v>
+      </c>
+      <c r="D58">
+        <v>252.4229967363363</v>
+      </c>
+      <c r="E58">
+        <v>33.81200000000007</v>
+      </c>
+      <c r="F58">
+        <v>322.1120000000001</v>
+      </c>
+      <c r="G58">
+        <v>1.23</v>
+      </c>
+      <c r="H58">
+        <v>286.9</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>16.6</v>
+      </c>
+      <c r="K58">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L58">
+        <v>11.5</v>
+      </c>
+      <c r="M58">
+        <v>76.92034560000002</v>
+      </c>
+      <c r="N58">
+        <v>-65.42034560000002</v>
+      </c>
+      <c r="O58">
+        <v>-9.813051840000004</v>
+      </c>
+      <c r="P58">
+        <v>-55.60729376000002</v>
+      </c>
+      <c r="Q58">
+        <v>-50.50729376000002</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2156486871000703</v>
+      </c>
+      <c r="T58">
+        <v>2.479863022596691</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.02242579627723357</v>
+      </c>
+      <c r="W58">
+        <v>0.2334447198489966</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.1495053085148904</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.227614465439469</v>
+      </c>
+      <c r="C59">
+        <v>-76.88477082854624</v>
+      </c>
+      <c r="D59">
+        <v>249.7492291714539</v>
+      </c>
+      <c r="E59">
+        <v>39.56400000000008</v>
+      </c>
+      <c r="F59">
+        <v>327.8640000000001</v>
+      </c>
+      <c r="G59">
+        <v>1.23</v>
+      </c>
+      <c r="H59">
+        <v>286.9</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>16.6</v>
+      </c>
+      <c r="K59">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L59">
+        <v>11.5</v>
+      </c>
+      <c r="M59">
+        <v>78.29392320000002</v>
+      </c>
+      <c r="N59">
+        <v>-66.79392320000002</v>
+      </c>
+      <c r="O59">
+        <v>-10.01908848</v>
+      </c>
+      <c r="P59">
+        <v>-56.77483472000002</v>
+      </c>
+      <c r="Q59">
+        <v>-51.67483472000001</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2197614472651882</v>
+      </c>
+      <c r="T59">
+        <v>2.537534255680336</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.02203236125482597</v>
+      </c>
+      <c r="W59">
+        <v>0.2335386721323476</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.1468824083655064</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.229614465439469</v>
+      </c>
+      <c r="C60">
+        <v>-85.2544888154529</v>
+      </c>
+      <c r="D60">
+        <v>247.1315111845471</v>
+      </c>
+      <c r="E60">
+        <v>45.31599999999997</v>
+      </c>
+      <c r="F60">
+        <v>333.616</v>
+      </c>
+      <c r="G60">
+        <v>1.23</v>
+      </c>
+      <c r="H60">
+        <v>286.9</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>16.6</v>
+      </c>
+      <c r="K60">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L60">
+        <v>11.5</v>
+      </c>
+      <c r="M60">
+        <v>79.6675008</v>
+      </c>
+      <c r="N60">
+        <v>-68.1675008</v>
+      </c>
+      <c r="O60">
+        <v>-10.22512512</v>
+      </c>
+      <c r="P60">
+        <v>-57.94237568</v>
+      </c>
+      <c r="Q60">
+        <v>-52.84237568</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2240700531524546</v>
+      </c>
+      <c r="T60">
+        <v>2.597951737958438</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.02165249295732898</v>
+      </c>
+      <c r="W60">
+        <v>0.2336293846817898</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.1443499530488598</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.231614465439469</v>
+      </c>
+      <c r="C61">
+        <v>-93.56990137499591</v>
+      </c>
+      <c r="D61">
+        <v>244.5680986250041</v>
+      </c>
+      <c r="E61">
+        <v>51.06799999999998</v>
+      </c>
+      <c r="F61">
+        <v>339.368</v>
+      </c>
+      <c r="G61">
+        <v>1.23</v>
+      </c>
+      <c r="H61">
+        <v>286.9</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>16.6</v>
+      </c>
+      <c r="K61">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L61">
+        <v>11.5</v>
+      </c>
+      <c r="M61">
+        <v>81.0410784</v>
+      </c>
+      <c r="N61">
+        <v>-69.5410784</v>
+      </c>
+      <c r="O61">
+        <v>-10.43116176</v>
+      </c>
+      <c r="P61">
+        <v>-59.10991664</v>
+      </c>
+      <c r="Q61">
+        <v>-54.00991664</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2285888349366607</v>
+      </c>
+      <c r="T61">
+        <v>2.66131641449401</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.02128550155127255</v>
+      </c>
+      <c r="W61">
+        <v>0.2337170222295561</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.1419033436751503</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.233614465439469</v>
+      </c>
+      <c r="C62">
+        <v>-101.8326810347434</v>
+      </c>
+      <c r="D62">
+        <v>242.0573189652566</v>
+      </c>
+      <c r="E62">
+        <v>56.81999999999999</v>
+      </c>
+      <c r="F62">
+        <v>345.12</v>
+      </c>
+      <c r="G62">
+        <v>1.23</v>
+      </c>
+      <c r="H62">
+        <v>286.9</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>16.6</v>
+      </c>
+      <c r="K62">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L62">
+        <v>11.5</v>
+      </c>
+      <c r="M62">
+        <v>82.41465600000001</v>
+      </c>
+      <c r="N62">
+        <v>-70.91465600000001</v>
+      </c>
+      <c r="O62">
+        <v>-10.6371984</v>
+      </c>
+      <c r="P62">
+        <v>-60.27745760000001</v>
+      </c>
+      <c r="Q62">
+        <v>-55.1774576</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2333335558100773</v>
+      </c>
+      <c r="T62">
+        <v>2.72784932485636</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.02093074319208467</v>
+      </c>
+      <c r="W62">
+        <v>0.2338017385257302</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.1395382879472311</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.235614465439469</v>
+      </c>
+      <c r="C63">
+        <v>-110.0444323383355</v>
+      </c>
+      <c r="D63">
+        <v>239.5975676616645</v>
+      </c>
+      <c r="E63">
+        <v>62.572</v>
+      </c>
+      <c r="F63">
+        <v>350.872</v>
+      </c>
+      <c r="G63">
+        <v>1.23</v>
+      </c>
+      <c r="H63">
+        <v>286.9</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>16.6</v>
+      </c>
+      <c r="K63">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L63">
+        <v>11.5</v>
+      </c>
+      <c r="M63">
+        <v>83.78823360000001</v>
+      </c>
+      <c r="N63">
+        <v>-72.28823360000001</v>
+      </c>
+      <c r="O63">
+        <v>-10.84323504</v>
+      </c>
+      <c r="P63">
+        <v>-61.44499856000001</v>
+      </c>
+      <c r="Q63">
+        <v>-56.34499856000001</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2383215957026434</v>
+      </c>
+      <c r="T63">
+        <v>2.797794179339856</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.02058761625450951</v>
+      </c>
+      <c r="W63">
+        <v>0.2338836772384231</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.1372507750300634</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.237614465439469</v>
+      </c>
+      <c r="C64">
+        <v>-118.2066952649495</v>
+      </c>
+      <c r="D64">
+        <v>237.1873047350505</v>
+      </c>
+      <c r="E64">
+        <v>68.32400000000001</v>
+      </c>
+      <c r="F64">
+        <v>356.624</v>
+      </c>
+      <c r="G64">
+        <v>1.23</v>
+      </c>
+      <c r="H64">
+        <v>286.9</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>16.6</v>
+      </c>
+      <c r="K64">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L64">
+        <v>11.5</v>
+      </c>
+      <c r="M64">
+        <v>85.16181120000002</v>
+      </c>
+      <c r="N64">
+        <v>-73.66181120000002</v>
+      </c>
+      <c r="O64">
+        <v>-11.04927168</v>
+      </c>
+      <c r="P64">
+        <v>-62.61253952000001</v>
+      </c>
+      <c r="Q64">
+        <v>-57.51253952000001</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2435721640106077</v>
+      </c>
+      <c r="T64">
+        <v>2.871420341954063</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.02025555792782387</v>
+      </c>
+      <c r="W64">
+        <v>0.2339629727668357</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.1350370528521592</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.239614465439469</v>
+      </c>
+      <c r="C65">
+        <v>-126.3209484444302</v>
+      </c>
+      <c r="D65">
+        <v>234.8250515555698</v>
+      </c>
+      <c r="E65">
+        <v>74.07600000000002</v>
+      </c>
+      <c r="F65">
+        <v>362.376</v>
+      </c>
+      <c r="G65">
+        <v>1.23</v>
+      </c>
+      <c r="H65">
+        <v>286.9</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>16.6</v>
+      </c>
+      <c r="K65">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L65">
+        <v>11.5</v>
+      </c>
+      <c r="M65">
+        <v>86.53538880000001</v>
+      </c>
+      <c r="N65">
+        <v>-75.03538880000001</v>
+      </c>
+      <c r="O65">
+        <v>-11.25530832</v>
+      </c>
+      <c r="P65">
+        <v>-63.78008048</v>
+      </c>
+      <c r="Q65">
+        <v>-58.68008048</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2491065468217052</v>
+      </c>
+      <c r="T65">
+        <v>2.949026297142011</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.01993404113531873</v>
+      </c>
+      <c r="W65">
+        <v>0.2340397509768859</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.1328936075687915</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.241614465439469</v>
+      </c>
+      <c r="C66">
+        <v>-134.3886121821892</v>
+      </c>
+      <c r="D66">
+        <v>232.5093878178109</v>
+      </c>
+      <c r="E66">
+        <v>79.82800000000003</v>
+      </c>
+      <c r="F66">
+        <v>368.128</v>
+      </c>
+      <c r="G66">
+        <v>1.23</v>
+      </c>
+      <c r="H66">
+        <v>286.9</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>16.6</v>
+      </c>
+      <c r="K66">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L66">
+        <v>11.5</v>
+      </c>
+      <c r="M66">
+        <v>87.90896640000001</v>
+      </c>
+      <c r="N66">
+        <v>-76.40896640000001</v>
+      </c>
+      <c r="O66">
+        <v>-11.46134496</v>
+      </c>
+      <c r="P66">
+        <v>-64.94762144000001</v>
+      </c>
+      <c r="Q66">
+        <v>-59.84762144</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2549483953445303</v>
+      </c>
+      <c r="T66">
+        <v>3.030943694284845</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.01962257174257938</v>
+      </c>
+      <c r="W66">
+        <v>0.2341141298678721</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.1308171449505292</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.243614465439469</v>
+      </c>
+      <c r="C67">
+        <v>-142.4110513068761</v>
+      </c>
+      <c r="D67">
+        <v>230.2389486931239</v>
+      </c>
+      <c r="E67">
+        <v>85.58000000000004</v>
+      </c>
+      <c r="F67">
+        <v>373.8800000000001</v>
+      </c>
+      <c r="G67">
+        <v>1.23</v>
+      </c>
+      <c r="H67">
+        <v>286.9</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>16.6</v>
+      </c>
+      <c r="K67">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L67">
+        <v>11.5</v>
+      </c>
+      <c r="M67">
+        <v>89.28254400000002</v>
+      </c>
+      <c r="N67">
+        <v>-77.78254400000002</v>
+      </c>
+      <c r="O67">
+        <v>-11.6673816</v>
+      </c>
+      <c r="P67">
+        <v>-66.11516240000002</v>
+      </c>
+      <c r="Q67">
+        <v>-61.01516240000002</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2611240637829455</v>
+      </c>
+      <c r="T67">
+        <v>3.117542085550126</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.01932068602346277</v>
+      </c>
+      <c r="W67">
+        <v>0.2341862201775971</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.1288045734897518</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.245614465439469</v>
+      </c>
+      <c r="C68">
+        <v>-150.3895778528204</v>
+      </c>
+      <c r="D68">
+        <v>228.0124221471796</v>
+      </c>
+      <c r="E68">
+        <v>91.33200000000005</v>
+      </c>
+      <c r="F68">
+        <v>379.6320000000001</v>
+      </c>
+      <c r="G68">
+        <v>1.23</v>
+      </c>
+      <c r="H68">
+        <v>286.9</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>16.6</v>
+      </c>
+      <c r="K68">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L68">
+        <v>11.5</v>
+      </c>
+      <c r="M68">
+        <v>90.65612160000002</v>
+      </c>
+      <c r="N68">
+        <v>-79.15612160000002</v>
+      </c>
+      <c r="O68">
+        <v>-11.87341824</v>
+      </c>
+      <c r="P68">
+        <v>-67.28270336000001</v>
+      </c>
+      <c r="Q68">
+        <v>-62.18270336000001</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2676630068353851</v>
+      </c>
+      <c r="T68">
+        <v>3.209234499831012</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.01902794835644061</v>
+      </c>
+      <c r="W68">
+        <v>0.234256125932482</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.1268529890429374</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2476144654394691</v>
+      </c>
+      <c r="C69">
+        <v>-158.325453588319</v>
+      </c>
+      <c r="D69">
+        <v>225.828546411681</v>
+      </c>
+      <c r="E69">
+        <v>97.08400000000006</v>
+      </c>
+      <c r="F69">
+        <v>385.3840000000001</v>
+      </c>
+      <c r="G69">
+        <v>1.23</v>
+      </c>
+      <c r="H69">
+        <v>286.9</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>16.6</v>
+      </c>
+      <c r="K69">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L69">
+        <v>11.5</v>
+      </c>
+      <c r="M69">
+        <v>92.02969920000002</v>
+      </c>
+      <c r="N69">
+        <v>-80.52969920000002</v>
+      </c>
+      <c r="O69">
+        <v>-12.07945488000001</v>
+      </c>
+      <c r="P69">
+        <v>-68.45024432000002</v>
+      </c>
+      <c r="Q69">
+        <v>-63.35024432000002</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2745982494667604</v>
+      </c>
+      <c r="T69">
+        <v>3.306484030128922</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.01874394912724</v>
+      </c>
+      <c r="W69">
+        <v>0.2343239449484151</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.1249596608482667</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.249614465439469</v>
+      </c>
+      <c r="C70">
+        <v>-166.2198924000097</v>
+      </c>
+      <c r="D70">
+        <v>223.6861075999904</v>
+      </c>
+      <c r="E70">
+        <v>102.8360000000001</v>
+      </c>
+      <c r="F70">
+        <v>391.1360000000001</v>
+      </c>
+      <c r="G70">
+        <v>1.23</v>
+      </c>
+      <c r="H70">
+        <v>286.9</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>16.6</v>
+      </c>
+      <c r="K70">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L70">
+        <v>11.5</v>
+      </c>
+      <c r="M70">
+        <v>93.40327680000003</v>
+      </c>
+      <c r="N70">
+        <v>-81.90327680000003</v>
+      </c>
+      <c r="O70">
+        <v>-12.28549152000001</v>
+      </c>
+      <c r="P70">
+        <v>-69.61778528000002</v>
+      </c>
+      <c r="Q70">
+        <v>-64.51778528000003</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2819669447625966</v>
+      </c>
+      <c r="T70">
+        <v>3.409811656070451</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.0184683028165453</v>
+      </c>
+      <c r="W70">
+        <v>0.234389769287409</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.1231220187769686</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2516144654394691</v>
+      </c>
+      <c r="C71">
+        <v>-174.0740625427966</v>
+      </c>
+      <c r="D71">
+        <v>221.5839374572035</v>
+      </c>
+      <c r="E71">
+        <v>108.5880000000001</v>
+      </c>
+      <c r="F71">
+        <v>396.8880000000001</v>
+      </c>
+      <c r="G71">
+        <v>1.23</v>
+      </c>
+      <c r="H71">
+        <v>286.9</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>16.6</v>
+      </c>
+      <c r="K71">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L71">
+        <v>11.5</v>
+      </c>
+      <c r="M71">
+        <v>94.77685440000003</v>
+      </c>
+      <c r="N71">
+        <v>-83.27685440000003</v>
+      </c>
+      <c r="O71">
+        <v>-12.49152816000001</v>
+      </c>
+      <c r="P71">
+        <v>-70.78532624000003</v>
+      </c>
+      <c r="Q71">
+        <v>-65.68532624000002</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2898110397549385</v>
+      </c>
+      <c r="T71">
+        <v>3.519805580459821</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.01820064625398667</v>
+      </c>
+      <c r="W71">
+        <v>0.234453685674548</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.1213376416932445</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.253614465439469</v>
+      </c>
+      <c r="C72">
+        <v>-181.8890887640882</v>
+      </c>
+      <c r="D72">
+        <v>219.5209112359118</v>
+      </c>
+      <c r="E72">
+        <v>114.34</v>
+      </c>
+      <c r="F72">
+        <v>402.64</v>
+      </c>
+      <c r="G72">
+        <v>1.23</v>
+      </c>
+      <c r="H72">
+        <v>286.9</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>16.6</v>
+      </c>
+      <c r="K72">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L72">
+        <v>11.5</v>
+      </c>
+      <c r="M72">
+        <v>96.15043200000001</v>
+      </c>
+      <c r="N72">
+        <v>-84.65043200000001</v>
+      </c>
+      <c r="O72">
+        <v>-12.6975648</v>
+      </c>
+      <c r="P72">
+        <v>-71.9528672</v>
+      </c>
+      <c r="Q72">
+        <v>-66.85286719999999</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2981780744134364</v>
+      </c>
+      <c r="T72">
+        <v>3.637132433141814</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.01794063702178686</v>
+      </c>
+      <c r="W72">
+        <v>0.2345157758791973</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.1196042468119124</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.255614465439469</v>
+      </c>
+      <c r="C73">
+        <v>-189.6660543104687</v>
+      </c>
+      <c r="D73">
+        <v>217.4959456895313</v>
+      </c>
+      <c r="E73">
+        <v>120.092</v>
+      </c>
+      <c r="F73">
+        <v>408.392</v>
+      </c>
+      <c r="G73">
+        <v>1.23</v>
+      </c>
+      <c r="H73">
+        <v>286.9</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>16.6</v>
+      </c>
+      <c r="K73">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L73">
+        <v>11.5</v>
+      </c>
+      <c r="M73">
+        <v>97.5240096</v>
+      </c>
+      <c r="N73">
+        <v>-86.0240096</v>
+      </c>
+      <c r="O73">
+        <v>-12.90360144</v>
+      </c>
+      <c r="P73">
+        <v>-73.12040816</v>
+      </c>
+      <c r="Q73">
+        <v>-68.02040815999999</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.3071221459449342</v>
+      </c>
+      <c r="T73">
+        <v>3.762550792905324</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.01768795199331099</v>
+      </c>
+      <c r="W73">
+        <v>0.2345761170639974</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.1179196799554066</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.257614465439469</v>
+      </c>
+      <c r="C74">
+        <v>-197.4060028243178</v>
+      </c>
+      <c r="D74">
+        <v>215.5079971756822</v>
+      </c>
+      <c r="E74">
+        <v>125.844</v>
+      </c>
+      <c r="F74">
+        <v>414.144</v>
+      </c>
+      <c r="G74">
+        <v>1.23</v>
+      </c>
+      <c r="H74">
+        <v>286.9</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>16.6</v>
+      </c>
+      <c r="K74">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L74">
+        <v>11.5</v>
+      </c>
+      <c r="M74">
+        <v>98.8975872</v>
+      </c>
+      <c r="N74">
+        <v>-87.3975872</v>
+      </c>
+      <c r="O74">
+        <v>-13.10963808</v>
+      </c>
+      <c r="P74">
+        <v>-74.28794912000001</v>
+      </c>
+      <c r="Q74">
+        <v>-69.18794912000001</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.3167050797286818</v>
+      </c>
+      <c r="T74">
+        <v>3.896927606937657</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.0174422859934039</v>
+      </c>
+      <c r="W74">
+        <v>0.2346347821047751</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.1162819066226926</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.259614465439469</v>
+      </c>
+      <c r="C75">
+        <v>-205.1099401373627</v>
+      </c>
+      <c r="D75">
+        <v>213.5560598626374</v>
+      </c>
+      <c r="E75">
+        <v>131.596</v>
+      </c>
+      <c r="F75">
+        <v>419.896</v>
+      </c>
+      <c r="G75">
+        <v>1.23</v>
+      </c>
+      <c r="H75">
+        <v>286.9</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>16.6</v>
+      </c>
+      <c r="K75">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L75">
+        <v>11.5</v>
+      </c>
+      <c r="M75">
+        <v>100.2711648</v>
+      </c>
+      <c r="N75">
+        <v>-88.77116480000001</v>
+      </c>
+      <c r="O75">
+        <v>-13.31567472</v>
+      </c>
+      <c r="P75">
+        <v>-75.45549008</v>
+      </c>
+      <c r="Q75">
+        <v>-70.35549008000001</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3269978604593737</v>
+      </c>
+      <c r="T75">
+        <v>4.041258259046459</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.01720335056883672</v>
+      </c>
+      <c r="W75">
+        <v>0.2346918398841618</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.1146890037922448</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.261614465439469</v>
+      </c>
+      <c r="C76">
+        <v>-212.778835967635</v>
+      </c>
+      <c r="D76">
+        <v>211.6391640323651</v>
+      </c>
+      <c r="E76">
+        <v>137.348</v>
+      </c>
+      <c r="F76">
+        <v>425.648</v>
+      </c>
+      <c r="G76">
+        <v>1.23</v>
+      </c>
+      <c r="H76">
+        <v>286.9</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>16.6</v>
+      </c>
+      <c r="K76">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L76">
+        <v>11.5</v>
+      </c>
+      <c r="M76">
+        <v>101.6447424</v>
+      </c>
+      <c r="N76">
+        <v>-90.14474240000001</v>
+      </c>
+      <c r="O76">
+        <v>-13.52171136</v>
+      </c>
+      <c r="P76">
+        <v>-76.62303104</v>
+      </c>
+      <c r="Q76">
+        <v>-71.52303104000001</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.338082393553965</v>
+      </c>
+      <c r="T76">
+        <v>4.196691269009785</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.01697087285844703</v>
+      </c>
+      <c r="W76">
+        <v>0.2347473555614029</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.1131391523896469</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.263614465439469</v>
+      </c>
+      <c r="C77">
+        <v>-220.4136255258483</v>
+      </c>
+      <c r="D77">
+        <v>209.7563744741518</v>
+      </c>
+      <c r="E77">
+        <v>143.1</v>
+      </c>
+      <c r="F77">
+        <v>431.4</v>
+      </c>
+      <c r="G77">
+        <v>1.23</v>
+      </c>
+      <c r="H77">
+        <v>286.9</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>16.6</v>
+      </c>
+      <c r="K77">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L77">
+        <v>11.5</v>
+      </c>
+      <c r="M77">
+        <v>103.01832</v>
+      </c>
+      <c r="N77">
+        <v>-91.51832000000002</v>
+      </c>
+      <c r="O77">
+        <v>-13.72774800000001</v>
+      </c>
+      <c r="P77">
+        <v>-77.79057200000001</v>
+      </c>
+      <c r="Q77">
+        <v>-72.690572</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3500536892961236</v>
+      </c>
+      <c r="T77">
+        <v>4.364558919770176</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.01674459455366774</v>
+      </c>
+      <c r="W77">
+        <v>0.2348013908205842</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.1116306303577849</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.265614465439469</v>
+      </c>
+      <c r="C78">
+        <v>-228.0152110367877</v>
+      </c>
+      <c r="D78">
+        <v>207.9067889632124</v>
+      </c>
+      <c r="E78">
+        <v>148.852</v>
+      </c>
+      <c r="F78">
+        <v>437.152</v>
+      </c>
+      <c r="G78">
+        <v>1.23</v>
+      </c>
+      <c r="H78">
+        <v>286.9</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>16.6</v>
+      </c>
+      <c r="K78">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L78">
+        <v>11.5</v>
+      </c>
+      <c r="M78">
+        <v>104.3918976</v>
+      </c>
+      <c r="N78">
+        <v>-92.89189760000002</v>
+      </c>
+      <c r="O78">
+        <v>-13.93378464000001</v>
+      </c>
+      <c r="P78">
+        <v>-78.95811296000002</v>
+      </c>
+      <c r="Q78">
+        <v>-73.85811296000003</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3630225930167956</v>
+      </c>
+      <c r="T78">
+        <v>4.546415541427268</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.01652427094111947</v>
+      </c>
+      <c r="W78">
+        <v>0.2348540040992607</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.1101618062741299</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2676144654394691</v>
+      </c>
+      <c r="C79">
+        <v>-235.5844631809115</v>
+      </c>
+      <c r="D79">
+        <v>206.0895368190885</v>
+      </c>
+      <c r="E79">
+        <v>154.604</v>
+      </c>
+      <c r="F79">
+        <v>442.9040000000001</v>
+      </c>
+      <c r="G79">
+        <v>1.23</v>
+      </c>
+      <c r="H79">
+        <v>286.9</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>16.6</v>
+      </c>
+      <c r="K79">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L79">
+        <v>11.5</v>
+      </c>
+      <c r="M79">
+        <v>105.7654752</v>
+      </c>
+      <c r="N79">
+        <v>-94.26547520000001</v>
+      </c>
+      <c r="O79">
+        <v>-14.13982128</v>
+      </c>
+      <c r="P79">
+        <v>-80.12565392</v>
+      </c>
+      <c r="Q79">
+        <v>-75.02565392</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3771192274957866</v>
+      </c>
+      <c r="T79">
+        <v>4.744085782358888</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.01630967001980624</v>
+      </c>
+      <c r="W79">
+        <v>0.2349052507992703</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.1087311334653749</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.269614465439469</v>
+      </c>
+      <c r="C80">
+        <v>-243.1222224610043</v>
+      </c>
+      <c r="D80">
+        <v>204.3037775389958</v>
+      </c>
+      <c r="E80">
+        <v>160.3560000000001</v>
+      </c>
+      <c r="F80">
+        <v>448.6560000000001</v>
+      </c>
+      <c r="G80">
+        <v>1.23</v>
+      </c>
+      <c r="H80">
+        <v>286.9</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>16.6</v>
+      </c>
+      <c r="K80">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L80">
+        <v>11.5</v>
+      </c>
+      <c r="M80">
+        <v>107.1390528</v>
+      </c>
+      <c r="N80">
+        <v>-95.63905280000002</v>
+      </c>
+      <c r="O80">
+        <v>-14.34585792</v>
+      </c>
+      <c r="P80">
+        <v>-81.29319488000002</v>
+      </c>
+      <c r="Q80">
+        <v>-76.19319488000002</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3924973742001405</v>
+      </c>
+      <c r="T80">
+        <v>4.959726045193382</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.01610057168621898</v>
+      </c>
+      <c r="W80">
+        <v>0.2349551834813309</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.1073371445747932</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.271614465439469</v>
+      </c>
+      <c r="C81">
+        <v>-250.6293004983878</v>
+      </c>
+      <c r="D81">
+        <v>202.5486995016123</v>
+      </c>
+      <c r="E81">
+        <v>166.1080000000001</v>
+      </c>
+      <c r="F81">
+        <v>454.4080000000001</v>
+      </c>
+      <c r="G81">
+        <v>1.23</v>
+      </c>
+      <c r="H81">
+        <v>286.9</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>16.6</v>
+      </c>
+      <c r="K81">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L81">
+        <v>11.5</v>
+      </c>
+      <c r="M81">
+        <v>108.5126304</v>
+      </c>
+      <c r="N81">
+        <v>-97.01263040000002</v>
+      </c>
+      <c r="O81">
+        <v>-14.55189456</v>
+      </c>
+      <c r="P81">
+        <v>-82.46073584000001</v>
+      </c>
+      <c r="Q81">
+        <v>-77.36073584000002</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.4093401063049092</v>
+      </c>
+      <c r="T81">
+        <v>5.195903475916878</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.01589676698133013</v>
+      </c>
+      <c r="W81">
+        <v>0.2350038520448584</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.1059784465422008</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.273614465439469</v>
+      </c>
+      <c r="C82">
+        <v>-258.1064812628908</v>
+      </c>
+      <c r="D82">
+        <v>200.8235187371093</v>
+      </c>
+      <c r="E82">
+        <v>171.8600000000001</v>
+      </c>
+      <c r="F82">
+        <v>460.1600000000001</v>
+      </c>
+      <c r="G82">
+        <v>1.23</v>
+      </c>
+      <c r="H82">
+        <v>286.9</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>16.6</v>
+      </c>
+      <c r="K82">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L82">
+        <v>11.5</v>
+      </c>
+      <c r="M82">
+        <v>109.886208</v>
+      </c>
+      <c r="N82">
+        <v>-98.38620800000002</v>
+      </c>
+      <c r="O82">
+        <v>-14.75793120000001</v>
+      </c>
+      <c r="P82">
+        <v>-83.62827680000002</v>
+      </c>
+      <c r="Q82">
+        <v>-78.52827680000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4278671116201547</v>
+      </c>
+      <c r="T82">
+        <v>5.455698649712722</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.0156980573940635</v>
+      </c>
+      <c r="W82">
+        <v>0.2350513038942977</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.1046537159604233</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.275614465439469</v>
+      </c>
+      <c r="C83">
+        <v>-265.5545222404926</v>
+      </c>
+      <c r="D83">
+        <v>199.1274777595075</v>
+      </c>
+      <c r="E83">
+        <v>177.6120000000001</v>
+      </c>
+      <c r="F83">
+        <v>465.9120000000001</v>
+      </c>
+      <c r="G83">
+        <v>1.23</v>
+      </c>
+      <c r="H83">
+        <v>286.9</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>16.6</v>
+      </c>
+      <c r="K83">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L83">
+        <v>11.5</v>
+      </c>
+      <c r="M83">
+        <v>111.2597856</v>
+      </c>
+      <c r="N83">
+        <v>-99.75978560000003</v>
+      </c>
+      <c r="O83">
+        <v>-14.96396784000001</v>
+      </c>
+      <c r="P83">
+        <v>-84.79581776000002</v>
+      </c>
+      <c r="Q83">
+        <v>-79.69581776000001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.4483443280212155</v>
+      </c>
+      <c r="T83">
+        <v>5.742840683908129</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.01550425421635901</v>
+      </c>
+      <c r="W83">
+        <v>0.2350975840931335</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.1033616947757268</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.277614465439469</v>
+      </c>
+      <c r="C84">
+        <v>-272.9741555422952</v>
+      </c>
+      <c r="D84">
+        <v>197.4598444577049</v>
+      </c>
+      <c r="E84">
+        <v>183.3640000000001</v>
+      </c>
+      <c r="F84">
+        <v>471.6640000000001</v>
+      </c>
+      <c r="G84">
+        <v>1.23</v>
+      </c>
+      <c r="H84">
+        <v>286.9</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>16.6</v>
+      </c>
+      <c r="K84">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L84">
+        <v>11.5</v>
+      </c>
+      <c r="M84">
+        <v>112.6333632</v>
+      </c>
+      <c r="N84">
+        <v>-101.1333632</v>
+      </c>
+      <c r="O84">
+        <v>-15.17000448000001</v>
+      </c>
+      <c r="P84">
+        <v>-85.96335872000003</v>
+      </c>
+      <c r="Q84">
+        <v>-80.86335872000004</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4710967906890608</v>
+      </c>
+      <c r="T84">
+        <v>6.061887388569692</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.0153151779454278</v>
+      </c>
+      <c r="W84">
+        <v>0.2351427355066318</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.102101186302852</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2796144654394691</v>
+      </c>
+      <c r="C85">
+        <v>-280.366088958233</v>
+      </c>
+      <c r="D85">
+        <v>195.8199110417671</v>
+      </c>
+      <c r="E85">
+        <v>189.116</v>
+      </c>
+      <c r="F85">
+        <v>477.4160000000001</v>
+      </c>
+      <c r="G85">
+        <v>1.23</v>
+      </c>
+      <c r="H85">
+        <v>286.9</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>16.6</v>
+      </c>
+      <c r="K85">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L85">
+        <v>11.5</v>
+      </c>
+      <c r="M85">
+        <v>114.0069408</v>
+      </c>
+      <c r="N85">
+        <v>-102.5069408</v>
+      </c>
+      <c r="O85">
+        <v>-15.37604112000001</v>
+      </c>
+      <c r="P85">
+        <v>-87.13089968000001</v>
+      </c>
+      <c r="Q85">
+        <v>-82.03089968</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4965260136707703</v>
+      </c>
+      <c r="T85">
+        <v>6.418468999662027</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.01513065772921783</v>
+      </c>
+      <c r="W85">
+        <v>0.2351867989342628</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.1008710515281188</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.281614465439469</v>
+      </c>
+      <c r="C86">
+        <v>-287.7310069587099</v>
+      </c>
+      <c r="D86">
+        <v>194.2069930412901</v>
+      </c>
+      <c r="E86">
+        <v>194.868</v>
+      </c>
+      <c r="F86">
+        <v>483.168</v>
+      </c>
+      <c r="G86">
+        <v>1.23</v>
+      </c>
+      <c r="H86">
+        <v>286.9</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>16.6</v>
+      </c>
+      <c r="K86">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L86">
+        <v>11.5</v>
+      </c>
+      <c r="M86">
+        <v>115.3805184</v>
+      </c>
+      <c r="N86">
+        <v>-103.8805184</v>
+      </c>
+      <c r="O86">
+        <v>-15.58207776</v>
+      </c>
+      <c r="P86">
+        <v>-88.29844064000001</v>
+      </c>
+      <c r="Q86">
+        <v>-83.19844064</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.5251338895251931</v>
+      </c>
+      <c r="T86">
+        <v>6.8196233121409</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.01495053085148905</v>
+      </c>
+      <c r="W86">
+        <v>0.2352298132326644</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.09967020567659368</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2836144654394691</v>
+      </c>
+      <c r="C87">
+        <v>-295.0695716471378</v>
+      </c>
+      <c r="D87">
+        <v>192.6204283528623</v>
+      </c>
+      <c r="E87">
+        <v>200.62</v>
+      </c>
+      <c r="F87">
+        <v>488.92</v>
+      </c>
+      <c r="G87">
+        <v>1.23</v>
+      </c>
+      <c r="H87">
+        <v>286.9</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>16.6</v>
+      </c>
+      <c r="K87">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L87">
+        <v>11.5</v>
+      </c>
+      <c r="M87">
+        <v>116.754096</v>
+      </c>
+      <c r="N87">
+        <v>-105.254096</v>
+      </c>
+      <c r="O87">
+        <v>-15.7881144</v>
+      </c>
+      <c r="P87">
+        <v>-89.46598160000001</v>
+      </c>
+      <c r="Q87">
+        <v>-84.3659816</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.5575561488268728</v>
+      </c>
+      <c r="T87">
+        <v>7.274264866283627</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.01477464225323624</v>
+      </c>
+      <c r="W87">
+        <v>0.2352718154299272</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.09849761502157495</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2856144654394691</v>
+      </c>
+      <c r="C88">
+        <v>-302.3824236661626</v>
+      </c>
+      <c r="D88">
+        <v>191.0595763338374</v>
+      </c>
+      <c r="E88">
+        <v>206.372</v>
+      </c>
+      <c r="F88">
+        <v>494.672</v>
+      </c>
+      <c r="G88">
+        <v>1.23</v>
+      </c>
+      <c r="H88">
+        <v>286.9</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>16.6</v>
+      </c>
+      <c r="K88">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L88">
+        <v>11.5</v>
+      </c>
+      <c r="M88">
+        <v>118.1276736</v>
+      </c>
+      <c r="N88">
+        <v>-106.6276736</v>
+      </c>
+      <c r="O88">
+        <v>-15.99415104</v>
+      </c>
+      <c r="P88">
+        <v>-90.63352256</v>
+      </c>
+      <c r="Q88">
+        <v>-85.53352255999999</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.5946101594573636</v>
+      </c>
+      <c r="T88">
+        <v>7.793855213875315</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.01460284408750093</v>
+      </c>
+      <c r="W88">
+        <v>0.2353128408319048</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.09735229391667288</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.287614465439469</v>
+      </c>
+      <c r="C89">
+        <v>-309.6701830601863</v>
+      </c>
+      <c r="D89">
+        <v>189.5238169398137</v>
+      </c>
+      <c r="E89">
+        <v>212.124</v>
+      </c>
+      <c r="F89">
+        <v>500.424</v>
+      </c>
+      <c r="G89">
+        <v>1.23</v>
+      </c>
+      <c r="H89">
+        <v>286.9</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>16.6</v>
+      </c>
+      <c r="K89">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L89">
+        <v>11.5</v>
+      </c>
+      <c r="M89">
+        <v>119.5012512</v>
+      </c>
+      <c r="N89">
+        <v>-108.0012512</v>
+      </c>
+      <c r="O89">
+        <v>-16.20018768</v>
+      </c>
+      <c r="P89">
+        <v>-91.80106352000001</v>
+      </c>
+      <c r="Q89">
+        <v>-86.70106352000002</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.63736478710793</v>
+      </c>
+      <c r="T89">
+        <v>8.393382538019569</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.01443499530488598</v>
+      </c>
+      <c r="W89">
+        <v>0.2353529231211932</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.09623330203257319</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2896144654394691</v>
+      </c>
+      <c r="C90">
+        <v>-316.933450096621</v>
+      </c>
+      <c r="D90">
+        <v>188.0125499033791</v>
+      </c>
+      <c r="E90">
+        <v>217.876</v>
+      </c>
+      <c r="F90">
+        <v>506.176</v>
+      </c>
+      <c r="G90">
+        <v>1.23</v>
+      </c>
+      <c r="H90">
+        <v>286.9</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>16.6</v>
+      </c>
+      <c r="K90">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L90">
+        <v>11.5</v>
+      </c>
+      <c r="M90">
+        <v>120.8748288</v>
+      </c>
+      <c r="N90">
+        <v>-109.3748288</v>
+      </c>
+      <c r="O90">
+        <v>-16.40622432</v>
+      </c>
+      <c r="P90">
+        <v>-92.96860448000001</v>
+      </c>
+      <c r="Q90">
+        <v>-87.86860448000002</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.6872451860335911</v>
+      </c>
+      <c r="T90">
+        <v>9.092831082854536</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.01427096126733046</v>
+      </c>
+      <c r="W90">
+        <v>0.2353920944493615</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.09513974178220308</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.291614465439469</v>
+      </c>
+      <c r="C91">
+        <v>-324.1728060481609</v>
+      </c>
+      <c r="D91">
+        <v>186.5251939518392</v>
+      </c>
+      <c r="E91">
+        <v>223.628</v>
+      </c>
+      <c r="F91">
+        <v>511.9280000000001</v>
+      </c>
+      <c r="G91">
+        <v>1.23</v>
+      </c>
+      <c r="H91">
+        <v>286.9</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>16.6</v>
+      </c>
+      <c r="K91">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L91">
+        <v>11.5</v>
+      </c>
+      <c r="M91">
+        <v>122.2484064</v>
+      </c>
+      <c r="N91">
+        <v>-110.7484064</v>
+      </c>
+      <c r="O91">
+        <v>-16.61226096</v>
+      </c>
+      <c r="P91">
+        <v>-94.13614544000002</v>
+      </c>
+      <c r="Q91">
+        <v>-89.03614544000001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.7461947484002811</v>
+      </c>
+      <c r="T91">
+        <v>9.919452090386764</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.01411061338792225</v>
+      </c>
+      <c r="W91">
+        <v>0.2354303855229642</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.09407075591948166</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2936144654394691</v>
+      </c>
+      <c r="C92">
+        <v>-331.3888139382165</v>
+      </c>
+      <c r="D92">
+        <v>185.0611860617836</v>
+      </c>
+      <c r="E92">
+        <v>229.3800000000001</v>
+      </c>
+      <c r="F92">
+        <v>517.6800000000001</v>
+      </c>
+      <c r="G92">
+        <v>1.23</v>
+      </c>
+      <c r="H92">
+        <v>286.9</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>16.6</v>
+      </c>
+      <c r="K92">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L92">
+        <v>11.5</v>
+      </c>
+      <c r="M92">
+        <v>123.621984</v>
+      </c>
+      <c r="N92">
+        <v>-112.121984</v>
+      </c>
+      <c r="O92">
+        <v>-16.81829760000001</v>
+      </c>
+      <c r="P92">
+        <v>-95.30368640000002</v>
+      </c>
+      <c r="Q92">
+        <v>-90.20368640000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.8169342232403094</v>
+      </c>
+      <c r="T92">
+        <v>10.91139729942544</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.01395382879472311</v>
+      </c>
+      <c r="W92">
+        <v>0.2354678256838201</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.09302552529815411</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2956144654394691</v>
+      </c>
+      <c r="C93">
+        <v>-338.582019251516</v>
+      </c>
+      <c r="D93">
+        <v>183.619980748484</v>
+      </c>
+      <c r="E93">
+        <v>235.132</v>
+      </c>
+      <c r="F93">
+        <v>523.432</v>
+      </c>
+      <c r="G93">
+        <v>1.23</v>
+      </c>
+      <c r="H93">
+        <v>286.9</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>16.6</v>
+      </c>
+      <c r="K93">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L93">
+        <v>11.5</v>
+      </c>
+      <c r="M93">
+        <v>124.9955616</v>
+      </c>
+      <c r="N93">
+        <v>-113.4955616</v>
+      </c>
+      <c r="O93">
+        <v>-17.02433424000001</v>
+      </c>
+      <c r="P93">
+        <v>-96.47122736000001</v>
+      </c>
+      <c r="Q93">
+        <v>-91.37122736000001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.9033935813781215</v>
+      </c>
+      <c r="T93">
+        <v>12.12377477713938</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.01380049001675912</v>
+      </c>
+      <c r="W93">
+        <v>0.2355044429839979</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.0920032667783941</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.297614465439469</v>
+      </c>
+      <c r="C94">
+        <v>-345.7529506117605</v>
+      </c>
+      <c r="D94">
+        <v>182.2010493882396</v>
+      </c>
+      <c r="E94">
+        <v>240.8840000000001</v>
+      </c>
+      <c r="F94">
+        <v>529.1840000000001</v>
+      </c>
+      <c r="G94">
+        <v>1.23</v>
+      </c>
+      <c r="H94">
+        <v>286.9</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>16.6</v>
+      </c>
+      <c r="K94">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L94">
+        <v>11.5</v>
+      </c>
+      <c r="M94">
+        <v>126.3691392</v>
+      </c>
+      <c r="N94">
+        <v>-114.8691392</v>
+      </c>
+      <c r="O94">
+        <v>-17.23037088000001</v>
+      </c>
+      <c r="P94">
+        <v>-97.63876832000001</v>
+      </c>
+      <c r="Q94">
+        <v>-92.53876832</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.011467779050387</v>
+      </c>
+      <c r="T94">
+        <v>13.63924662428181</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.01365048469049</v>
+      </c>
+      <c r="W94">
+        <v>0.235540264255911</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.09100323126993337</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.299614465439469</v>
+      </c>
+      <c r="C95">
+        <v>-352.902120428099</v>
+      </c>
+      <c r="D95">
+        <v>180.8038795719011</v>
+      </c>
+      <c r="E95">
+        <v>246.636</v>
+      </c>
+      <c r="F95">
+        <v>534.936</v>
+      </c>
+      <c r="G95">
+        <v>1.23</v>
+      </c>
+      <c r="H95">
+        <v>286.9</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>16.6</v>
+      </c>
+      <c r="K95">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L95">
+        <v>11.5</v>
+      </c>
+      <c r="M95">
+        <v>127.7427168</v>
+      </c>
+      <c r="N95">
+        <v>-116.2427168</v>
+      </c>
+      <c r="O95">
+        <v>-17.43640752</v>
+      </c>
+      <c r="P95">
+        <v>-98.80630928000001</v>
+      </c>
+      <c r="Q95">
+        <v>-93.70630928</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.150420318914728</v>
+      </c>
+      <c r="T95">
+        <v>15.58771042775064</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.01350370528521592</v>
+      </c>
+      <c r="W95">
+        <v>0.2355753151778905</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.09002470190143941</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.301614465439469</v>
+      </c>
+      <c r="C96">
+        <v>-360.0300255120871</v>
+      </c>
+      <c r="D96">
+        <v>179.4279744879129</v>
+      </c>
+      <c r="E96">
+        <v>252.3880000000001</v>
+      </c>
+      <c r="F96">
+        <v>540.6880000000001</v>
+      </c>
+      <c r="G96">
+        <v>1.23</v>
+      </c>
+      <c r="H96">
+        <v>286.9</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>16.6</v>
+      </c>
+      <c r="K96">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L96">
+        <v>11.5</v>
+      </c>
+      <c r="M96">
+        <v>129.1162944</v>
+      </c>
+      <c r="N96">
+        <v>-117.6162944</v>
+      </c>
+      <c r="O96">
+        <v>-17.64244416000001</v>
+      </c>
+      <c r="P96">
+        <v>-99.97385024000003</v>
+      </c>
+      <c r="Q96">
+        <v>-94.87385024000002</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.335690372067183</v>
+      </c>
+      <c r="T96">
+        <v>18.18566216570909</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.01336004884601149</v>
+      </c>
+      <c r="W96">
+        <v>0.2356096203355725</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.0890669923067432</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3036144654394691</v>
+      </c>
+      <c r="C97">
+        <v>-367.1371476666881</v>
+      </c>
+      <c r="D97">
+        <v>178.0728523333119</v>
+      </c>
+      <c r="E97">
+        <v>258.14</v>
+      </c>
+      <c r="F97">
+        <v>546.4400000000001</v>
+      </c>
+      <c r="G97">
+        <v>1.23</v>
+      </c>
+      <c r="H97">
+        <v>286.9</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>16.6</v>
+      </c>
+      <c r="K97">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L97">
+        <v>11.5</v>
+      </c>
+      <c r="M97">
+        <v>130.489872</v>
+      </c>
+      <c r="N97">
+        <v>-118.989872</v>
+      </c>
+      <c r="O97">
+        <v>-17.8484808</v>
+      </c>
+      <c r="P97">
+        <v>-101.1413912</v>
+      </c>
+      <c r="Q97">
+        <v>-96.04139120000002</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.595068446480621</v>
+      </c>
+      <c r="T97">
+        <v>21.82279459885092</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.01321941675289558</v>
+      </c>
+      <c r="W97">
+        <v>0.2356432032794085</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.08812944501930386</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.305614465439469</v>
+      </c>
+      <c r="C98">
+        <v>-374.2239542487825</v>
+      </c>
+      <c r="D98">
+        <v>176.7380457512175</v>
+      </c>
+      <c r="E98">
+        <v>263.892</v>
+      </c>
+      <c r="F98">
+        <v>552.192</v>
+      </c>
+      <c r="G98">
+        <v>1.23</v>
+      </c>
+      <c r="H98">
+        <v>286.9</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>16.6</v>
+      </c>
+      <c r="K98">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L98">
+        <v>11.5</v>
+      </c>
+      <c r="M98">
+        <v>131.8634496</v>
+      </c>
+      <c r="N98">
+        <v>-120.3634496</v>
+      </c>
+      <c r="O98">
+        <v>-18.05451744</v>
+      </c>
+      <c r="P98">
+        <v>-102.30893216</v>
+      </c>
+      <c r="Q98">
+        <v>-97.20893215999999</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.984135558100771</v>
+      </c>
+      <c r="T98">
+        <v>27.27849324856358</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.01308171449505292</v>
+      </c>
+      <c r="W98">
+        <v>0.2356760865785814</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.08721142996701947</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3076144654394691</v>
+      </c>
+      <c r="C99">
+        <v>-381.290898706569</v>
+      </c>
+      <c r="D99">
+        <v>175.4231012934311</v>
+      </c>
+      <c r="E99">
+        <v>269.6440000000001</v>
+      </c>
+      <c r="F99">
+        <v>557.9440000000001</v>
+      </c>
+      <c r="G99">
+        <v>1.23</v>
+      </c>
+      <c r="H99">
+        <v>286.9</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>16.6</v>
+      </c>
+      <c r="K99">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L99">
+        <v>11.5</v>
+      </c>
+      <c r="M99">
+        <v>133.2370272</v>
+      </c>
+      <c r="N99">
+        <v>-121.7370272</v>
+      </c>
+      <c r="O99">
+        <v>-18.26055408000001</v>
+      </c>
+      <c r="P99">
+        <v>-103.47647312</v>
+      </c>
+      <c r="Q99">
+        <v>-98.37647312000001</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.632580744134362</v>
+      </c>
+      <c r="T99">
+        <v>36.37132433141812</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.01294685145902144</v>
+      </c>
+      <c r="W99">
+        <v>0.2357082918715857</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.0863123430601429</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.309614465439469</v>
+      </c>
+      <c r="C100">
+        <v>-388.3384210931501</v>
+      </c>
+      <c r="D100">
+        <v>174.1275789068499</v>
+      </c>
+      <c r="E100">
+        <v>275.396</v>
+      </c>
+      <c r="F100">
+        <v>563.696</v>
+      </c>
+      <c r="G100">
+        <v>1.23</v>
+      </c>
+      <c r="H100">
+        <v>286.9</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>16.6</v>
+      </c>
+      <c r="K100">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L100">
+        <v>11.5</v>
+      </c>
+      <c r="M100">
+        <v>134.6106048</v>
+      </c>
+      <c r="N100">
+        <v>-123.1106048</v>
+      </c>
+      <c r="O100">
+        <v>-18.46659072</v>
+      </c>
+      <c r="P100">
+        <v>-104.64401408</v>
+      </c>
+      <c r="Q100">
+        <v>-99.54401408000001</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.929471116201543</v>
+      </c>
+      <c r="T100">
+        <v>54.55698649712716</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.01281474072984776</v>
+      </c>
+      <c r="W100">
+        <v>0.2357398399137124</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.08543160486565171</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.311614465439469</v>
+      </c>
+      <c r="C101">
+        <v>-395.3669485575305</v>
+      </c>
+      <c r="D101">
+        <v>172.8510514424697</v>
+      </c>
+      <c r="E101">
+        <v>281.1480000000001</v>
+      </c>
+      <c r="F101">
+        <v>569.4480000000001</v>
+      </c>
+      <c r="G101">
+        <v>1.23</v>
+      </c>
+      <c r="H101">
+        <v>286.9</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>16.6</v>
+      </c>
+      <c r="K101">
+        <v>5.100000000000001</v>
+      </c>
+      <c r="L101">
+        <v>11.5</v>
+      </c>
+      <c r="M101">
+        <v>135.9841824</v>
+      </c>
+      <c r="N101">
+        <v>-124.4841824</v>
+      </c>
+      <c r="O101">
+        <v>-18.67262736000001</v>
+      </c>
+      <c r="P101">
+        <v>-105.81155504</v>
+      </c>
+      <c r="Q101">
+        <v>-100.71155504</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>7.820142232403086</v>
+      </c>
+      <c r="T101">
+        <v>109.1139729942543</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.01268529890429374</v>
+      </c>
+      <c r="W101">
+        <v>0.2357707506216547</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.08456865936195823</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/kuwait/kuwait_entertainment.xlsx
+++ b/research/traditional_assets/database/data/kuwait/kuwait_entertainment.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09943901204655192</v>
+        <v>0.09932810352848208</v>
       </c>
       <c r="C2">
-        <v>715.4875858826165</v>
+        <v>709.4878599355453</v>
       </c>
       <c r="D2">
-        <v>582.1875858826165</v>
+        <v>583.3938599355454</v>
       </c>
       <c r="E2">
-        <v>-372.1</v>
+        <v>-364.894</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>7.206</v>
       </c>
       <c r="G2">
         <v>133.3</v>
@@ -1451,28 +1451,28 @@
         <v>50.425</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.3624618</v>
       </c>
       <c r="N2">
-        <v>50.425</v>
+        <v>50.0625382</v>
       </c>
       <c r="O2">
-        <v>7.563749999999999</v>
+        <v>7.509380729999999</v>
       </c>
       <c r="P2">
-        <v>42.86125</v>
+        <v>42.55315747</v>
       </c>
       <c r="Q2">
-        <v>50.56125</v>
+        <v>50.25315747</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09943901204655192</v>
+        <v>0.09989954901866877</v>
       </c>
       <c r="T2">
-        <v>1.017512237681883</v>
+        <v>1.026248453864</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>139.1181084461866</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09932810352848208</v>
+        <v>0.09921719501041226</v>
       </c>
       <c r="C3">
-        <v>709.4878599355453</v>
+        <v>703.4931430896659</v>
       </c>
       <c r="D3">
-        <v>583.3938599355454</v>
+        <v>584.6051430896659</v>
       </c>
       <c r="E3">
-        <v>-364.894</v>
+        <v>-357.688</v>
       </c>
       <c r="F3">
-        <v>7.206</v>
+        <v>14.412</v>
       </c>
       <c r="G3">
         <v>133.3</v>
@@ -1533,28 +1533,28 @@
         <v>50.425</v>
       </c>
       <c r="M3">
-        <v>0.3624618</v>
+        <v>0.7249236</v>
       </c>
       <c r="N3">
-        <v>50.0625382</v>
+        <v>49.7000764</v>
       </c>
       <c r="O3">
-        <v>7.509380729999999</v>
+        <v>7.45501146</v>
       </c>
       <c r="P3">
-        <v>42.55315747</v>
+        <v>42.24506494</v>
       </c>
       <c r="Q3">
-        <v>50.25315747</v>
+        <v>49.94506494</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09989954901866877</v>
+        <v>0.1003694847045023</v>
       </c>
       <c r="T3">
-        <v>1.026248453864</v>
+        <v>1.035162960172283</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>139.1181084461866</v>
+        <v>69.5590542230933</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09921719501041226</v>
+        <v>0.09910628649234242</v>
       </c>
       <c r="C4">
-        <v>703.4931430896659</v>
+        <v>697.5034666106336</v>
       </c>
       <c r="D4">
-        <v>584.6051430896659</v>
+        <v>585.8214666106337</v>
       </c>
       <c r="E4">
-        <v>-357.688</v>
+        <v>-350.482</v>
       </c>
       <c r="F4">
-        <v>14.412</v>
+        <v>21.618</v>
       </c>
       <c r="G4">
         <v>133.3</v>
@@ -1615,28 +1615,28 @@
         <v>50.425</v>
       </c>
       <c r="M4">
-        <v>0.7249236</v>
+        <v>1.0873854</v>
       </c>
       <c r="N4">
-        <v>49.7000764</v>
+        <v>49.33761459999999</v>
       </c>
       <c r="O4">
-        <v>7.45501146</v>
+        <v>7.400642189999999</v>
       </c>
       <c r="P4">
-        <v>42.24506494</v>
+        <v>41.93697241</v>
       </c>
       <c r="Q4">
-        <v>49.94506494</v>
+        <v>49.63697241</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1003694847045023</v>
+        <v>0.10084910978592</v>
       </c>
       <c r="T4">
-        <v>1.035162960172283</v>
+        <v>1.044261270734344</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>69.5590542230933</v>
+        <v>46.37270281539553</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09910628649234242</v>
+        <v>0.09899537797427259</v>
       </c>
       <c r="C5">
-        <v>697.5034666106336</v>
+        <v>691.5188620248501</v>
       </c>
       <c r="D5">
-        <v>585.8214666106337</v>
+        <v>587.04286202485</v>
       </c>
       <c r="E5">
-        <v>-350.482</v>
+        <v>-343.276</v>
       </c>
       <c r="F5">
-        <v>21.618</v>
+        <v>28.824</v>
       </c>
       <c r="G5">
         <v>133.3</v>
@@ -1697,28 +1697,28 @@
         <v>50.425</v>
       </c>
       <c r="M5">
-        <v>1.0873854</v>
+        <v>1.4498472</v>
       </c>
       <c r="N5">
-        <v>49.33761459999999</v>
+        <v>48.9751528</v>
       </c>
       <c r="O5">
-        <v>7.400642189999999</v>
+        <v>7.346272919999999</v>
       </c>
       <c r="P5">
-        <v>41.93697241</v>
+        <v>41.62887988</v>
       </c>
       <c r="Q5">
-        <v>49.63697241</v>
+        <v>49.32887988</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.10084910978592</v>
+        <v>0.101338727056534</v>
       </c>
       <c r="T5">
-        <v>1.044261270734344</v>
+        <v>1.053549129433116</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>46.37270281539553</v>
+        <v>34.77952711154665</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09899537797427259</v>
+        <v>0.09888446945620276</v>
       </c>
       <c r="C6">
-        <v>691.5188620248501</v>
+        <v>685.5393611221871</v>
       </c>
       <c r="D6">
-        <v>587.04286202485</v>
+        <v>588.269361122187</v>
       </c>
       <c r="E6">
-        <v>-343.276</v>
+        <v>-336.0700000000001</v>
       </c>
       <c r="F6">
-        <v>28.824</v>
+        <v>36.03</v>
       </c>
       <c r="G6">
         <v>133.3</v>
@@ -1779,28 +1779,28 @@
         <v>50.425</v>
       </c>
       <c r="M6">
-        <v>1.4498472</v>
+        <v>1.812309</v>
       </c>
       <c r="N6">
-        <v>48.9751528</v>
+        <v>48.612691</v>
       </c>
       <c r="O6">
-        <v>7.346272919999999</v>
+        <v>7.291903649999999</v>
       </c>
       <c r="P6">
-        <v>41.62887988</v>
+        <v>41.32078735</v>
       </c>
       <c r="Q6">
-        <v>49.32887988</v>
+        <v>49.02078735</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.101338727056534</v>
+        <v>0.1018386520591608</v>
       </c>
       <c r="T6">
-        <v>1.053549129433116</v>
+        <v>1.06303252199923</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>34.77952711154665</v>
+        <v>27.82362168923732</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09888446945620276</v>
+        <v>0.09877356093813294</v>
       </c>
       <c r="C7">
-        <v>685.5393611221871</v>
+        <v>679.5649959587453</v>
       </c>
       <c r="D7">
-        <v>588.269361122187</v>
+        <v>589.5009959587452</v>
       </c>
       <c r="E7">
-        <v>-336.0700000000001</v>
+        <v>-328.864</v>
       </c>
       <c r="F7">
-        <v>36.03</v>
+        <v>43.236</v>
       </c>
       <c r="G7">
         <v>133.3</v>
@@ -1861,28 +1861,28 @@
         <v>50.425</v>
       </c>
       <c r="M7">
-        <v>1.812309</v>
+        <v>2.1747708</v>
       </c>
       <c r="N7">
-        <v>48.612691</v>
+        <v>48.2502292</v>
       </c>
       <c r="O7">
-        <v>7.291903649999999</v>
+        <v>7.23753438</v>
       </c>
       <c r="P7">
-        <v>41.32078735</v>
+        <v>41.01269482</v>
       </c>
       <c r="Q7">
-        <v>49.02078735</v>
+        <v>48.71269482</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1018386520591608</v>
+        <v>0.1023492137639712</v>
       </c>
       <c r="T7">
-        <v>1.06303252199923</v>
+        <v>1.072717688875261</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>27.82362168923732</v>
+        <v>23.18635140769777</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09877356093813294</v>
+        <v>0.09866265242006313</v>
       </c>
       <c r="C8">
-        <v>679.5649959587453</v>
+        <v>673.5957988596465</v>
       </c>
       <c r="D8">
-        <v>589.5009959587452</v>
+        <v>590.7377988596464</v>
       </c>
       <c r="E8">
-        <v>-328.864</v>
+        <v>-321.658</v>
       </c>
       <c r="F8">
-        <v>43.236</v>
+        <v>50.44199999999999</v>
       </c>
       <c r="G8">
         <v>133.3</v>
@@ -1943,28 +1943,28 @@
         <v>50.425</v>
       </c>
       <c r="M8">
-        <v>2.1747708</v>
+        <v>2.537232599999999</v>
       </c>
       <c r="N8">
-        <v>48.2502292</v>
+        <v>47.8877674</v>
       </c>
       <c r="O8">
-        <v>7.23753438</v>
+        <v>7.18316511</v>
       </c>
       <c r="P8">
-        <v>41.01269482</v>
+        <v>40.70460229</v>
       </c>
       <c r="Q8">
-        <v>48.71269482</v>
+        <v>48.40460229000001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1023492137639712</v>
+        <v>0.1028707552903904</v>
       </c>
       <c r="T8">
-        <v>1.072717688875261</v>
+        <v>1.082611138909917</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>23.18635140769777</v>
+        <v>19.87401549231238</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09866265242006311</v>
+        <v>0.0985517439019933</v>
       </c>
       <c r="C9">
-        <v>673.5957988596465</v>
+        <v>667.6318024218618</v>
       </c>
       <c r="D9">
-        <v>590.7377988596465</v>
+        <v>591.9798024218619</v>
       </c>
       <c r="E9">
-        <v>-321.658</v>
+        <v>-314.452</v>
       </c>
       <c r="F9">
-        <v>50.44200000000001</v>
+        <v>57.648</v>
       </c>
       <c r="G9">
         <v>133.3</v>
@@ -2025,28 +2025,28 @@
         <v>50.425</v>
       </c>
       <c r="M9">
-        <v>2.5372326</v>
+        <v>2.8996944</v>
       </c>
       <c r="N9">
-        <v>47.88776739999999</v>
+        <v>47.5253056</v>
       </c>
       <c r="O9">
-        <v>7.183165109999999</v>
+        <v>7.12879584</v>
       </c>
       <c r="P9">
-        <v>40.70460229</v>
+        <v>40.39650975999999</v>
       </c>
       <c r="Q9">
-        <v>48.40460229</v>
+        <v>48.09650976</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1028707552903904</v>
+        <v>0.1034036346760797</v>
       </c>
       <c r="T9">
-        <v>1.082611138909917</v>
+        <v>1.092719663945326</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>19.87401549231237</v>
+        <v>17.38976355577332</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.0985517439019933</v>
+        <v>0.09844083538392347</v>
       </c>
       <c r="C10">
-        <v>667.6318024218618</v>
+        <v>661.6730395170757</v>
       </c>
       <c r="D10">
-        <v>591.9798024218619</v>
+        <v>593.2270395170758</v>
       </c>
       <c r="E10">
-        <v>-314.452</v>
+        <v>-307.246</v>
       </c>
       <c r="F10">
-        <v>57.648</v>
+        <v>64.854</v>
       </c>
       <c r="G10">
         <v>133.3</v>
@@ -2107,28 +2107,28 @@
         <v>50.425</v>
       </c>
       <c r="M10">
-        <v>2.8996944</v>
+        <v>3.2621562</v>
       </c>
       <c r="N10">
-        <v>47.5253056</v>
+        <v>47.1628438</v>
       </c>
       <c r="O10">
-        <v>7.12879584</v>
+        <v>7.074426569999999</v>
       </c>
       <c r="P10">
-        <v>40.39650975999999</v>
+        <v>40.08841723</v>
       </c>
       <c r="Q10">
-        <v>48.09650976</v>
+        <v>47.78841723</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1034036346760797</v>
+        <v>0.1039482256966192</v>
       </c>
       <c r="T10">
-        <v>1.092719663945326</v>
+        <v>1.103050354366129</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>17.38976355577332</v>
+        <v>15.45756760513185</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09844083538392347</v>
+        <v>0.09832992686585365</v>
       </c>
       <c r="C11">
-        <v>661.6730395170757</v>
+        <v>655.7195432945855</v>
       </c>
       <c r="D11">
-        <v>593.2270395170758</v>
+        <v>594.4795432945854</v>
       </c>
       <c r="E11">
-        <v>-307.246</v>
+        <v>-300.04</v>
       </c>
       <c r="F11">
-        <v>64.854</v>
+        <v>72.06</v>
       </c>
       <c r="G11">
         <v>133.3</v>
@@ -2189,28 +2189,28 @@
         <v>50.425</v>
       </c>
       <c r="M11">
-        <v>3.2621562</v>
+        <v>3.624618</v>
       </c>
       <c r="N11">
-        <v>47.1628438</v>
+        <v>46.800382</v>
       </c>
       <c r="O11">
-        <v>7.074426569999999</v>
+        <v>7.0200573</v>
       </c>
       <c r="P11">
-        <v>40.08841723</v>
+        <v>39.7803247</v>
       </c>
       <c r="Q11">
-        <v>47.78841723</v>
+        <v>47.4803247</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1039482256966192</v>
+        <v>0.1045049187398374</v>
       </c>
       <c r="T11">
-        <v>1.103050354366129</v>
+        <v>1.113610615685172</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>15.45756760513185</v>
+        <v>13.91181084461866</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09832992686585365</v>
+        <v>0.0983592683477838</v>
       </c>
       <c r="C12">
-        <v>655.7195432945855</v>
+        <v>648.181672031424</v>
       </c>
       <c r="D12">
-        <v>594.4795432945854</v>
+        <v>594.1476720314239</v>
       </c>
       <c r="E12">
-        <v>-300.04</v>
+        <v>-292.834</v>
       </c>
       <c r="F12">
-        <v>72.06</v>
+        <v>79.26600000000001</v>
       </c>
       <c r="G12">
         <v>133.3</v>
@@ -2271,45 +2271,45 @@
         <v>50.425</v>
       </c>
       <c r="M12">
-        <v>3.624618</v>
+        <v>4.1059788</v>
       </c>
       <c r="N12">
-        <v>46.800382</v>
+        <v>46.31902119999999</v>
       </c>
       <c r="O12">
-        <v>7.0200573</v>
+        <v>6.947853179999999</v>
       </c>
       <c r="P12">
-        <v>39.7803247</v>
+        <v>39.37116802</v>
       </c>
       <c r="Q12">
-        <v>47.4803247</v>
+        <v>47.07116802</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1045049187398374</v>
+        <v>0.1050741217390829</v>
       </c>
       <c r="T12">
-        <v>1.113610615685172</v>
+        <v>1.124408186247339</v>
       </c>
       <c r="U12">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V12">
         <v>0.15</v>
       </c>
       <c r="W12">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y12">
-        <v>13.91181084461866</v>
+        <v>12.28087198112177</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.0983592683477838</v>
+        <v>0.09826110982971398</v>
       </c>
       <c r="C13">
-        <v>648.181672031424</v>
+        <v>642.087365154016</v>
       </c>
       <c r="D13">
-        <v>594.1476720314239</v>
+        <v>595.259365154016</v>
       </c>
       <c r="E13">
-        <v>-292.834</v>
+        <v>-285.628</v>
       </c>
       <c r="F13">
-        <v>79.26600000000001</v>
+        <v>86.47199999999999</v>
       </c>
       <c r="G13">
         <v>133.3</v>
@@ -2353,28 +2353,28 @@
         <v>50.425</v>
       </c>
       <c r="M13">
-        <v>4.1059788</v>
+        <v>4.479249599999999</v>
       </c>
       <c r="N13">
-        <v>46.31902119999999</v>
+        <v>45.94575039999999</v>
       </c>
       <c r="O13">
-        <v>6.947853179999999</v>
+        <v>6.891862559999999</v>
       </c>
       <c r="P13">
-        <v>39.37116802</v>
+        <v>39.05388783999999</v>
       </c>
       <c r="Q13">
-        <v>47.07116802</v>
+        <v>46.75388784</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1050741217390829</v>
+        <v>0.1056562611701295</v>
       </c>
       <c r="T13">
-        <v>1.124408186247339</v>
+        <v>1.135451156140465</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>12.28087198112177</v>
+        <v>11.25746598269496</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09826110982971398</v>
+        <v>0.09816295131164415</v>
       </c>
       <c r="C14">
-        <v>642.087365154016</v>
+        <v>635.9972261910106</v>
       </c>
       <c r="D14">
-        <v>595.259365154016</v>
+        <v>596.3752261910105</v>
       </c>
       <c r="E14">
-        <v>-285.628</v>
+        <v>-278.422</v>
       </c>
       <c r="F14">
-        <v>86.47199999999999</v>
+        <v>93.67800000000001</v>
       </c>
       <c r="G14">
         <v>133.3</v>
@@ -2435,28 +2435,28 @@
         <v>50.425</v>
       </c>
       <c r="M14">
-        <v>4.479249599999999</v>
+        <v>4.8525204</v>
       </c>
       <c r="N14">
-        <v>45.94575039999999</v>
+        <v>45.57247959999999</v>
       </c>
       <c r="O14">
-        <v>6.891862559999999</v>
+        <v>6.835871939999999</v>
       </c>
       <c r="P14">
-        <v>39.05388783999999</v>
+        <v>38.73660766</v>
       </c>
       <c r="Q14">
-        <v>46.75388784</v>
+        <v>46.43660766</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1056562611701295</v>
+        <v>0.1062517831168324</v>
       </c>
       <c r="T14">
-        <v>1.135451156140465</v>
+        <v>1.146747987410443</v>
       </c>
       <c r="U14">
         <v>0.0518</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>11.25746598269496</v>
+        <v>10.39150706094919</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09816295131164415</v>
+        <v>0.09826709279357432</v>
       </c>
       <c r="C15">
-        <v>635.9972261910106</v>
+        <v>627.6074861258553</v>
       </c>
       <c r="D15">
-        <v>596.3752261910105</v>
+        <v>595.1914861258552</v>
       </c>
       <c r="E15">
-        <v>-278.422</v>
+        <v>-271.216</v>
       </c>
       <c r="F15">
-        <v>93.67800000000001</v>
+        <v>100.884</v>
       </c>
       <c r="G15">
         <v>133.3</v>
@@ -2517,45 +2517,45 @@
         <v>50.425</v>
       </c>
       <c r="M15">
-        <v>4.8525204</v>
+        <v>5.397294</v>
       </c>
       <c r="N15">
-        <v>45.57247959999999</v>
+        <v>45.02770599999999</v>
       </c>
       <c r="O15">
-        <v>6.835871939999999</v>
+        <v>6.754155899999999</v>
       </c>
       <c r="P15">
-        <v>38.73660766</v>
+        <v>38.27355009999999</v>
       </c>
       <c r="Q15">
-        <v>46.43660766</v>
+        <v>45.9735501</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1062517831168324</v>
+        <v>0.1068611544111329</v>
       </c>
       <c r="T15">
-        <v>1.146747987410443</v>
+        <v>1.158307535686701</v>
       </c>
       <c r="U15">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V15">
         <v>0.15</v>
       </c>
       <c r="W15">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y15">
-        <v>10.39150706094919</v>
+        <v>9.342644666012262</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09826709279357432</v>
+        <v>0.09818338427550449</v>
       </c>
       <c r="C16">
-        <v>627.6074861258553</v>
+        <v>621.3526006435683</v>
       </c>
       <c r="D16">
-        <v>595.1914861258552</v>
+        <v>596.1426006435684</v>
       </c>
       <c r="E16">
-        <v>-271.216</v>
+        <v>-264.01</v>
       </c>
       <c r="F16">
-        <v>100.884</v>
+        <v>108.09</v>
       </c>
       <c r="G16">
         <v>133.3</v>
@@ -2599,28 +2599,28 @@
         <v>50.425</v>
       </c>
       <c r="M16">
-        <v>5.397294</v>
+        <v>5.782815000000001</v>
       </c>
       <c r="N16">
-        <v>45.02770599999999</v>
+        <v>44.642185</v>
       </c>
       <c r="O16">
-        <v>6.754155899999999</v>
+        <v>6.696327749999999</v>
       </c>
       <c r="P16">
-        <v>38.27355009999999</v>
+        <v>37.94585725</v>
       </c>
       <c r="Q16">
-        <v>45.9735501</v>
+        <v>45.64585725</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1068611544111329</v>
+        <v>0.1074848638535347</v>
       </c>
       <c r="T16">
-        <v>1.158307535686701</v>
+        <v>1.170139073334165</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>9.342644666012262</v>
+        <v>8.719801688278112</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09818338427550449</v>
+        <v>0.09809967575743468</v>
       </c>
       <c r="C17">
-        <v>621.3526006435683</v>
+        <v>615.1007597838582</v>
       </c>
       <c r="D17">
-        <v>596.1426006435684</v>
+        <v>597.0967597838581</v>
       </c>
       <c r="E17">
-        <v>-264.01</v>
+        <v>-256.804</v>
       </c>
       <c r="F17">
-        <v>108.09</v>
+        <v>115.296</v>
       </c>
       <c r="G17">
         <v>133.3</v>
@@ -2681,28 +2681,28 @@
         <v>50.425</v>
       </c>
       <c r="M17">
-        <v>5.782815</v>
+        <v>6.168336</v>
       </c>
       <c r="N17">
-        <v>44.642185</v>
+        <v>44.256664</v>
       </c>
       <c r="O17">
-        <v>6.696327749999999</v>
+        <v>6.6384996</v>
       </c>
       <c r="P17">
-        <v>37.94585725</v>
+        <v>37.6181644</v>
       </c>
       <c r="Q17">
-        <v>45.64585725</v>
+        <v>45.3181644</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1074848638535347</v>
+        <v>0.1081234235207556</v>
       </c>
       <c r="T17">
-        <v>1.170139073334165</v>
+        <v>1.182252314258949</v>
       </c>
       <c r="U17">
         <v>0.0535</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>8.719801688278114</v>
+        <v>8.174814082760733</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09809967575743468</v>
+        <v>0.09801596723936483</v>
       </c>
       <c r="C18">
-        <v>615.1007597838582</v>
+        <v>608.8519781894217</v>
       </c>
       <c r="D18">
-        <v>597.0967597838581</v>
+        <v>598.0539781894216</v>
       </c>
       <c r="E18">
-        <v>-256.804</v>
+        <v>-249.598</v>
       </c>
       <c r="F18">
-        <v>115.296</v>
+        <v>122.502</v>
       </c>
       <c r="G18">
         <v>133.3</v>
@@ -2763,28 +2763,28 @@
         <v>50.425</v>
       </c>
       <c r="M18">
-        <v>6.168336</v>
+        <v>6.553857000000001</v>
       </c>
       <c r="N18">
-        <v>44.256664</v>
+        <v>43.871143</v>
       </c>
       <c r="O18">
-        <v>6.6384996</v>
+        <v>6.58067145</v>
       </c>
       <c r="P18">
-        <v>37.6181644</v>
+        <v>37.29047155</v>
       </c>
       <c r="Q18">
-        <v>45.3181644</v>
+        <v>44.99047155</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1081234235207556</v>
+        <v>0.1087773701679094</v>
       </c>
       <c r="T18">
-        <v>1.182252314258949</v>
+        <v>1.194657440507222</v>
       </c>
       <c r="U18">
         <v>0.0535</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>8.174814082760733</v>
+        <v>7.693942666127746</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09801596723936483</v>
+        <v>0.098054658721295</v>
       </c>
       <c r="C19">
-        <v>608.8519781894217</v>
+        <v>601.2031546162393</v>
       </c>
       <c r="D19">
-        <v>598.0539781894216</v>
+        <v>597.6111546162393</v>
       </c>
       <c r="E19">
-        <v>-249.598</v>
+        <v>-242.392</v>
       </c>
       <c r="F19">
-        <v>122.502</v>
+        <v>129.708</v>
       </c>
       <c r="G19">
         <v>133.3</v>
@@ -2845,45 +2845,45 @@
         <v>50.425</v>
       </c>
       <c r="M19">
-        <v>6.553857000000001</v>
+        <v>7.043144400000002</v>
       </c>
       <c r="N19">
-        <v>43.871143</v>
+        <v>43.38185559999999</v>
       </c>
       <c r="O19">
-        <v>6.58067145</v>
+        <v>6.507278339999999</v>
       </c>
       <c r="P19">
-        <v>37.29047155</v>
+        <v>36.87457726</v>
       </c>
       <c r="Q19">
-        <v>44.99047155</v>
+        <v>44.57457726</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1087773701679094</v>
+        <v>0.1094472667332866</v>
       </c>
       <c r="T19">
-        <v>1.194657440507222</v>
+        <v>1.207365130810331</v>
       </c>
       <c r="U19">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V19">
         <v>0.15</v>
       </c>
       <c r="W19">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y19">
-        <v>7.693942666127746</v>
+        <v>7.159444295931229</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09805465872129501</v>
+        <v>0.09797775020322518</v>
       </c>
       <c r="C20">
-        <v>601.2031546162392</v>
+        <v>594.8780164415293</v>
       </c>
       <c r="D20">
-        <v>597.6111546162392</v>
+        <v>598.4920164415294</v>
       </c>
       <c r="E20">
-        <v>-242.392</v>
+        <v>-235.186</v>
       </c>
       <c r="F20">
-        <v>129.708</v>
+        <v>136.914</v>
       </c>
       <c r="G20">
         <v>133.3</v>
@@ -2927,28 +2927,28 @@
         <v>50.425</v>
       </c>
       <c r="M20">
-        <v>7.0431444</v>
+        <v>7.434430200000001</v>
       </c>
       <c r="N20">
-        <v>43.38185559999999</v>
+        <v>42.9905698</v>
       </c>
       <c r="O20">
-        <v>6.507278339999999</v>
+        <v>6.448585469999999</v>
       </c>
       <c r="P20">
-        <v>36.87457726</v>
+        <v>36.54198433</v>
       </c>
       <c r="Q20">
-        <v>44.57457726</v>
+        <v>44.24198433</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1094472667332866</v>
+        <v>0.110133703954599</v>
       </c>
       <c r="T20">
-        <v>1.207365130810331</v>
+        <v>1.220386591244381</v>
       </c>
       <c r="U20">
         <v>0.0543</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.159444295931231</v>
+        <v>6.78263143825064</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09797775020322518</v>
+        <v>0.09790084168515535</v>
       </c>
       <c r="C21">
-        <v>594.8780164415293</v>
+        <v>588.5554788304729</v>
       </c>
       <c r="D21">
-        <v>598.4920164415294</v>
+        <v>599.3754788304728</v>
       </c>
       <c r="E21">
-        <v>-235.186</v>
+        <v>-227.98</v>
       </c>
       <c r="F21">
-        <v>136.914</v>
+        <v>144.12</v>
       </c>
       <c r="G21">
         <v>133.3</v>
@@ -3009,28 +3009,28 @@
         <v>50.425</v>
       </c>
       <c r="M21">
-        <v>7.434430200000001</v>
+        <v>7.825716000000001</v>
       </c>
       <c r="N21">
-        <v>42.9905698</v>
+        <v>42.599284</v>
       </c>
       <c r="O21">
-        <v>6.448585469999999</v>
+        <v>6.3898926</v>
       </c>
       <c r="P21">
-        <v>36.54198433</v>
+        <v>36.2093914</v>
       </c>
       <c r="Q21">
-        <v>44.24198433</v>
+        <v>43.9093914</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.110133703954599</v>
+        <v>0.1108373021064442</v>
       </c>
       <c r="T21">
-        <v>1.220386591244381</v>
+        <v>1.233733588189283</v>
       </c>
       <c r="U21">
         <v>0.0543</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>6.78263143825064</v>
+        <v>6.443499866338108</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09790084168515535</v>
+        <v>0.09782393316708554</v>
       </c>
       <c r="C22">
-        <v>588.5554788304729</v>
+        <v>582.2355533165403</v>
       </c>
       <c r="D22">
-        <v>599.3754788304728</v>
+        <v>600.2615533165404</v>
       </c>
       <c r="E22">
-        <v>-227.98</v>
+        <v>-220.774</v>
       </c>
       <c r="F22">
-        <v>144.12</v>
+        <v>151.326</v>
       </c>
       <c r="G22">
         <v>133.3</v>
@@ -3091,28 +3091,28 @@
         <v>50.425</v>
       </c>
       <c r="M22">
-        <v>7.825716000000001</v>
+        <v>8.217001800000002</v>
       </c>
       <c r="N22">
-        <v>42.599284</v>
+        <v>42.20799819999999</v>
       </c>
       <c r="O22">
-        <v>6.3898926</v>
+        <v>6.331199729999999</v>
       </c>
       <c r="P22">
-        <v>36.2093914</v>
+        <v>35.87679846999999</v>
       </c>
       <c r="Q22">
-        <v>43.9093914</v>
+        <v>43.57679846999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1108373021064442</v>
+        <v>0.1115587128697285</v>
       </c>
       <c r="T22">
-        <v>1.233733588189283</v>
+        <v>1.247418483791017</v>
       </c>
       <c r="U22">
         <v>0.0543</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>6.443499866338108</v>
+        <v>6.136666539369625</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09782393316708553</v>
+        <v>0.09793402464901571</v>
       </c>
       <c r="C23">
-        <v>582.2355533165405</v>
+        <v>573.7619802796374</v>
       </c>
       <c r="D23">
-        <v>600.2615533165405</v>
+        <v>598.9939802796374</v>
       </c>
       <c r="E23">
-        <v>-220.774</v>
+        <v>-213.568</v>
       </c>
       <c r="F23">
-        <v>151.326</v>
+        <v>158.532</v>
       </c>
       <c r="G23">
         <v>133.3</v>
@@ -3173,45 +3173,45 @@
         <v>50.425</v>
       </c>
       <c r="M23">
-        <v>8.2170018</v>
+        <v>8.766819600000002</v>
       </c>
       <c r="N23">
-        <v>42.2079982</v>
+        <v>41.65818039999999</v>
       </c>
       <c r="O23">
-        <v>6.33119973</v>
+        <v>6.248727059999998</v>
       </c>
       <c r="P23">
-        <v>35.87679847</v>
+        <v>35.40945333999999</v>
       </c>
       <c r="Q23">
-        <v>43.57679847</v>
+        <v>43.10945333999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1115587128697285</v>
+        <v>0.1122986213448919</v>
       </c>
       <c r="T23">
-        <v>1.247418483791017</v>
+        <v>1.26145427415177</v>
       </c>
       <c r="U23">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V23">
         <v>0.15</v>
       </c>
       <c r="W23">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y23">
-        <v>6.136666539369627</v>
+        <v>5.75180080128488</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09793402464901571</v>
+        <v>0.09786561613094588</v>
       </c>
       <c r="C24">
-        <v>573.7619802796374</v>
+        <v>567.3429927759578</v>
       </c>
       <c r="D24">
-        <v>598.9939802796374</v>
+        <v>599.7809927759579</v>
       </c>
       <c r="E24">
-        <v>-213.568</v>
+        <v>-206.362</v>
       </c>
       <c r="F24">
-        <v>158.532</v>
+        <v>165.738</v>
       </c>
       <c r="G24">
         <v>133.3</v>
@@ -3255,28 +3255,28 @@
         <v>50.425</v>
       </c>
       <c r="M24">
-        <v>8.766819600000002</v>
+        <v>9.1653114</v>
       </c>
       <c r="N24">
-        <v>41.65818039999999</v>
+        <v>41.2596886</v>
       </c>
       <c r="O24">
-        <v>6.248727059999998</v>
+        <v>6.18895329</v>
       </c>
       <c r="P24">
-        <v>35.40945333999999</v>
+        <v>35.07073531</v>
       </c>
       <c r="Q24">
-        <v>43.10945333999999</v>
+        <v>42.77073531</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1122986213448919</v>
+        <v>0.1130577482220076</v>
       </c>
       <c r="T24">
-        <v>1.26145427415177</v>
+        <v>1.275854630495919</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.75180080128488</v>
+        <v>5.501722505576843</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09786561613094588</v>
+        <v>0.09779720761287605</v>
       </c>
       <c r="C25">
-        <v>567.3429927759578</v>
+        <v>560.9260760895797</v>
       </c>
       <c r="D25">
-        <v>599.7809927759579</v>
+        <v>600.5700760895797</v>
       </c>
       <c r="E25">
-        <v>-206.362</v>
+        <v>-199.156</v>
       </c>
       <c r="F25">
-        <v>165.738</v>
+        <v>172.944</v>
       </c>
       <c r="G25">
         <v>133.3</v>
@@ -3337,28 +3337,28 @@
         <v>50.425</v>
       </c>
       <c r="M25">
-        <v>9.1653114</v>
+        <v>9.563803200000001</v>
       </c>
       <c r="N25">
-        <v>41.2596886</v>
+        <v>40.86119679999999</v>
       </c>
       <c r="O25">
-        <v>6.18895329</v>
+        <v>6.129179519999999</v>
       </c>
       <c r="P25">
-        <v>35.07073531</v>
+        <v>34.73201727999999</v>
       </c>
       <c r="Q25">
-        <v>42.77073531</v>
+        <v>42.43201728</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1130577482220076</v>
+        <v>0.1138368521222053</v>
       </c>
       <c r="T25">
-        <v>1.275854630495919</v>
+        <v>1.290633943585967</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.501722505576843</v>
+        <v>5.272484067844474</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09779720761287605</v>
+        <v>0.09772879909480622</v>
       </c>
       <c r="C26">
-        <v>560.9260760895797</v>
+        <v>554.5112384044904</v>
       </c>
       <c r="D26">
-        <v>600.5700760895797</v>
+        <v>601.3612384044903</v>
       </c>
       <c r="E26">
-        <v>-199.156</v>
+        <v>-191.95</v>
       </c>
       <c r="F26">
-        <v>172.944</v>
+        <v>180.15</v>
       </c>
       <c r="G26">
         <v>133.3</v>
@@ -3419,28 +3419,28 @@
         <v>50.425</v>
       </c>
       <c r="M26">
-        <v>9.563803199999999</v>
+        <v>9.962295000000001</v>
       </c>
       <c r="N26">
-        <v>40.8611968</v>
+        <v>40.462705</v>
       </c>
       <c r="O26">
-        <v>6.12917952</v>
+        <v>6.06940575</v>
       </c>
       <c r="P26">
-        <v>34.73201728</v>
+        <v>34.39329925</v>
       </c>
       <c r="Q26">
-        <v>42.43201728</v>
+        <v>42.09329925</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1138368521222053</v>
+        <v>0.1146367321264083</v>
       </c>
       <c r="T26">
-        <v>1.290633943585967</v>
+        <v>1.305807371691749</v>
       </c>
       <c r="U26">
         <v>0.0553</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>5.272484067844475</v>
+        <v>5.061584705130695</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09772879909480622</v>
+        <v>0.09766039057673639</v>
       </c>
       <c r="C27">
-        <v>554.5112384044904</v>
+        <v>548.0984879478585</v>
       </c>
       <c r="D27">
-        <v>601.3612384044903</v>
+        <v>602.1544879478586</v>
       </c>
       <c r="E27">
-        <v>-191.95</v>
+        <v>-184.744</v>
       </c>
       <c r="F27">
-        <v>180.15</v>
+        <v>187.356</v>
       </c>
       <c r="G27">
         <v>133.3</v>
@@ -3501,28 +3501,28 @@
         <v>50.425</v>
       </c>
       <c r="M27">
-        <v>9.962295000000001</v>
+        <v>10.3607868</v>
       </c>
       <c r="N27">
-        <v>40.462705</v>
+        <v>40.0642132</v>
       </c>
       <c r="O27">
-        <v>6.06940575</v>
+        <v>6.009631979999999</v>
       </c>
       <c r="P27">
-        <v>34.39329925</v>
+        <v>34.05458122</v>
       </c>
       <c r="Q27">
-        <v>42.09329925</v>
+        <v>41.75458122</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1146367321264083</v>
+        <v>0.1154582305091032</v>
       </c>
       <c r="T27">
-        <v>1.305807371691749</v>
+        <v>1.321390892449039</v>
       </c>
       <c r="U27">
         <v>0.0553</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.061584705130695</v>
+        <v>4.866908370317976</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09766039057673639</v>
+        <v>0.09759198205866658</v>
       </c>
       <c r="C28">
-        <v>548.0984879478585</v>
+        <v>541.6878329903196</v>
       </c>
       <c r="D28">
-        <v>602.1544879478586</v>
+        <v>602.9498329903197</v>
       </c>
       <c r="E28">
-        <v>-184.744</v>
+        <v>-177.538</v>
       </c>
       <c r="F28">
-        <v>187.356</v>
+        <v>194.562</v>
       </c>
       <c r="G28">
         <v>133.3</v>
@@ -3583,28 +3583,28 @@
         <v>50.425</v>
       </c>
       <c r="M28">
-        <v>10.3607868</v>
+        <v>10.7592786</v>
       </c>
       <c r="N28">
-        <v>40.0642132</v>
+        <v>39.6657214</v>
       </c>
       <c r="O28">
-        <v>6.009631979999999</v>
+        <v>5.949858209999999</v>
       </c>
       <c r="P28">
-        <v>34.05458122</v>
+        <v>33.71586318999999</v>
       </c>
       <c r="Q28">
-        <v>41.75458122</v>
+        <v>41.41586319</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1154582305091032</v>
+        <v>0.1163022356968035</v>
       </c>
       <c r="T28">
-        <v>1.321390892449039</v>
+        <v>1.337401358980502</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>4.866908370317976</v>
+        <v>4.686652504750643</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09759198205866658</v>
+        <v>0.09752357354059675</v>
       </c>
       <c r="C29">
-        <v>541.6878329903196</v>
+        <v>535.2792818462642</v>
       </c>
       <c r="D29">
-        <v>602.9498329903197</v>
+        <v>603.7472818462643</v>
       </c>
       <c r="E29">
-        <v>-177.538</v>
+        <v>-170.332</v>
       </c>
       <c r="F29">
-        <v>194.562</v>
+        <v>201.768</v>
       </c>
       <c r="G29">
         <v>133.3</v>
@@ -3665,28 +3665,28 @@
         <v>50.425</v>
       </c>
       <c r="M29">
-        <v>10.7592786</v>
+        <v>11.1577704</v>
       </c>
       <c r="N29">
-        <v>39.6657214</v>
+        <v>39.26722959999999</v>
       </c>
       <c r="O29">
-        <v>5.949858209999999</v>
+        <v>5.890084439999999</v>
       </c>
       <c r="P29">
-        <v>33.71586318999999</v>
+        <v>33.37714516</v>
       </c>
       <c r="Q29">
-        <v>41.41586319</v>
+        <v>41.07714516</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1163022356968035</v>
+        <v>0.117169685473051</v>
       </c>
       <c r="T29">
-        <v>1.337401358980502</v>
+        <v>1.353856560693394</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>4.686652504750643</v>
+        <v>4.519272058152405</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09752357354059675</v>
+        <v>0.09807141502252692</v>
       </c>
       <c r="C30">
-        <v>535.2792818462642</v>
+        <v>521.7455823673919</v>
       </c>
       <c r="D30">
-        <v>603.7472818462643</v>
+        <v>597.419582367392</v>
       </c>
       <c r="E30">
-        <v>-170.332</v>
+        <v>-163.126</v>
       </c>
       <c r="F30">
-        <v>201.768</v>
+        <v>208.974</v>
       </c>
       <c r="G30">
         <v>133.3</v>
@@ -3747,45 +3747,45 @@
         <v>50.425</v>
       </c>
       <c r="M30">
-        <v>11.1577704</v>
+        <v>12.0786972</v>
       </c>
       <c r="N30">
-        <v>39.26722959999999</v>
+        <v>38.34630279999999</v>
       </c>
       <c r="O30">
-        <v>5.890084439999999</v>
+        <v>5.751945419999998</v>
       </c>
       <c r="P30">
-        <v>33.37714516</v>
+        <v>32.59435737999999</v>
       </c>
       <c r="Q30">
-        <v>41.07714516</v>
+        <v>40.29435737999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.117169685473051</v>
+        <v>0.1180615704542633</v>
       </c>
       <c r="T30">
-        <v>1.353856560693394</v>
+        <v>1.3707752892151</v>
       </c>
       <c r="U30">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V30">
         <v>0.15</v>
       </c>
       <c r="W30">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>4.519272058152405</v>
+        <v>4.174705199166676</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09807141502252692</v>
+        <v>0.09802425650445709</v>
       </c>
       <c r="C31">
-        <v>521.745582367392</v>
+        <v>515.0790524155282</v>
       </c>
       <c r="D31">
-        <v>597.419582367392</v>
+        <v>597.9590524155283</v>
       </c>
       <c r="E31">
-        <v>-163.126</v>
+        <v>-155.92</v>
       </c>
       <c r="F31">
-        <v>208.974</v>
+        <v>216.18</v>
       </c>
       <c r="G31">
         <v>133.3</v>
@@ -3829,28 +3829,28 @@
         <v>50.425</v>
       </c>
       <c r="M31">
-        <v>12.0786972</v>
+        <v>12.495204</v>
       </c>
       <c r="N31">
-        <v>38.3463028</v>
+        <v>37.929796</v>
       </c>
       <c r="O31">
-        <v>5.751945419999999</v>
+        <v>5.689469399999999</v>
       </c>
       <c r="P31">
-        <v>32.59435738</v>
+        <v>32.2403266</v>
       </c>
       <c r="Q31">
-        <v>40.29435738</v>
+        <v>39.9403266</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1180615704542633</v>
+        <v>0.1189789378635101</v>
       </c>
       <c r="T31">
-        <v>1.3707752892151</v>
+        <v>1.388177409980283</v>
       </c>
       <c r="U31">
         <v>0.0578</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.174705199166677</v>
+        <v>4.035548359194455</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09802425650445709</v>
+        <v>0.09889934798638725</v>
       </c>
       <c r="C32">
-        <v>515.0790524155282</v>
+        <v>498.0185270182296</v>
       </c>
       <c r="D32">
-        <v>597.9590524155283</v>
+        <v>588.1045270182295</v>
       </c>
       <c r="E32">
-        <v>-155.92</v>
+        <v>-148.714</v>
       </c>
       <c r="F32">
-        <v>216.18</v>
+        <v>223.386</v>
       </c>
       <c r="G32">
         <v>133.3</v>
@@ -3911,45 +3911,45 @@
         <v>50.425</v>
       </c>
       <c r="M32">
-        <v>12.495204</v>
+        <v>13.6935618</v>
       </c>
       <c r="N32">
-        <v>37.929796</v>
+        <v>36.7314382</v>
       </c>
       <c r="O32">
-        <v>5.689469399999999</v>
+        <v>5.50971573</v>
       </c>
       <c r="P32">
-        <v>32.2403266</v>
+        <v>31.22172247</v>
       </c>
       <c r="Q32">
-        <v>39.9403266</v>
+        <v>38.92172247000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1189789378635101</v>
+        <v>0.1199228956324453</v>
       </c>
       <c r="T32">
-        <v>1.388177409980283</v>
+        <v>1.406083940043007</v>
       </c>
       <c r="U32">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V32">
         <v>0.15</v>
       </c>
       <c r="W32">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>4.035548359194455</v>
+        <v>3.682387441374092</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09889934798638725</v>
+        <v>0.0988819394683174</v>
       </c>
       <c r="C33">
-        <v>498.0185270182296</v>
+        <v>491.0053991775384</v>
       </c>
       <c r="D33">
-        <v>588.1045270182295</v>
+        <v>588.2973991775383</v>
       </c>
       <c r="E33">
-        <v>-148.714</v>
+        <v>-141.508</v>
       </c>
       <c r="F33">
-        <v>223.386</v>
+        <v>230.592</v>
       </c>
       <c r="G33">
         <v>133.3</v>
@@ -3993,28 +3993,28 @@
         <v>50.425</v>
       </c>
       <c r="M33">
-        <v>13.6935618</v>
+        <v>14.1352896</v>
       </c>
       <c r="N33">
-        <v>36.7314382</v>
+        <v>36.2897104</v>
       </c>
       <c r="O33">
-        <v>5.50971573</v>
+        <v>5.44345656</v>
       </c>
       <c r="P33">
-        <v>31.22172247</v>
+        <v>30.84625384</v>
       </c>
       <c r="Q33">
-        <v>38.92172247000001</v>
+        <v>38.54625384</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1199228956324453</v>
+        <v>0.1208946168651727</v>
       </c>
       <c r="T33">
-        <v>1.406083940043007</v>
+        <v>1.424517132754636</v>
       </c>
       <c r="U33">
         <v>0.0613</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>3.682387441374092</v>
+        <v>3.567312833831151</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.0988819394683174</v>
+        <v>0.09964993095024759</v>
       </c>
       <c r="C34">
-        <v>491.0053991775384</v>
+        <v>475.4092790151287</v>
       </c>
       <c r="D34">
-        <v>588.2973991775383</v>
+        <v>579.9072790151288</v>
       </c>
       <c r="E34">
-        <v>-141.508</v>
+        <v>-134.302</v>
       </c>
       <c r="F34">
-        <v>230.592</v>
+        <v>237.798</v>
       </c>
       <c r="G34">
         <v>133.3</v>
@@ -4075,45 +4075,45 @@
         <v>50.425</v>
       </c>
       <c r="M34">
-        <v>14.1352896</v>
+        <v>15.2428518</v>
       </c>
       <c r="N34">
-        <v>36.2897104</v>
+        <v>35.18214819999999</v>
       </c>
       <c r="O34">
-        <v>5.44345656</v>
+        <v>5.277322229999998</v>
       </c>
       <c r="P34">
-        <v>30.84625384</v>
+        <v>29.90482596999999</v>
       </c>
       <c r="Q34">
-        <v>38.54625384</v>
+        <v>37.60482596999999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1208946168651727</v>
+        <v>0.1218953447018621</v>
       </c>
       <c r="T34">
-        <v>1.424517132754636</v>
+        <v>1.44350057002482</v>
       </c>
       <c r="U34">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V34">
         <v>0.15</v>
       </c>
       <c r="W34">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y34">
-        <v>3.567312833831151</v>
+        <v>3.308108001155006</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09964993095024759</v>
+        <v>0.09965632243217777</v>
       </c>
       <c r="C35">
-        <v>475.4092790151287</v>
+        <v>468.1344576265225</v>
       </c>
       <c r="D35">
-        <v>579.9072790151288</v>
+        <v>579.8384576265225</v>
       </c>
       <c r="E35">
-        <v>-134.302</v>
+        <v>-127.096</v>
       </c>
       <c r="F35">
-        <v>237.798</v>
+        <v>245.004</v>
       </c>
       <c r="G35">
         <v>133.3</v>
@@ -4157,28 +4157,28 @@
         <v>50.425</v>
       </c>
       <c r="M35">
-        <v>15.2428518</v>
+        <v>15.7047564</v>
       </c>
       <c r="N35">
-        <v>35.18214819999999</v>
+        <v>34.7202436</v>
       </c>
       <c r="O35">
-        <v>5.277322229999998</v>
+        <v>5.208036539999999</v>
       </c>
       <c r="P35">
-        <v>29.90482596999999</v>
+        <v>29.51220706</v>
       </c>
       <c r="Q35">
-        <v>37.60482596999999</v>
+        <v>37.21220706</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1218953447018621</v>
+        <v>0.1229263976245118</v>
       </c>
       <c r="T35">
-        <v>1.44350057002482</v>
+        <v>1.463059262969859</v>
       </c>
       <c r="U35">
         <v>0.0641</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>3.308108001155006</v>
+        <v>3.210810707003389</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09965632243217777</v>
+        <v>0.09966271391410794</v>
       </c>
       <c r="C36">
-        <v>468.1344576265225</v>
+        <v>460.8596525709465</v>
       </c>
       <c r="D36">
-        <v>579.8384576265225</v>
+        <v>579.7696525709465</v>
       </c>
       <c r="E36">
-        <v>-127.096</v>
+        <v>-119.89</v>
       </c>
       <c r="F36">
-        <v>245.004</v>
+        <v>252.21</v>
       </c>
       <c r="G36">
         <v>133.3</v>
@@ -4239,28 +4239,28 @@
         <v>50.425</v>
       </c>
       <c r="M36">
-        <v>15.7047564</v>
+        <v>16.166661</v>
       </c>
       <c r="N36">
-        <v>34.7202436</v>
+        <v>34.25833899999999</v>
       </c>
       <c r="O36">
-        <v>5.208036539999999</v>
+        <v>5.138750849999998</v>
       </c>
       <c r="P36">
-        <v>29.51220706</v>
+        <v>29.11958814999999</v>
       </c>
       <c r="Q36">
-        <v>37.21220706</v>
+        <v>36.81958815</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1229263976245118</v>
+        <v>0.1239891752524738</v>
       </c>
       <c r="T36">
-        <v>1.463059262969859</v>
+        <v>1.483219761851667</v>
       </c>
       <c r="U36">
         <v>0.0641</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.210810707003389</v>
+        <v>3.119073258231863</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09966271391410794</v>
+        <v>0.0996691053960381</v>
       </c>
       <c r="C37">
-        <v>460.8596525709465</v>
+        <v>453.584863842587</v>
       </c>
       <c r="D37">
-        <v>579.7696525709465</v>
+        <v>579.700863842587</v>
       </c>
       <c r="E37">
-        <v>-119.89</v>
+        <v>-112.684</v>
       </c>
       <c r="F37">
-        <v>252.21</v>
+        <v>259.4160000000001</v>
       </c>
       <c r="G37">
         <v>133.3</v>
@@ -4321,28 +4321,28 @@
         <v>50.425</v>
       </c>
       <c r="M37">
-        <v>16.166661</v>
+        <v>16.62856560000001</v>
       </c>
       <c r="N37">
-        <v>34.25833899999999</v>
+        <v>33.7964344</v>
       </c>
       <c r="O37">
-        <v>5.138750849999998</v>
+        <v>5.069465159999999</v>
       </c>
       <c r="P37">
-        <v>29.11958814999999</v>
+        <v>28.72696924</v>
       </c>
       <c r="Q37">
-        <v>36.81958815</v>
+        <v>36.42696924</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1239891752524738</v>
+        <v>0.1250851646813096</v>
       </c>
       <c r="T37">
-        <v>1.483219761851667</v>
+        <v>1.504010276323533</v>
       </c>
       <c r="U37">
         <v>0.0641</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.119073258231863</v>
+        <v>3.032432334392089</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.0996691053960381</v>
+        <v>0.1021285968779683</v>
       </c>
       <c r="C38">
-        <v>453.584863842587</v>
+        <v>421.0672208102345</v>
       </c>
       <c r="D38">
-        <v>579.700863842587</v>
+        <v>554.3892208102344</v>
       </c>
       <c r="E38">
-        <v>-112.684</v>
+        <v>-105.478</v>
       </c>
       <c r="F38">
-        <v>259.416</v>
+        <v>266.622</v>
       </c>
       <c r="G38">
         <v>133.3</v>
@@ -4403,45 +4403,45 @@
         <v>50.425</v>
       </c>
       <c r="M38">
-        <v>16.6285656</v>
+        <v>19.1701218</v>
       </c>
       <c r="N38">
-        <v>33.7964344</v>
+        <v>31.25487819999999</v>
       </c>
       <c r="O38">
-        <v>5.069465159999999</v>
+        <v>4.688231729999999</v>
       </c>
       <c r="P38">
-        <v>28.72696924</v>
+        <v>26.56664646999999</v>
       </c>
       <c r="Q38">
-        <v>36.42696924</v>
+        <v>34.26664647</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1250851646813095</v>
+        <v>0.1262159474253465</v>
       </c>
       <c r="T38">
-        <v>1.504010276323533</v>
+        <v>1.525460807127838</v>
       </c>
       <c r="U38">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V38">
         <v>0.15</v>
       </c>
       <c r="W38">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>3.032432334392089</v>
+        <v>2.630395389558766</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1021285968779683</v>
+        <v>0.1022012883598985</v>
       </c>
       <c r="C39">
-        <v>421.0672208102345</v>
+        <v>413.1467092237321</v>
       </c>
       <c r="D39">
-        <v>554.3892208102344</v>
+        <v>553.6747092237322</v>
       </c>
       <c r="E39">
-        <v>-105.478</v>
+        <v>-98.27199999999999</v>
       </c>
       <c r="F39">
-        <v>266.622</v>
+        <v>273.828</v>
       </c>
       <c r="G39">
         <v>133.3</v>
@@ -4485,28 +4485,28 @@
         <v>50.425</v>
       </c>
       <c r="M39">
-        <v>19.1701218</v>
+        <v>19.6882332</v>
       </c>
       <c r="N39">
-        <v>31.25487819999999</v>
+        <v>30.73676679999999</v>
       </c>
       <c r="O39">
-        <v>4.688231729999999</v>
+        <v>4.610515019999999</v>
       </c>
       <c r="P39">
-        <v>26.56664646999999</v>
+        <v>26.12625178</v>
       </c>
       <c r="Q39">
-        <v>34.26664647</v>
+        <v>33.82625178</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1262159474253465</v>
+        <v>0.1273832070320943</v>
       </c>
       <c r="T39">
-        <v>1.525460807127838</v>
+        <v>1.547603290538734</v>
       </c>
       <c r="U39">
         <v>0.07190000000000001</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.630395389558766</v>
+        <v>2.561174458254588</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1022012883598985</v>
+        <v>0.1035668298418286</v>
       </c>
       <c r="C40">
-        <v>413.1467092237321</v>
+        <v>392.8524752837565</v>
       </c>
       <c r="D40">
-        <v>553.6747092237322</v>
+        <v>540.5864752837564</v>
       </c>
       <c r="E40">
-        <v>-98.27199999999999</v>
+        <v>-91.06600000000003</v>
       </c>
       <c r="F40">
-        <v>273.828</v>
+        <v>281.034</v>
       </c>
       <c r="G40">
         <v>133.3</v>
@@ -4567,45 +4567,45 @@
         <v>50.425</v>
       </c>
       <c r="M40">
-        <v>19.6882332</v>
+        <v>21.3023772</v>
       </c>
       <c r="N40">
-        <v>30.73676679999999</v>
+        <v>29.12262279999999</v>
       </c>
       <c r="O40">
-        <v>4.610515019999999</v>
+        <v>4.368393419999999</v>
       </c>
       <c r="P40">
-        <v>26.12625178</v>
+        <v>24.75422937999999</v>
       </c>
       <c r="Q40">
-        <v>33.82625178</v>
+        <v>32.45422938</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1273832070320943</v>
+        <v>0.1285887374456207</v>
       </c>
       <c r="T40">
-        <v>1.547603290538734</v>
+        <v>1.570471757012283</v>
       </c>
       <c r="U40">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V40">
         <v>0.15</v>
       </c>
       <c r="W40">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y40">
-        <v>2.561174458254588</v>
+        <v>2.367106709574178</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1035668298418286</v>
+        <v>0.1036726713237588</v>
       </c>
       <c r="C41">
-        <v>392.8524752837565</v>
+        <v>384.6578139286348</v>
       </c>
       <c r="D41">
-        <v>540.5864752837564</v>
+        <v>539.5978139286348</v>
       </c>
       <c r="E41">
-        <v>-91.06600000000003</v>
+        <v>-83.86000000000001</v>
       </c>
       <c r="F41">
-        <v>281.034</v>
+        <v>288.24</v>
       </c>
       <c r="G41">
         <v>133.3</v>
@@ -4649,28 +4649,28 @@
         <v>50.425</v>
       </c>
       <c r="M41">
-        <v>21.3023772</v>
+        <v>21.848592</v>
       </c>
       <c r="N41">
-        <v>29.12262279999999</v>
+        <v>28.57640799999999</v>
       </c>
       <c r="O41">
-        <v>4.368393419999999</v>
+        <v>4.286461199999999</v>
       </c>
       <c r="P41">
-        <v>24.75422937999999</v>
+        <v>24.2899468</v>
       </c>
       <c r="Q41">
-        <v>32.45422938</v>
+        <v>31.9899468</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1285887374456207</v>
+        <v>0.1298344522062647</v>
       </c>
       <c r="T41">
-        <v>1.570471757012283</v>
+        <v>1.594102505701616</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.367106709574178</v>
+        <v>2.307929041834823</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1036726713237588</v>
+        <v>0.103778512805689</v>
       </c>
       <c r="C42">
-        <v>384.6578139286348</v>
+        <v>376.4667622343305</v>
       </c>
       <c r="D42">
-        <v>539.5978139286348</v>
+        <v>538.6127622343306</v>
       </c>
       <c r="E42">
-        <v>-83.86000000000001</v>
+        <v>-76.654</v>
       </c>
       <c r="F42">
-        <v>288.24</v>
+        <v>295.446</v>
       </c>
       <c r="G42">
         <v>133.3</v>
@@ -4731,28 +4731,28 @@
         <v>50.425</v>
       </c>
       <c r="M42">
-        <v>21.848592</v>
+        <v>22.3948068</v>
       </c>
       <c r="N42">
-        <v>28.57640799999999</v>
+        <v>28.03019319999999</v>
       </c>
       <c r="O42">
-        <v>4.286461199999999</v>
+        <v>4.204528979999998</v>
       </c>
       <c r="P42">
-        <v>24.2899468</v>
+        <v>23.82566421999999</v>
       </c>
       <c r="Q42">
-        <v>31.9899468</v>
+        <v>31.52566422</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1298344522062647</v>
+        <v>0.1311223945859135</v>
       </c>
       <c r="T42">
-        <v>1.594102505701616</v>
+        <v>1.618534296719401</v>
       </c>
       <c r="U42">
         <v>0.07580000000000001</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>2.307929041834823</v>
+        <v>2.251638089594949</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.103778512805689</v>
+        <v>0.1038843542876192</v>
       </c>
       <c r="C43">
-        <v>376.4667622343305</v>
+        <v>368.2793004682394</v>
       </c>
       <c r="D43">
-        <v>538.6127622343306</v>
+        <v>537.6313004682394</v>
       </c>
       <c r="E43">
-        <v>-76.654</v>
+        <v>-69.44799999999998</v>
       </c>
       <c r="F43">
-        <v>295.446</v>
+        <v>302.652</v>
       </c>
       <c r="G43">
         <v>133.3</v>
@@ -4813,28 +4813,28 @@
         <v>50.425</v>
       </c>
       <c r="M43">
-        <v>22.3948068</v>
+        <v>22.94102160000001</v>
       </c>
       <c r="N43">
-        <v>28.03019319999999</v>
+        <v>27.48397839999999</v>
       </c>
       <c r="O43">
-        <v>4.204528979999998</v>
+        <v>4.122596759999999</v>
       </c>
       <c r="P43">
-        <v>23.82566421999999</v>
+        <v>23.36138163999999</v>
       </c>
       <c r="Q43">
-        <v>31.52566422</v>
+        <v>31.06138163999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1311223945859135</v>
+        <v>0.1324547487717572</v>
       </c>
       <c r="T43">
-        <v>1.618534296719401</v>
+        <v>1.643808563289524</v>
       </c>
       <c r="U43">
         <v>0.07580000000000001</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>2.251638089594949</v>
+        <v>2.198027658890308</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1038843542876191</v>
+        <v>0.1039901957695493</v>
       </c>
       <c r="C44">
-        <v>368.2793004682395</v>
+        <v>360.0954090413235</v>
       </c>
       <c r="D44">
-        <v>537.6313004682395</v>
+        <v>536.6534090413235</v>
       </c>
       <c r="E44">
-        <v>-69.44800000000004</v>
+        <v>-62.24200000000002</v>
       </c>
       <c r="F44">
-        <v>302.652</v>
+        <v>309.858</v>
       </c>
       <c r="G44">
         <v>133.3</v>
@@ -4895,28 +4895,28 @@
         <v>50.425</v>
       </c>
       <c r="M44">
-        <v>22.9410216</v>
+        <v>23.4872364</v>
       </c>
       <c r="N44">
-        <v>27.4839784</v>
+        <v>26.93776359999999</v>
       </c>
       <c r="O44">
-        <v>4.12259676</v>
+        <v>4.040664539999999</v>
       </c>
       <c r="P44">
-        <v>23.36138164</v>
+        <v>22.89709906</v>
       </c>
       <c r="Q44">
-        <v>31.06138164</v>
+        <v>30.59709906</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1324547487717571</v>
+        <v>0.1338338522272795</v>
       </c>
       <c r="T44">
-        <v>1.643808563289524</v>
+        <v>1.669969646230528</v>
       </c>
       <c r="U44">
         <v>0.07580000000000001</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>2.198027658890308</v>
+        <v>2.146910736590534</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1039901957695493</v>
+        <v>0.1040960372514795</v>
       </c>
       <c r="C45">
-        <v>360.0954090413235</v>
+        <v>351.9150685068069</v>
       </c>
       <c r="D45">
-        <v>536.6534090413235</v>
+        <v>535.6790685068069</v>
       </c>
       <c r="E45">
-        <v>-62.24200000000002</v>
+        <v>-55.036</v>
       </c>
       <c r="F45">
-        <v>309.858</v>
+        <v>317.064</v>
       </c>
       <c r="G45">
         <v>133.3</v>
@@ -4977,28 +4977,28 @@
         <v>50.425</v>
       </c>
       <c r="M45">
-        <v>23.4872364</v>
+        <v>24.03345120000001</v>
       </c>
       <c r="N45">
-        <v>26.93776359999999</v>
+        <v>26.39154879999999</v>
       </c>
       <c r="O45">
-        <v>4.040664539999999</v>
+        <v>3.958732319999998</v>
       </c>
       <c r="P45">
-        <v>22.89709906</v>
+        <v>22.43281647999999</v>
       </c>
       <c r="Q45">
-        <v>30.59709906</v>
+        <v>30.13281648</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1338338522272795</v>
+        <v>0.1352622093776419</v>
       </c>
       <c r="T45">
-        <v>1.669969646230528</v>
+        <v>1.697065053562283</v>
       </c>
       <c r="U45">
         <v>0.07580000000000001</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>2.146910736590534</v>
+        <v>2.09811731075893</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1040960372514795</v>
+        <v>0.1042018787334097</v>
       </c>
       <c r="C46">
-        <v>351.9150685068069</v>
+        <v>343.7382595588869</v>
       </c>
       <c r="D46">
-        <v>535.6790685068069</v>
+        <v>534.7082595588869</v>
       </c>
       <c r="E46">
-        <v>-55.036</v>
+        <v>-47.82999999999998</v>
       </c>
       <c r="F46">
-        <v>317.064</v>
+        <v>324.27</v>
       </c>
       <c r="G46">
         <v>133.3</v>
@@ -5059,28 +5059,28 @@
         <v>50.425</v>
       </c>
       <c r="M46">
-        <v>24.03345120000001</v>
+        <v>24.57966600000001</v>
       </c>
       <c r="N46">
-        <v>26.39154879999999</v>
+        <v>25.84533399999999</v>
       </c>
       <c r="O46">
-        <v>3.958732319999998</v>
+        <v>3.876800099999998</v>
       </c>
       <c r="P46">
-        <v>22.43281647999999</v>
+        <v>21.96853389999999</v>
       </c>
       <c r="Q46">
-        <v>30.13281648</v>
+        <v>29.6685339</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1352622093776419</v>
+        <v>0.1367425067880176</v>
       </c>
       <c r="T46">
-        <v>1.697065053562283</v>
+        <v>1.725145748433373</v>
       </c>
       <c r="U46">
         <v>0.07580000000000001</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.09811731075893</v>
+        <v>2.051492481630954</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1042018787334097</v>
+        <v>0.1043077202153398</v>
       </c>
       <c r="C47">
-        <v>343.7382595588869</v>
+        <v>335.5649630314591</v>
       </c>
       <c r="D47">
-        <v>534.7082595588869</v>
+        <v>533.740963031459</v>
       </c>
       <c r="E47">
-        <v>-47.82999999999998</v>
+        <v>-40.62400000000002</v>
       </c>
       <c r="F47">
-        <v>324.27</v>
+        <v>331.476</v>
       </c>
       <c r="G47">
         <v>133.3</v>
@@ -5141,28 +5141,28 @@
         <v>50.425</v>
       </c>
       <c r="M47">
-        <v>24.57966600000001</v>
+        <v>25.1258808</v>
       </c>
       <c r="N47">
-        <v>25.84533399999999</v>
+        <v>25.2991192</v>
       </c>
       <c r="O47">
-        <v>3.876800099999998</v>
+        <v>3.794867879999999</v>
       </c>
       <c r="P47">
-        <v>21.96853389999999</v>
+        <v>21.50425132</v>
       </c>
       <c r="Q47">
-        <v>29.6685339</v>
+        <v>29.20425132</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1367425067880176</v>
+        <v>0.1382776300284071</v>
       </c>
       <c r="T47">
-        <v>1.725145748433373</v>
+        <v>1.754266469040431</v>
       </c>
       <c r="U47">
         <v>0.07580000000000001</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.051492481630954</v>
+        <v>2.006894818986803</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1043077202153398</v>
+        <v>0.11008646169727</v>
       </c>
       <c r="C48">
-        <v>335.5649630314591</v>
+        <v>280.3807268329931</v>
       </c>
       <c r="D48">
-        <v>533.740963031459</v>
+        <v>485.7627268329932</v>
       </c>
       <c r="E48">
-        <v>-40.62400000000002</v>
+        <v>-33.41800000000001</v>
       </c>
       <c r="F48">
-        <v>331.476</v>
+        <v>338.682</v>
       </c>
       <c r="G48">
         <v>133.3</v>
@@ -5223,45 +5223,45 @@
         <v>50.425</v>
       </c>
       <c r="M48">
-        <v>25.1258808</v>
+        <v>30.48138</v>
       </c>
       <c r="N48">
-        <v>25.2991192</v>
+        <v>19.94362</v>
       </c>
       <c r="O48">
-        <v>3.794867879999999</v>
+        <v>2.991542999999999</v>
       </c>
       <c r="P48">
-        <v>21.50425132</v>
+        <v>16.952077</v>
       </c>
       <c r="Q48">
-        <v>29.20425132</v>
+        <v>24.652077</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1382776300284071</v>
+        <v>0.1398706824476793</v>
       </c>
       <c r="T48">
-        <v>1.754266469040431</v>
+        <v>1.784486084764736</v>
       </c>
       <c r="U48">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V48">
         <v>0.15</v>
       </c>
       <c r="W48">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.006894818986803</v>
+        <v>1.654288618166238</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.11008646169727</v>
+        <v>0.1103130031792002</v>
       </c>
       <c r="C49">
-        <v>280.3807268329931</v>
+        <v>271.4689403623569</v>
       </c>
       <c r="D49">
-        <v>485.7627268329932</v>
+        <v>484.056940362357</v>
       </c>
       <c r="E49">
-        <v>-33.41800000000001</v>
+        <v>-26.21199999999999</v>
       </c>
       <c r="F49">
-        <v>338.682</v>
+        <v>345.888</v>
       </c>
       <c r="G49">
         <v>133.3</v>
@@ -5305,28 +5305,28 @@
         <v>50.425</v>
       </c>
       <c r="M49">
-        <v>30.48138</v>
+        <v>31.12992</v>
       </c>
       <c r="N49">
-        <v>19.94362</v>
+        <v>19.29508</v>
       </c>
       <c r="O49">
-        <v>2.991542999999999</v>
+        <v>2.894261999999999</v>
       </c>
       <c r="P49">
-        <v>16.952077</v>
+        <v>16.400818</v>
       </c>
       <c r="Q49">
-        <v>24.652077</v>
+        <v>24.100818</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1398706824476793</v>
+        <v>0.1415250061138465</v>
       </c>
       <c r="T49">
-        <v>1.784486084764736</v>
+        <v>1.815867993401513</v>
       </c>
       <c r="U49">
         <v>0.09</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>1.654288618166238</v>
+        <v>1.619824271954441</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1103130031792002</v>
+        <v>0.1105395446611303</v>
       </c>
       <c r="C50">
-        <v>271.468940362357</v>
+        <v>262.5690919242462</v>
       </c>
       <c r="D50">
-        <v>484.056940362357</v>
+        <v>482.3630919242461</v>
       </c>
       <c r="E50">
-        <v>-26.21200000000005</v>
+        <v>-19.00600000000003</v>
       </c>
       <c r="F50">
-        <v>345.888</v>
+        <v>353.094</v>
       </c>
       <c r="G50">
         <v>133.3</v>
@@ -5387,28 +5387,28 @@
         <v>50.425</v>
       </c>
       <c r="M50">
-        <v>31.12992</v>
+        <v>31.77846</v>
       </c>
       <c r="N50">
-        <v>19.29508</v>
+        <v>18.64654</v>
       </c>
       <c r="O50">
-        <v>2.894262</v>
+        <v>2.796981</v>
       </c>
       <c r="P50">
-        <v>16.400818</v>
+        <v>15.849559</v>
       </c>
       <c r="Q50">
-        <v>24.100818</v>
+        <v>23.549559</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1415250061138465</v>
+        <v>0.1432442052179026</v>
       </c>
       <c r="T50">
-        <v>1.815867993401513</v>
+        <v>1.848480565122086</v>
       </c>
       <c r="U50">
         <v>0.09</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>1.619824271954441</v>
+        <v>1.586766633751289</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1105395446611303</v>
+        <v>0.1107660861430605</v>
       </c>
       <c r="C51">
-        <v>262.5690919242462</v>
+        <v>253.6810566322892</v>
       </c>
       <c r="D51">
-        <v>482.3630919242461</v>
+        <v>480.6810566322891</v>
       </c>
       <c r="E51">
-        <v>-19.00600000000003</v>
+        <v>-11.80000000000001</v>
       </c>
       <c r="F51">
-        <v>353.094</v>
+        <v>360.3</v>
       </c>
       <c r="G51">
         <v>133.3</v>
@@ -5469,28 +5469,28 @@
         <v>50.425</v>
       </c>
       <c r="M51">
-        <v>31.77846</v>
+        <v>32.427</v>
       </c>
       <c r="N51">
-        <v>18.64654</v>
+        <v>17.998</v>
       </c>
       <c r="O51">
-        <v>2.796981</v>
+        <v>2.6997</v>
       </c>
       <c r="P51">
-        <v>15.849559</v>
+        <v>15.2983</v>
       </c>
       <c r="Q51">
-        <v>23.549559</v>
+        <v>22.9983</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1432442052179026</v>
+        <v>0.1450321722861211</v>
       </c>
       <c r="T51">
-        <v>1.848480565122086</v>
+        <v>1.882397639711483</v>
       </c>
       <c r="U51">
         <v>0.09</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>1.586766633751289</v>
+        <v>1.555031301076264</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1107660861430605</v>
+        <v>0.1109926276249907</v>
       </c>
       <c r="C52">
-        <v>253.6810566322892</v>
+        <v>244.8047113360136</v>
       </c>
       <c r="D52">
-        <v>480.6810566322891</v>
+        <v>479.0107113360136</v>
       </c>
       <c r="E52">
-        <v>-11.80000000000001</v>
+        <v>-4.593999999999994</v>
       </c>
       <c r="F52">
-        <v>360.3</v>
+        <v>367.506</v>
       </c>
       <c r="G52">
         <v>133.3</v>
@@ -5551,28 +5551,28 @@
         <v>50.425</v>
       </c>
       <c r="M52">
-        <v>32.427</v>
+        <v>33.07554</v>
       </c>
       <c r="N52">
-        <v>17.998</v>
+        <v>17.34945999999999</v>
       </c>
       <c r="O52">
-        <v>2.6997</v>
+        <v>2.602418999999999</v>
       </c>
       <c r="P52">
-        <v>15.2983</v>
+        <v>14.74704099999999</v>
       </c>
       <c r="Q52">
-        <v>22.9983</v>
+        <v>22.447041</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1450321722861211</v>
+        <v>0.1468931176020218</v>
       </c>
       <c r="T52">
-        <v>1.882397639711483</v>
+        <v>1.917699084692283</v>
       </c>
       <c r="U52">
         <v>0.09</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>1.555031301076264</v>
+        <v>1.524540491251239</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1109926276249907</v>
+        <v>0.137627265933459</v>
       </c>
       <c r="C53">
-        <v>244.8047113360136</v>
+        <v>98.660925128136</v>
       </c>
       <c r="D53">
-        <v>479.0107113360136</v>
+        <v>340.072925128136</v>
       </c>
       <c r="E53">
-        <v>-4.593999999999994</v>
+        <v>2.612000000000023</v>
       </c>
       <c r="F53">
-        <v>367.506</v>
+        <v>374.712</v>
       </c>
       <c r="G53">
         <v>133.3</v>
@@ -5633,45 +5633,45 @@
         <v>50.425</v>
       </c>
       <c r="M53">
-        <v>33.07554</v>
+        <v>55.00772160000001</v>
       </c>
       <c r="N53">
-        <v>17.34945999999999</v>
+        <v>-4.582721600000013</v>
       </c>
       <c r="O53">
-        <v>2.602418999999999</v>
+        <v>-0.687408240000002</v>
       </c>
       <c r="P53">
-        <v>14.74704099999999</v>
+        <v>-3.895313360000011</v>
       </c>
       <c r="Q53">
-        <v>22.447041</v>
+        <v>3.804686639999991</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1468931176020218</v>
+        <v>0.1495577650327579</v>
       </c>
       <c r="T53">
-        <v>1.917699084692283</v>
+        <v>1.968246461805204</v>
       </c>
       <c r="U53">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.15</v>
+        <v>0.1375034227921921</v>
       </c>
       <c r="W53">
-        <v>0.0765</v>
+        <v>0.1266144975341062</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y53">
-        <v>1.524540491251239</v>
+        <v>0.9166894852812807</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.137627265933459</v>
+        <v>0.138637265933459</v>
       </c>
       <c r="C54">
-        <v>98.660925128136</v>
+        <v>87.75518611788112</v>
       </c>
       <c r="D54">
-        <v>340.072925128136</v>
+        <v>336.3731861178811</v>
       </c>
       <c r="E54">
-        <v>2.612000000000023</v>
+        <v>9.817999999999984</v>
       </c>
       <c r="F54">
-        <v>374.712</v>
+        <v>381.918</v>
       </c>
       <c r="G54">
         <v>133.3</v>
@@ -5715,37 +5715,37 @@
         <v>50.425</v>
       </c>
       <c r="M54">
-        <v>55.00772160000001</v>
+        <v>56.0655624</v>
       </c>
       <c r="N54">
-        <v>-4.582721600000013</v>
+        <v>-5.640562400000007</v>
       </c>
       <c r="O54">
-        <v>-0.687408240000002</v>
+        <v>-0.8460843600000011</v>
       </c>
       <c r="P54">
-        <v>-3.895313360000011</v>
+        <v>-4.794478040000007</v>
       </c>
       <c r="Q54">
-        <v>3.804686639999991</v>
+        <v>2.905521959999996</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1495577650327579</v>
+        <v>0.1517653770547315</v>
       </c>
       <c r="T54">
-        <v>1.968246461805204</v>
+        <v>2.010124046098932</v>
       </c>
       <c r="U54">
         <v>0.1468</v>
       </c>
       <c r="V54">
-        <v>0.1375034227921921</v>
+        <v>0.1349090185885659</v>
       </c>
       <c r="W54">
-        <v>0.1266144975341062</v>
+        <v>0.1269953560711986</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.9166894852812807</v>
+        <v>0.8993934572571057</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.138637265933459</v>
+        <v>0.1396472659334591</v>
       </c>
       <c r="C55">
-        <v>87.75518611788112</v>
+        <v>76.92908152985888</v>
       </c>
       <c r="D55">
-        <v>336.3731861178811</v>
+        <v>332.7530815298589</v>
       </c>
       <c r="E55">
-        <v>9.817999999999984</v>
+        <v>17.024</v>
       </c>
       <c r="F55">
-        <v>381.918</v>
+        <v>389.124</v>
       </c>
       <c r="G55">
         <v>133.3</v>
@@ -5797,37 +5797,37 @@
         <v>50.425</v>
       </c>
       <c r="M55">
-        <v>56.0655624</v>
+        <v>57.12340320000001</v>
       </c>
       <c r="N55">
-        <v>-5.640562400000007</v>
+        <v>-6.698403200000008</v>
       </c>
       <c r="O55">
-        <v>-0.8460843600000011</v>
+        <v>-1.004760480000001</v>
       </c>
       <c r="P55">
-        <v>-4.794478040000007</v>
+        <v>-5.693642720000007</v>
       </c>
       <c r="Q55">
-        <v>2.905521959999996</v>
+        <v>2.006357279999996</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1517653770547315</v>
+        <v>0.1540689722080953</v>
       </c>
       <c r="T55">
-        <v>2.010124046098932</v>
+        <v>2.05382239492717</v>
       </c>
       <c r="U55">
         <v>0.1468</v>
       </c>
       <c r="V55">
-        <v>0.1349090185885659</v>
+        <v>0.1324107034295183</v>
       </c>
       <c r="W55">
-        <v>0.1269953560711986</v>
+        <v>0.1273621087365467</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.8993934572571057</v>
+        <v>0.8827380228634556</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1396472659334591</v>
+        <v>0.1406572659334591</v>
       </c>
       <c r="C56">
-        <v>76.92908152985888</v>
+        <v>66.18006762324973</v>
       </c>
       <c r="D56">
-        <v>332.7530815298589</v>
+        <v>329.2100676232498</v>
       </c>
       <c r="E56">
-        <v>17.024</v>
+        <v>24.23000000000002</v>
       </c>
       <c r="F56">
-        <v>389.124</v>
+        <v>396.33</v>
       </c>
       <c r="G56">
         <v>133.3</v>
@@ -5879,37 +5879,37 @@
         <v>50.425</v>
       </c>
       <c r="M56">
-        <v>57.12340320000001</v>
+        <v>58.18124400000001</v>
       </c>
       <c r="N56">
-        <v>-6.698403200000008</v>
+        <v>-7.756244000000017</v>
       </c>
       <c r="O56">
-        <v>-1.004760480000001</v>
+        <v>-1.163436600000002</v>
       </c>
       <c r="P56">
-        <v>-5.693642720000007</v>
+        <v>-6.592807400000014</v>
       </c>
       <c r="Q56">
-        <v>2.006357279999996</v>
+        <v>1.107192599999989</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1540689722080953</v>
+        <v>0.1564749493682752</v>
       </c>
       <c r="T56">
-        <v>2.05382239492717</v>
+        <v>2.099462892592218</v>
       </c>
       <c r="U56">
         <v>0.1468</v>
       </c>
       <c r="V56">
-        <v>0.1324107034295183</v>
+        <v>0.1300032360944362</v>
       </c>
       <c r="W56">
-        <v>0.1273621087365467</v>
+        <v>0.1277155249413368</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.8827380228634556</v>
+        <v>0.8666882406295744</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1406572659334591</v>
+        <v>0.141667265933459</v>
       </c>
       <c r="C57">
-        <v>66.18006762324973</v>
+        <v>55.50570785454346</v>
       </c>
       <c r="D57">
-        <v>329.2100676232498</v>
+        <v>325.7417078545435</v>
       </c>
       <c r="E57">
-        <v>24.23000000000002</v>
+        <v>31.43600000000004</v>
       </c>
       <c r="F57">
-        <v>396.33</v>
+        <v>403.5360000000001</v>
       </c>
       <c r="G57">
         <v>133.3</v>
@@ -5961,37 +5961,37 @@
         <v>50.425</v>
       </c>
       <c r="M57">
-        <v>58.18124400000001</v>
+        <v>59.23908480000001</v>
       </c>
       <c r="N57">
-        <v>-7.756244000000017</v>
+        <v>-8.814084800000018</v>
       </c>
       <c r="O57">
-        <v>-1.163436600000002</v>
+        <v>-1.322112720000003</v>
       </c>
       <c r="P57">
-        <v>-6.592807400000014</v>
+        <v>-7.491972080000015</v>
       </c>
       <c r="Q57">
-        <v>1.107192599999989</v>
+        <v>0.2080279199999877</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1564749493682752</v>
+        <v>0.158990289126645</v>
       </c>
       <c r="T57">
-        <v>2.099462892592218</v>
+        <v>2.14717795833295</v>
       </c>
       <c r="U57">
         <v>0.1468</v>
       </c>
       <c r="V57">
-        <v>0.1300032360944362</v>
+        <v>0.1276817497356069</v>
       </c>
       <c r="W57">
-        <v>0.1277155249413368</v>
+        <v>0.1280563191388129</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.8666882406295744</v>
+        <v>0.8512116649040463</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.141667265933459</v>
+        <v>0.142677265933459</v>
       </c>
       <c r="C58">
-        <v>55.50570785454346</v>
+        <v>44.90366728957679</v>
       </c>
       <c r="D58">
-        <v>325.7417078545435</v>
+        <v>322.3456672895769</v>
       </c>
       <c r="E58">
-        <v>31.43600000000004</v>
+        <v>38.64200000000005</v>
       </c>
       <c r="F58">
-        <v>403.5360000000001</v>
+        <v>410.7420000000001</v>
       </c>
       <c r="G58">
         <v>133.3</v>
@@ -6043,37 +6043,37 @@
         <v>50.425</v>
       </c>
       <c r="M58">
-        <v>59.23908480000001</v>
+        <v>60.29692560000002</v>
       </c>
       <c r="N58">
-        <v>-8.814084800000018</v>
+        <v>-9.871925600000019</v>
       </c>
       <c r="O58">
-        <v>-1.322112720000003</v>
+        <v>-1.480788840000003</v>
       </c>
       <c r="P58">
-        <v>-7.491972080000015</v>
+        <v>-8.391136760000016</v>
       </c>
       <c r="Q58">
-        <v>0.2080279199999877</v>
+        <v>-0.6911367600000133</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.158990289126645</v>
+        <v>0.1616226214319159</v>
       </c>
       <c r="T58">
-        <v>2.14717795833295</v>
+        <v>2.197112329456972</v>
       </c>
       <c r="U58">
         <v>0.1468</v>
       </c>
       <c r="V58">
-        <v>0.1276817497356069</v>
+        <v>0.1254417190384911</v>
       </c>
       <c r="W58">
-        <v>0.1280563191388129</v>
+        <v>0.1283851556451495</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.8512116649040463</v>
+        <v>0.8362781269232735</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.142677265933459</v>
+        <v>0.143687265933459</v>
       </c>
       <c r="C59">
-        <v>44.90366728957679</v>
+        <v>34.37170736151234</v>
       </c>
       <c r="D59">
-        <v>322.3456672895769</v>
+        <v>319.0197073615124</v>
       </c>
       <c r="E59">
-        <v>38.64200000000005</v>
+        <v>45.84800000000007</v>
       </c>
       <c r="F59">
-        <v>410.7420000000001</v>
+        <v>417.9480000000001</v>
       </c>
       <c r="G59">
         <v>133.3</v>
@@ -6125,37 +6125,37 @@
         <v>50.425</v>
       </c>
       <c r="M59">
-        <v>60.29692560000002</v>
+        <v>61.35476640000002</v>
       </c>
       <c r="N59">
-        <v>-9.871925600000019</v>
+        <v>-10.92976640000002</v>
       </c>
       <c r="O59">
-        <v>-1.480788840000003</v>
+        <v>-1.639464960000003</v>
       </c>
       <c r="P59">
-        <v>-8.391136760000016</v>
+        <v>-9.290301440000016</v>
       </c>
       <c r="Q59">
-        <v>-0.6911367600000133</v>
+        <v>-1.590301440000013</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1616226214319159</v>
+        <v>0.1643803028945805</v>
       </c>
       <c r="T59">
-        <v>2.197112329456972</v>
+        <v>2.249424527777376</v>
       </c>
       <c r="U59">
         <v>0.1468</v>
       </c>
       <c r="V59">
-        <v>0.1254417190384911</v>
+        <v>0.1232789307792067</v>
       </c>
       <c r="W59">
-        <v>0.1283851556451495</v>
+        <v>0.1287026529616125</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.8362781269232735</v>
+        <v>0.8218595385280447</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.143687265933459</v>
+        <v>0.144697265933459</v>
       </c>
       <c r="C60">
-        <v>34.37170736151245</v>
+        <v>23.90768095002483</v>
       </c>
       <c r="D60">
-        <v>319.0197073615124</v>
+        <v>315.7616809500248</v>
       </c>
       <c r="E60">
-        <v>45.84799999999996</v>
+        <v>53.05399999999997</v>
       </c>
       <c r="F60">
-        <v>417.948</v>
+        <v>425.154</v>
       </c>
       <c r="G60">
         <v>133.3</v>
@@ -6207,37 +6207,37 @@
         <v>50.425</v>
       </c>
       <c r="M60">
-        <v>61.3547664</v>
+        <v>62.4126072</v>
       </c>
       <c r="N60">
-        <v>-10.92976640000001</v>
+        <v>-11.98760720000001</v>
       </c>
       <c r="O60">
-        <v>-1.639464960000001</v>
+        <v>-1.798141080000001</v>
       </c>
       <c r="P60">
-        <v>-9.290301440000004</v>
+        <v>-10.18946612000001</v>
       </c>
       <c r="Q60">
-        <v>-1.590301440000001</v>
+        <v>-2.489466120000003</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1643803028945805</v>
+        <v>0.1672725054042044</v>
       </c>
       <c r="T60">
-        <v>2.249424527777375</v>
+        <v>2.304288540649995</v>
       </c>
       <c r="U60">
         <v>0.1468</v>
       </c>
       <c r="V60">
-        <v>0.1232789307792067</v>
+        <v>0.1211894573761693</v>
       </c>
       <c r="W60">
-        <v>0.1287026529616125</v>
+        <v>0.1290093876571783</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.8218595385280449</v>
+        <v>0.8079297158411289</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.144697265933459</v>
+        <v>0.1791386672325861</v>
       </c>
       <c r="C61">
-        <v>23.90768095002483</v>
+        <v>-64.85961701552861</v>
       </c>
       <c r="D61">
-        <v>315.7616809500248</v>
+        <v>234.2003829844714</v>
       </c>
       <c r="E61">
-        <v>53.05399999999997</v>
+        <v>60.25999999999999</v>
       </c>
       <c r="F61">
-        <v>425.154</v>
+        <v>432.36</v>
       </c>
       <c r="G61">
         <v>133.3</v>
@@ -6289,45 +6289,45 @@
         <v>50.425</v>
       </c>
       <c r="M61">
-        <v>62.4126072</v>
+        <v>86.81788800000001</v>
       </c>
       <c r="N61">
-        <v>-11.98760720000001</v>
+        <v>-36.39288800000001</v>
       </c>
       <c r="O61">
-        <v>-1.798141080000001</v>
+        <v>-5.458933200000001</v>
       </c>
       <c r="P61">
-        <v>-10.18946612000001</v>
+        <v>-30.93395480000001</v>
       </c>
       <c r="Q61">
-        <v>-2.489466120000003</v>
+        <v>-23.23395480000001</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1672725054042044</v>
+        <v>0.1728878212871272</v>
       </c>
       <c r="T61">
-        <v>2.304288540649995</v>
+        <v>2.410809007961449</v>
       </c>
       <c r="U61">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1211894573761693</v>
+        <v>0.08712202259515917</v>
       </c>
       <c r="W61">
-        <v>0.1290093876571783</v>
+        <v>0.183305897862892</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.8079297158411289</v>
+        <v>0.5808134839677279</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1791386672325861</v>
+        <v>0.1806886672325861</v>
       </c>
       <c r="C62">
-        <v>-64.85961701552861</v>
+        <v>-74.75680376289273</v>
       </c>
       <c r="D62">
-        <v>234.2003829844714</v>
+        <v>231.5091962371073</v>
       </c>
       <c r="E62">
-        <v>60.25999999999999</v>
+        <v>67.46600000000001</v>
       </c>
       <c r="F62">
-        <v>432.36</v>
+        <v>439.566</v>
       </c>
       <c r="G62">
         <v>133.3</v>
@@ -6371,37 +6371,37 @@
         <v>50.425</v>
       </c>
       <c r="M62">
-        <v>86.81788800000001</v>
+        <v>88.26485280000001</v>
       </c>
       <c r="N62">
-        <v>-36.39288800000001</v>
+        <v>-37.83985280000002</v>
       </c>
       <c r="O62">
-        <v>-5.458933200000001</v>
+        <v>-5.675977920000002</v>
       </c>
       <c r="P62">
-        <v>-30.93395480000001</v>
+        <v>-32.16387488000002</v>
       </c>
       <c r="Q62">
-        <v>-23.23395480000001</v>
+        <v>-24.46387488000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1728878212871272</v>
+        <v>0.1761464833714126</v>
       </c>
       <c r="T62">
-        <v>2.410809007961449</v>
+        <v>2.472624623550204</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.08712202259515917</v>
+        <v>0.08569379271655</v>
       </c>
       <c r="W62">
-        <v>0.183305897862892</v>
+        <v>0.1835926864225168</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5808134839677279</v>
+        <v>0.5712919514436667</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1806886672325861</v>
+        <v>0.1822386672325861</v>
       </c>
       <c r="C63">
-        <v>-74.75680376289273</v>
+        <v>-84.59284450900907</v>
       </c>
       <c r="D63">
-        <v>231.5091962371073</v>
+        <v>228.8791554909909</v>
       </c>
       <c r="E63">
-        <v>67.46600000000001</v>
+        <v>74.67199999999997</v>
       </c>
       <c r="F63">
-        <v>439.566</v>
+        <v>446.772</v>
       </c>
       <c r="G63">
         <v>133.3</v>
@@ -6453,37 +6453,37 @@
         <v>50.425</v>
       </c>
       <c r="M63">
-        <v>88.26485280000001</v>
+        <v>89.7118176</v>
       </c>
       <c r="N63">
-        <v>-37.83985280000002</v>
+        <v>-39.28681760000001</v>
       </c>
       <c r="O63">
-        <v>-5.675977920000002</v>
+        <v>-5.893022640000001</v>
       </c>
       <c r="P63">
-        <v>-32.16387488000002</v>
+        <v>-33.39379496000001</v>
       </c>
       <c r="Q63">
-        <v>-24.46387488000001</v>
+        <v>-25.69379496000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1761464833714126</v>
+        <v>0.1795766539864497</v>
       </c>
       <c r="T63">
-        <v>2.472624623550204</v>
+        <v>2.537693692590998</v>
       </c>
       <c r="U63">
         <v>0.2008</v>
       </c>
       <c r="V63">
-        <v>0.08569379271655</v>
+        <v>0.08431163476950888</v>
       </c>
       <c r="W63">
-        <v>0.1835926864225168</v>
+        <v>0.1838702237382826</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.5712919514436667</v>
+        <v>0.5620775651300592</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1822386672325861</v>
+        <v>0.1837886672325861</v>
       </c>
       <c r="C64">
-        <v>-84.59284450900907</v>
+        <v>-94.36979977748103</v>
       </c>
       <c r="D64">
-        <v>228.8791554909909</v>
+        <v>226.308200222519</v>
       </c>
       <c r="E64">
-        <v>74.67199999999997</v>
+        <v>81.87799999999999</v>
       </c>
       <c r="F64">
-        <v>446.772</v>
+        <v>453.978</v>
       </c>
       <c r="G64">
         <v>133.3</v>
@@ -6535,37 +6535,37 @@
         <v>50.425</v>
       </c>
       <c r="M64">
-        <v>89.7118176</v>
+        <v>91.15878240000001</v>
       </c>
       <c r="N64">
-        <v>-39.28681760000001</v>
+        <v>-40.73378240000001</v>
       </c>
       <c r="O64">
-        <v>-5.893022640000001</v>
+        <v>-6.110067360000001</v>
       </c>
       <c r="P64">
-        <v>-33.39379496000001</v>
+        <v>-34.62371504000001</v>
       </c>
       <c r="Q64">
-        <v>-25.69379496000001</v>
+        <v>-26.92371504</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1795766539864497</v>
+        <v>0.1831922392293267</v>
       </c>
       <c r="T64">
-        <v>2.537693692590998</v>
+        <v>2.606280008606972</v>
       </c>
       <c r="U64">
         <v>0.2008</v>
       </c>
       <c r="V64">
-        <v>0.08431163476950888</v>
+        <v>0.08297335485253254</v>
       </c>
       <c r="W64">
-        <v>0.1838702237382826</v>
+        <v>0.1841389503456115</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.5620775651300592</v>
+        <v>0.5531556990168837</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1837886672325861</v>
+        <v>0.1853386672325861</v>
       </c>
       <c r="C65">
-        <v>-94.36979977748103</v>
+        <v>-104.089638538462</v>
       </c>
       <c r="D65">
-        <v>226.308200222519</v>
+        <v>223.794361461538</v>
       </c>
       <c r="E65">
-        <v>81.87799999999999</v>
+        <v>89.084</v>
       </c>
       <c r="F65">
-        <v>453.978</v>
+        <v>461.184</v>
       </c>
       <c r="G65">
         <v>133.3</v>
@@ -6617,37 +6617,37 @@
         <v>50.425</v>
       </c>
       <c r="M65">
-        <v>91.15878240000001</v>
+        <v>92.60574720000001</v>
       </c>
       <c r="N65">
-        <v>-40.73378240000001</v>
+        <v>-42.18074720000001</v>
       </c>
       <c r="O65">
-        <v>-6.110067360000001</v>
+        <v>-6.327112080000002</v>
       </c>
       <c r="P65">
-        <v>-34.62371504000001</v>
+        <v>-35.85363512000001</v>
       </c>
       <c r="Q65">
-        <v>-26.92371504</v>
+        <v>-28.15363512000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1831922392293267</v>
+        <v>0.1870086903190303</v>
       </c>
       <c r="T65">
-        <v>2.606280008606972</v>
+        <v>2.678676675512721</v>
       </c>
       <c r="U65">
         <v>0.2008</v>
       </c>
       <c r="V65">
-        <v>0.08297335485253254</v>
+        <v>0.08167689618296173</v>
       </c>
       <c r="W65">
-        <v>0.1841389503456115</v>
+        <v>0.1843992792464613</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.5531556990168837</v>
+        <v>0.5445126412197449</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1853386672325861</v>
+        <v>0.1868886672325861</v>
       </c>
       <c r="C66">
-        <v>-104.089638538462</v>
+        <v>-113.7542432376868</v>
       </c>
       <c r="D66">
-        <v>223.794361461538</v>
+        <v>221.3357567623133</v>
       </c>
       <c r="E66">
-        <v>89.084</v>
+        <v>96.29000000000002</v>
       </c>
       <c r="F66">
-        <v>461.184</v>
+        <v>468.39</v>
       </c>
       <c r="G66">
         <v>133.3</v>
@@ -6699,37 +6699,37 @@
         <v>50.425</v>
       </c>
       <c r="M66">
-        <v>92.60574720000001</v>
+        <v>94.05271200000001</v>
       </c>
       <c r="N66">
-        <v>-42.18074720000001</v>
+        <v>-43.62771200000002</v>
       </c>
       <c r="O66">
-        <v>-6.327112080000002</v>
+        <v>-6.544156800000002</v>
       </c>
       <c r="P66">
-        <v>-35.85363512000001</v>
+        <v>-37.08355520000001</v>
       </c>
       <c r="Q66">
-        <v>-28.15363512000001</v>
+        <v>-29.38355520000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1870086903190303</v>
+        <v>0.1910432243281454</v>
       </c>
       <c r="T66">
-        <v>2.678676675512721</v>
+        <v>2.755210294813084</v>
       </c>
       <c r="U66">
         <v>0.2008</v>
       </c>
       <c r="V66">
-        <v>0.08167689618296173</v>
+        <v>0.08042032854937771</v>
       </c>
       <c r="W66">
-        <v>0.1843992792464613</v>
+        <v>0.184651598027285</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.5445126412197449</v>
+        <v>0.536135523662518</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1868886672325861</v>
+        <v>0.1884386672325861</v>
       </c>
       <c r="C67">
-        <v>-113.7542432376868</v>
+        <v>-123.3654144976101</v>
       </c>
       <c r="D67">
-        <v>221.3357567623133</v>
+        <v>218.93058550239</v>
       </c>
       <c r="E67">
-        <v>96.29000000000002</v>
+        <v>103.496</v>
       </c>
       <c r="F67">
-        <v>468.39</v>
+        <v>475.5960000000001</v>
       </c>
       <c r="G67">
         <v>133.3</v>
@@ -6781,37 +6781,37 @@
         <v>50.425</v>
       </c>
       <c r="M67">
-        <v>94.05271200000001</v>
+        <v>95.49967680000002</v>
       </c>
       <c r="N67">
-        <v>-43.62771200000002</v>
+        <v>-45.07467680000002</v>
       </c>
       <c r="O67">
-        <v>-6.544156800000002</v>
+        <v>-6.761201520000003</v>
       </c>
       <c r="P67">
-        <v>-37.08355520000001</v>
+        <v>-38.31347528000002</v>
       </c>
       <c r="Q67">
-        <v>-29.38355520000001</v>
+        <v>-30.61347528000002</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1910432243281454</v>
+        <v>0.1953150838672085</v>
       </c>
       <c r="T67">
-        <v>2.755210294813084</v>
+        <v>2.836245891719352</v>
       </c>
       <c r="U67">
         <v>0.2008</v>
       </c>
       <c r="V67">
-        <v>0.08042032854937771</v>
+        <v>0.07920183872287198</v>
       </c>
       <c r="W67">
-        <v>0.184651598027285</v>
+        <v>0.1848962707844473</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.536135523662518</v>
+        <v>0.5280122581524798</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1884386672325861</v>
+        <v>0.1899886672325861</v>
       </c>
       <c r="C68">
-        <v>-123.3654144976101</v>
+        <v>-132.9248755153287</v>
       </c>
       <c r="D68">
-        <v>218.93058550239</v>
+        <v>216.5771244846713</v>
       </c>
       <c r="E68">
-        <v>103.496</v>
+        <v>110.702</v>
       </c>
       <c r="F68">
-        <v>475.5960000000001</v>
+        <v>482.802</v>
       </c>
       <c r="G68">
         <v>133.3</v>
@@ -6863,37 +6863,37 @@
         <v>50.425</v>
       </c>
       <c r="M68">
-        <v>95.49967680000002</v>
+        <v>96.94664160000001</v>
       </c>
       <c r="N68">
-        <v>-45.07467680000002</v>
+        <v>-46.52164160000001</v>
       </c>
       <c r="O68">
-        <v>-6.761201520000003</v>
+        <v>-6.978246240000002</v>
       </c>
       <c r="P68">
-        <v>-38.31347528000002</v>
+        <v>-39.54339536000001</v>
       </c>
       <c r="Q68">
-        <v>-30.61347528000002</v>
+        <v>-31.84339536</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1953150838672085</v>
+        <v>0.1998458439843966</v>
       </c>
       <c r="T68">
-        <v>2.836245891719352</v>
+        <v>2.922192736922968</v>
       </c>
       <c r="U68">
         <v>0.2008</v>
       </c>
       <c r="V68">
-        <v>0.07920183872287198</v>
+        <v>0.07801972172700822</v>
       </c>
       <c r="W68">
-        <v>0.1848962707844473</v>
+        <v>0.1851336398772168</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.5280122581524798</v>
+        <v>0.5201314781800548</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1899886672325861</v>
+        <v>0.1915386672325861</v>
       </c>
       <c r="C69">
-        <v>-132.9248755153287</v>
+        <v>-142.4342761798586</v>
       </c>
       <c r="D69">
-        <v>216.5771244846713</v>
+        <v>214.2737238201414</v>
       </c>
       <c r="E69">
-        <v>110.702</v>
+        <v>117.908</v>
       </c>
       <c r="F69">
-        <v>482.802</v>
+        <v>490.008</v>
       </c>
       <c r="G69">
         <v>133.3</v>
@@ -6945,37 +6945,37 @@
         <v>50.425</v>
       </c>
       <c r="M69">
-        <v>96.94664160000001</v>
+        <v>98.39360640000001</v>
       </c>
       <c r="N69">
-        <v>-46.52164160000001</v>
+        <v>-47.96860640000001</v>
       </c>
       <c r="O69">
-        <v>-6.978246240000002</v>
+        <v>-7.195290960000002</v>
       </c>
       <c r="P69">
-        <v>-39.54339536000001</v>
+        <v>-40.77331544000001</v>
       </c>
       <c r="Q69">
-        <v>-31.84339536</v>
+        <v>-33.07331544000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1998458439843966</v>
+        <v>0.204659776608909</v>
       </c>
       <c r="T69">
-        <v>2.922192736922968</v>
+        <v>3.013511259951811</v>
       </c>
       <c r="U69">
         <v>0.2008</v>
       </c>
       <c r="V69">
-        <v>0.07801972172700822</v>
+        <v>0.07687237287808163</v>
       </c>
       <c r="W69">
-        <v>0.1851336398772168</v>
+        <v>0.1853640275260812</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.5201314781800548</v>
+        <v>0.5124824858538775</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1915386672325861</v>
+        <v>0.1930886672325861</v>
       </c>
       <c r="C70">
-        <v>-142.4342761798586</v>
+        <v>-151.8951969294419</v>
       </c>
       <c r="D70">
-        <v>214.2737238201414</v>
+        <v>212.0188030705581</v>
       </c>
       <c r="E70">
-        <v>117.908</v>
+        <v>125.114</v>
       </c>
       <c r="F70">
-        <v>490.008</v>
+        <v>497.2140000000001</v>
       </c>
       <c r="G70">
         <v>133.3</v>
@@ -7027,37 +7027,37 @@
         <v>50.425</v>
       </c>
       <c r="M70">
-        <v>98.39360640000001</v>
+        <v>99.84057120000001</v>
       </c>
       <c r="N70">
-        <v>-47.96860640000001</v>
+        <v>-49.41557120000002</v>
       </c>
       <c r="O70">
-        <v>-7.195290960000002</v>
+        <v>-7.412335680000002</v>
       </c>
       <c r="P70">
-        <v>-40.77331544000001</v>
+        <v>-42.00323552000002</v>
       </c>
       <c r="Q70">
-        <v>-33.07331544000001</v>
+        <v>-34.30323552000002</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.204659776608909</v>
+        <v>0.2097842855317771</v>
       </c>
       <c r="T70">
-        <v>3.013511259951811</v>
+        <v>3.110721300595418</v>
       </c>
       <c r="U70">
         <v>0.2008</v>
       </c>
       <c r="V70">
-        <v>0.07687237287808163</v>
+        <v>0.07575828051752972</v>
       </c>
       <c r="W70">
-        <v>0.1853640275260812</v>
+        <v>0.18558773727208</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.5124824858538775</v>
+        <v>0.5050552034501981</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1930886672325861</v>
+        <v>0.21955485011473</v>
       </c>
       <c r="C71">
-        <v>-151.8951969294419</v>
+        <v>-191.3957107966145</v>
       </c>
       <c r="D71">
-        <v>212.0188030705581</v>
+        <v>179.7242892033856</v>
       </c>
       <c r="E71">
-        <v>125.114</v>
+        <v>132.3200000000001</v>
       </c>
       <c r="F71">
-        <v>497.2140000000001</v>
+        <v>504.4200000000001</v>
       </c>
       <c r="G71">
         <v>133.3</v>
@@ -7109,45 +7109,45 @@
         <v>50.425</v>
       </c>
       <c r="M71">
-        <v>99.84057120000001</v>
+        <v>118.942236</v>
       </c>
       <c r="N71">
-        <v>-49.41557120000002</v>
+        <v>-68.51723600000003</v>
       </c>
       <c r="O71">
-        <v>-7.412335680000002</v>
+        <v>-10.2775854</v>
       </c>
       <c r="P71">
-        <v>-42.00323552000002</v>
+        <v>-58.23965060000002</v>
       </c>
       <c r="Q71">
-        <v>-34.30323552000002</v>
+        <v>-50.53965060000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2097842855317771</v>
+        <v>0.2166377046566494</v>
       </c>
       <c r="T71">
-        <v>3.110721300595418</v>
+        <v>3.240728128899201</v>
       </c>
       <c r="U71">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.07575828051752972</v>
+        <v>0.06359179257400203</v>
       </c>
       <c r="W71">
-        <v>0.18558773727208</v>
+        <v>0.2208050553110503</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y71">
-        <v>0.5050552034501981</v>
+        <v>0.4239452838266803</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.21955485011473</v>
+        <v>0.2214548501147301</v>
       </c>
       <c r="C72">
-        <v>-191.3957107966145</v>
+        <v>-200.5457285636355</v>
       </c>
       <c r="D72">
-        <v>179.7242892033856</v>
+        <v>177.7802714363646</v>
       </c>
       <c r="E72">
-        <v>132.3200000000001</v>
+        <v>139.5260000000001</v>
       </c>
       <c r="F72">
-        <v>504.4200000000001</v>
+        <v>511.6260000000001</v>
       </c>
       <c r="G72">
         <v>133.3</v>
@@ -7191,37 +7191,37 @@
         <v>50.425</v>
       </c>
       <c r="M72">
-        <v>118.942236</v>
+        <v>120.6414108</v>
       </c>
       <c r="N72">
-        <v>-68.51723600000003</v>
+        <v>-70.21641080000003</v>
       </c>
       <c r="O72">
-        <v>-10.2775854</v>
+        <v>-10.53246162</v>
       </c>
       <c r="P72">
-        <v>-58.23965060000002</v>
+        <v>-59.68394918000003</v>
       </c>
       <c r="Q72">
-        <v>-50.53965060000002</v>
+        <v>-51.98394918000002</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2166377046566494</v>
+        <v>0.2225286599896373</v>
       </c>
       <c r="T72">
-        <v>3.240728128899201</v>
+        <v>3.352477374723312</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.06359179257400203</v>
+        <v>0.06269613352366397</v>
       </c>
       <c r="W72">
-        <v>0.2208050553110503</v>
+        <v>0.22101625171512</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.4239452838266803</v>
+        <v>0.4179742234910931</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.22145485011473</v>
+        <v>0.2233548501147301</v>
       </c>
       <c r="C73">
-        <v>-200.5457285636354</v>
+        <v>-209.6541407788513</v>
       </c>
       <c r="D73">
-        <v>177.7802714363646</v>
+        <v>175.8778592211486</v>
       </c>
       <c r="E73">
-        <v>139.526</v>
+        <v>146.732</v>
       </c>
       <c r="F73">
-        <v>511.626</v>
+        <v>518.832</v>
       </c>
       <c r="G73">
         <v>133.3</v>
@@ -7273,37 +7273,37 @@
         <v>50.425</v>
       </c>
       <c r="M73">
-        <v>120.6414108</v>
+        <v>122.3405856</v>
       </c>
       <c r="N73">
-        <v>-70.21641080000001</v>
+        <v>-71.9155856</v>
       </c>
       <c r="O73">
-        <v>-10.53246162</v>
+        <v>-10.78733784</v>
       </c>
       <c r="P73">
-        <v>-59.68394918000001</v>
+        <v>-61.12824776</v>
       </c>
       <c r="Q73">
-        <v>-51.98394918</v>
+        <v>-53.42824776</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2225286599896373</v>
+        <v>0.22884039784641</v>
       </c>
       <c r="T73">
-        <v>3.352477374723311</v>
+        <v>3.472208709534857</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.06269613352366399</v>
+        <v>0.06182535389139088</v>
       </c>
       <c r="W73">
-        <v>0.22101625171512</v>
+        <v>0.22122158155241</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.4179742234910933</v>
+        <v>0.4121690259426058</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2233548501147301</v>
+        <v>0.22525485011473</v>
       </c>
       <c r="C74">
-        <v>-209.6541407788513</v>
+        <v>-218.7222689537462</v>
       </c>
       <c r="D74">
-        <v>175.8778592211486</v>
+        <v>174.0157310462538</v>
       </c>
       <c r="E74">
-        <v>146.732</v>
+        <v>153.938</v>
       </c>
       <c r="F74">
-        <v>518.832</v>
+        <v>526.038</v>
       </c>
       <c r="G74">
         <v>133.3</v>
@@ -7355,37 +7355,37 @@
         <v>50.425</v>
       </c>
       <c r="M74">
-        <v>122.3405856</v>
+        <v>124.0397604</v>
       </c>
       <c r="N74">
-        <v>-71.9155856</v>
+        <v>-73.61476040000001</v>
       </c>
       <c r="O74">
-        <v>-10.78733784</v>
+        <v>-11.04221406</v>
       </c>
       <c r="P74">
-        <v>-61.12824776</v>
+        <v>-62.57254634000001</v>
       </c>
       <c r="Q74">
-        <v>-53.42824776</v>
+        <v>-54.87254634000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.22884039784641</v>
+        <v>0.2356196718407215</v>
       </c>
       <c r="T74">
-        <v>3.472208709534857</v>
+        <v>3.600809032110222</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.06182535389139088</v>
+        <v>0.06097843123534443</v>
       </c>
       <c r="W74">
-        <v>0.22122158155241</v>
+        <v>0.2214212859147058</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.4121690259426058</v>
+        <v>0.4065228749022962</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.22525485011473</v>
+        <v>0.22715485011473</v>
       </c>
       <c r="C75">
-        <v>-218.7222689537462</v>
+        <v>-227.7513792194972</v>
       </c>
       <c r="D75">
-        <v>174.0157310462538</v>
+        <v>172.1926207805028</v>
       </c>
       <c r="E75">
-        <v>153.938</v>
+        <v>161.144</v>
       </c>
       <c r="F75">
-        <v>526.038</v>
+        <v>533.244</v>
       </c>
       <c r="G75">
         <v>133.3</v>
@@ -7437,37 +7437,37 @@
         <v>50.425</v>
       </c>
       <c r="M75">
-        <v>124.0397604</v>
+        <v>125.7389352</v>
       </c>
       <c r="N75">
-        <v>-73.61476040000001</v>
+        <v>-75.31393520000002</v>
       </c>
       <c r="O75">
-        <v>-11.04221406</v>
+        <v>-11.29709028</v>
       </c>
       <c r="P75">
-        <v>-62.57254634000001</v>
+        <v>-64.01684492000001</v>
       </c>
       <c r="Q75">
-        <v>-54.87254634000001</v>
+        <v>-56.31684492000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2356196718407215</v>
+        <v>0.24292042844998</v>
       </c>
       <c r="T75">
-        <v>3.600809032110222</v>
+        <v>3.739301687191385</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.06097843123534443</v>
+        <v>0.06015439838081274</v>
       </c>
       <c r="W75">
-        <v>0.2214212859147058</v>
+        <v>0.2216155928618044</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.4065228749022962</v>
+        <v>0.4010293225387517</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.22715485011473</v>
+        <v>0.22905485011473</v>
       </c>
       <c r="C76">
-        <v>-227.7513792194972</v>
+        <v>-236.7426851979099</v>
       </c>
       <c r="D76">
-        <v>172.1926207805028</v>
+        <v>170.4073148020902</v>
       </c>
       <c r="E76">
-        <v>161.144</v>
+        <v>168.35</v>
       </c>
       <c r="F76">
-        <v>533.244</v>
+        <v>540.45</v>
       </c>
       <c r="G76">
         <v>133.3</v>
@@ -7519,37 +7519,37 @@
         <v>50.425</v>
       </c>
       <c r="M76">
-        <v>125.7389352</v>
+        <v>127.43811</v>
       </c>
       <c r="N76">
-        <v>-75.31393520000002</v>
+        <v>-77.01311000000001</v>
       </c>
       <c r="O76">
-        <v>-11.29709028</v>
+        <v>-11.5519665</v>
       </c>
       <c r="P76">
-        <v>-64.01684492000001</v>
+        <v>-65.46114350000001</v>
       </c>
       <c r="Q76">
-        <v>-56.31684492000001</v>
+        <v>-57.7611435</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.24292042844998</v>
+        <v>0.2508052455879792</v>
       </c>
       <c r="T76">
-        <v>3.739301687191385</v>
+        <v>3.88887375467904</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.06015439838081274</v>
+        <v>0.05935233973573524</v>
       </c>
       <c r="W76">
-        <v>0.2216155928618044</v>
+        <v>0.2218047182903136</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.4010293225387517</v>
+        <v>0.3956822649049017</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.22905485011473</v>
+        <v>0.23095485011473</v>
       </c>
       <c r="C77">
-        <v>-236.7426851979099</v>
+        <v>-245.6973506955912</v>
       </c>
       <c r="D77">
-        <v>170.4073148020902</v>
+        <v>168.6586493044089</v>
       </c>
       <c r="E77">
-        <v>168.35</v>
+        <v>175.556</v>
       </c>
       <c r="F77">
-        <v>540.45</v>
+        <v>547.6560000000001</v>
       </c>
       <c r="G77">
         <v>133.3</v>
@@ -7601,37 +7601,37 @@
         <v>50.425</v>
       </c>
       <c r="M77">
-        <v>127.43811</v>
+        <v>129.1372848</v>
       </c>
       <c r="N77">
-        <v>-77.01311000000001</v>
+        <v>-78.71228480000003</v>
       </c>
       <c r="O77">
-        <v>-11.5519665</v>
+        <v>-11.80684272</v>
       </c>
       <c r="P77">
-        <v>-65.46114350000001</v>
+        <v>-66.90544208000003</v>
       </c>
       <c r="Q77">
-        <v>-57.7611435</v>
+        <v>-59.20544208000003</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2508052455879792</v>
+        <v>0.2593471308208117</v>
       </c>
       <c r="T77">
-        <v>3.88887375467904</v>
+        <v>4.050910161124001</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.05935233973573524</v>
+        <v>0.05857138789710713</v>
       </c>
       <c r="W77">
-        <v>0.2218047182903136</v>
+        <v>0.2219888667338621</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3956822649049017</v>
+        <v>0.3904759193140476</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.23095485011473</v>
+        <v>0.23285485011473</v>
       </c>
       <c r="C78">
-        <v>-245.6973506955912</v>
+        <v>-254.6164922339252</v>
       </c>
       <c r="D78">
-        <v>168.6586493044089</v>
+        <v>166.9455077660749</v>
       </c>
       <c r="E78">
-        <v>175.556</v>
+        <v>182.7620000000001</v>
       </c>
       <c r="F78">
-        <v>547.6560000000001</v>
+        <v>554.8620000000001</v>
       </c>
       <c r="G78">
         <v>133.3</v>
@@ -7683,37 +7683,37 @@
         <v>50.425</v>
       </c>
       <c r="M78">
-        <v>129.1372848</v>
+        <v>130.8364596</v>
       </c>
       <c r="N78">
-        <v>-78.71228480000003</v>
+        <v>-80.41145960000001</v>
       </c>
       <c r="O78">
-        <v>-11.80684272</v>
+        <v>-12.06171894</v>
       </c>
       <c r="P78">
-        <v>-66.90544208000003</v>
+        <v>-68.34974066000001</v>
       </c>
       <c r="Q78">
-        <v>-59.20544208000003</v>
+        <v>-60.64974066000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2593471308208117</v>
+        <v>0.2686317886825861</v>
       </c>
       <c r="T78">
-        <v>4.050910161124001</v>
+        <v>4.227036689868522</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.05857138789710713</v>
+        <v>0.05781072052182004</v>
       </c>
       <c r="W78">
-        <v>0.2219888667338621</v>
+        <v>0.2221682321009548</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3904759193140476</v>
+        <v>0.3854048034788002</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.23285485011473</v>
+        <v>0.23475485011473</v>
       </c>
       <c r="C79">
-        <v>-254.6164922339252</v>
+        <v>-263.5011814264118</v>
       </c>
       <c r="D79">
-        <v>166.9455077660749</v>
+        <v>165.2668185735882</v>
       </c>
       <c r="E79">
-        <v>182.7620000000001</v>
+        <v>189.968</v>
       </c>
       <c r="F79">
-        <v>554.8620000000001</v>
+        <v>562.068</v>
       </c>
       <c r="G79">
         <v>133.3</v>
@@ -7765,37 +7765,37 @@
         <v>50.425</v>
       </c>
       <c r="M79">
-        <v>130.8364596</v>
+        <v>132.5356344</v>
       </c>
       <c r="N79">
-        <v>-80.41145960000001</v>
+        <v>-82.1106344</v>
       </c>
       <c r="O79">
-        <v>-12.06171894</v>
+        <v>-12.31659516</v>
       </c>
       <c r="P79">
-        <v>-68.34974066000001</v>
+        <v>-69.79403923999999</v>
       </c>
       <c r="Q79">
-        <v>-60.64974066000001</v>
+        <v>-62.09403923999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2686317886825861</v>
+        <v>0.2787605063499765</v>
       </c>
       <c r="T79">
-        <v>4.227036689868522</v>
+        <v>4.419174721226184</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.05781072052182004</v>
+        <v>0.05706955743820697</v>
       </c>
       <c r="W79">
-        <v>0.2221682321009548</v>
+        <v>0.2223429983560708</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3854048034788002</v>
+        <v>0.3804637162547132</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.23475485011473</v>
+        <v>0.23665485011473</v>
       </c>
       <c r="C80">
-        <v>-263.5011814264118</v>
+        <v>-272.352447214004</v>
       </c>
       <c r="D80">
-        <v>165.2668185735882</v>
+        <v>163.621552785996</v>
       </c>
       <c r="E80">
-        <v>189.968</v>
+        <v>197.174</v>
       </c>
       <c r="F80">
-        <v>562.068</v>
+        <v>569.274</v>
       </c>
       <c r="G80">
         <v>133.3</v>
@@ -7847,37 +7847,37 @@
         <v>50.425</v>
       </c>
       <c r="M80">
-        <v>132.5356344</v>
+        <v>134.2348092</v>
       </c>
       <c r="N80">
-        <v>-82.1106344</v>
+        <v>-83.8098092</v>
       </c>
       <c r="O80">
-        <v>-12.31659516</v>
+        <v>-12.57147138</v>
       </c>
       <c r="P80">
-        <v>-69.79403923999999</v>
+        <v>-71.23833782</v>
       </c>
       <c r="Q80">
-        <v>-62.09403923999999</v>
+        <v>-63.53833782</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2787605063499765</v>
+        <v>0.2898538637952134</v>
       </c>
       <c r="T80">
-        <v>4.419174721226184</v>
+        <v>4.629611612713144</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.05706955743820697</v>
+        <v>0.05634715797696385</v>
       </c>
       <c r="W80">
-        <v>0.2223429983560708</v>
+        <v>0.2225133401490319</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3804637162547132</v>
+        <v>0.3756477198464256</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.23665485011473</v>
+        <v>0.2385548501147301</v>
       </c>
       <c r="C81">
-        <v>-272.352447214004</v>
+        <v>-281.1712779682412</v>
       </c>
       <c r="D81">
-        <v>163.621552785996</v>
+        <v>162.0087220317589</v>
       </c>
       <c r="E81">
-        <v>197.174</v>
+        <v>204.38</v>
       </c>
       <c r="F81">
-        <v>569.274</v>
+        <v>576.48</v>
       </c>
       <c r="G81">
         <v>133.3</v>
@@ -7929,37 +7929,37 @@
         <v>50.425</v>
       </c>
       <c r="M81">
-        <v>134.2348092</v>
+        <v>135.933984</v>
       </c>
       <c r="N81">
-        <v>-83.8098092</v>
+        <v>-85.50898400000001</v>
       </c>
       <c r="O81">
-        <v>-12.57147138</v>
+        <v>-12.8263476</v>
       </c>
       <c r="P81">
-        <v>-71.23833782</v>
+        <v>-72.68263640000001</v>
       </c>
       <c r="Q81">
-        <v>-63.53833782</v>
+        <v>-64.9826364</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2898538637952134</v>
+        <v>0.3020565569849741</v>
       </c>
       <c r="T81">
-        <v>4.629611612713144</v>
+        <v>4.861092193348802</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.05634715797696385</v>
+        <v>0.05564281850225179</v>
       </c>
       <c r="W81">
-        <v>0.2225133401490319</v>
+        <v>0.222679423397169</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3756477198464256</v>
+        <v>0.3709521233483453</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2385548501147301</v>
+        <v>0.2404548501147301</v>
       </c>
       <c r="C82">
-        <v>-281.1712779682412</v>
+        <v>-289.9586234712117</v>
       </c>
       <c r="D82">
-        <v>162.0087220317589</v>
+        <v>160.4273765287883</v>
       </c>
       <c r="E82">
-        <v>204.38</v>
+        <v>211.586</v>
       </c>
       <c r="F82">
-        <v>576.48</v>
+        <v>583.686</v>
       </c>
       <c r="G82">
         <v>133.3</v>
@@ -8011,37 +8011,37 @@
         <v>50.425</v>
       </c>
       <c r="M82">
-        <v>135.933984</v>
+        <v>137.6331588</v>
       </c>
       <c r="N82">
-        <v>-85.50898400000001</v>
+        <v>-87.20815880000002</v>
       </c>
       <c r="O82">
-        <v>-12.8263476</v>
+        <v>-13.08122382</v>
       </c>
       <c r="P82">
-        <v>-72.68263640000001</v>
+        <v>-74.12693498000002</v>
       </c>
       <c r="Q82">
-        <v>-64.9826364</v>
+        <v>-66.42693498000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3020565569849741</v>
+        <v>0.3155437441947095</v>
       </c>
       <c r="T82">
-        <v>4.861092193348802</v>
+        <v>5.116939150893475</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.05564281850225179</v>
+        <v>0.05495587012568078</v>
       </c>
       <c r="W82">
-        <v>0.222679423397169</v>
+        <v>0.2228414058243645</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3709521233483453</v>
+        <v>0.3663724675045386</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2404548501147301</v>
+        <v>0.2423548501147301</v>
       </c>
       <c r="C83">
-        <v>-289.9586234712117</v>
+        <v>-298.7153967806813</v>
       </c>
       <c r="D83">
-        <v>160.4273765287883</v>
+        <v>158.8766032193188</v>
       </c>
       <c r="E83">
-        <v>211.586</v>
+        <v>218.792</v>
       </c>
       <c r="F83">
-        <v>583.686</v>
+        <v>590.8920000000001</v>
       </c>
       <c r="G83">
         <v>133.3</v>
@@ -8093,37 +8093,37 @@
         <v>50.425</v>
       </c>
       <c r="M83">
-        <v>137.6331588</v>
+        <v>139.3323336</v>
       </c>
       <c r="N83">
-        <v>-87.20815880000002</v>
+        <v>-88.90733360000003</v>
       </c>
       <c r="O83">
-        <v>-13.08122382</v>
+        <v>-13.33610004</v>
       </c>
       <c r="P83">
-        <v>-74.12693498000002</v>
+        <v>-75.57123356000002</v>
       </c>
       <c r="Q83">
-        <v>-66.42693498000001</v>
+        <v>-67.87123356000002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3155437441947095</v>
+        <v>0.3305295077610824</v>
       </c>
       <c r="T83">
-        <v>5.116939150893475</v>
+        <v>5.401213548165336</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.05495587012568078</v>
+        <v>0.05428567658756272</v>
       </c>
       <c r="W83">
-        <v>0.2228414058243645</v>
+        <v>0.2229994374606527</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3663724675045386</v>
+        <v>0.3619045105837514</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2423548501147301</v>
+        <v>0.2442548501147301</v>
       </c>
       <c r="C84">
-        <v>-298.7153967806813</v>
+        <v>-307.4424759880788</v>
       </c>
       <c r="D84">
-        <v>158.8766032193188</v>
+        <v>157.3555240119213</v>
       </c>
       <c r="E84">
-        <v>218.792</v>
+        <v>225.998</v>
       </c>
       <c r="F84">
-        <v>590.8920000000001</v>
+        <v>598.0980000000001</v>
       </c>
       <c r="G84">
         <v>133.3</v>
@@ -8175,37 +8175,37 @@
         <v>50.425</v>
       </c>
       <c r="M84">
-        <v>139.3323336</v>
+        <v>141.0315084</v>
       </c>
       <c r="N84">
-        <v>-88.90733360000003</v>
+        <v>-90.60650840000004</v>
       </c>
       <c r="O84">
-        <v>-13.33610004</v>
+        <v>-13.59097626000001</v>
       </c>
       <c r="P84">
-        <v>-75.57123356000002</v>
+        <v>-77.01553214000003</v>
       </c>
       <c r="Q84">
-        <v>-67.87123356000002</v>
+        <v>-69.31553214000003</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3305295077610824</v>
+        <v>0.3472783023352637</v>
       </c>
       <c r="T84">
-        <v>5.401213548165336</v>
+        <v>5.718931992175062</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.05428567658756272</v>
+        <v>0.05363163229132702</v>
       </c>
       <c r="W84">
-        <v>0.2229994374606527</v>
+        <v>0.2231536611057051</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3619045105837514</v>
+        <v>0.3575442152755135</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2442548501147301</v>
+        <v>0.24615485011473</v>
       </c>
       <c r="C85">
-        <v>-307.4424759880788</v>
+        <v>-316.1407058764566</v>
       </c>
       <c r="D85">
-        <v>157.3555240119213</v>
+        <v>155.8632941235435</v>
       </c>
       <c r="E85">
-        <v>225.998</v>
+        <v>233.2040000000001</v>
       </c>
       <c r="F85">
-        <v>598.0980000000001</v>
+        <v>605.3040000000001</v>
       </c>
       <c r="G85">
         <v>133.3</v>
@@ -8257,37 +8257,37 @@
         <v>50.425</v>
       </c>
       <c r="M85">
-        <v>141.0315084</v>
+        <v>142.7306832</v>
       </c>
       <c r="N85">
-        <v>-90.60650840000004</v>
+        <v>-92.30568320000002</v>
       </c>
       <c r="O85">
-        <v>-13.59097626000001</v>
+        <v>-13.84585248</v>
       </c>
       <c r="P85">
-        <v>-77.01553214000003</v>
+        <v>-78.45983072000001</v>
       </c>
       <c r="Q85">
-        <v>-69.31553214000003</v>
+        <v>-70.75983072000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3472783023352637</v>
+        <v>0.3661206962312177</v>
       </c>
       <c r="T85">
-        <v>5.718931992175062</v>
+        <v>6.076365241686004</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.05363163229132702</v>
+        <v>0.05299316047833504</v>
       </c>
       <c r="W85">
-        <v>0.2231536611057051</v>
+        <v>0.2233042127592086</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3575442152755135</v>
+        <v>0.3532877365222336</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.24615485011473</v>
+        <v>0.24805485011473</v>
       </c>
       <c r="C86">
-        <v>-316.1407058764565</v>
+        <v>-324.8108994849991</v>
       </c>
       <c r="D86">
-        <v>155.8632941235435</v>
+        <v>154.3991005150009</v>
       </c>
       <c r="E86">
-        <v>233.204</v>
+        <v>240.41</v>
       </c>
       <c r="F86">
-        <v>605.304</v>
+        <v>612.51</v>
       </c>
       <c r="G86">
         <v>133.3</v>
@@ -8339,37 +8339,37 @@
         <v>50.425</v>
       </c>
       <c r="M86">
-        <v>142.7306832</v>
+        <v>144.429858</v>
       </c>
       <c r="N86">
-        <v>-92.30568319999999</v>
+        <v>-94.004858</v>
       </c>
       <c r="O86">
-        <v>-13.84585248</v>
+        <v>-14.1007287</v>
       </c>
       <c r="P86">
-        <v>-78.45983071999999</v>
+        <v>-79.90412929999999</v>
       </c>
       <c r="Q86">
-        <v>-70.75983071999998</v>
+        <v>-72.20412929999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3661206962312175</v>
+        <v>0.3874754093132987</v>
       </c>
       <c r="T86">
-        <v>6.076365241686</v>
+        <v>6.4814562577984</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.05299316047833505</v>
+        <v>0.0523697115315311</v>
       </c>
       <c r="W86">
-        <v>0.2233042127592086</v>
+        <v>0.223451222020865</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3532877365222337</v>
+        <v>0.3491314102102073</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.24805485011473</v>
+        <v>0.24995485011473</v>
       </c>
       <c r="C87">
-        <v>-324.8108994849991</v>
+        <v>-333.4538395861705</v>
       </c>
       <c r="D87">
-        <v>154.3991005150009</v>
+        <v>152.9621604138295</v>
       </c>
       <c r="E87">
-        <v>240.41</v>
+        <v>247.616</v>
       </c>
       <c r="F87">
-        <v>612.51</v>
+        <v>619.716</v>
       </c>
       <c r="G87">
         <v>133.3</v>
@@ -8421,37 +8421,37 @@
         <v>50.425</v>
       </c>
       <c r="M87">
-        <v>144.429858</v>
+        <v>146.1290328</v>
       </c>
       <c r="N87">
-        <v>-94.004858</v>
+        <v>-95.70403280000001</v>
       </c>
       <c r="O87">
-        <v>-14.1007287</v>
+        <v>-14.35560492</v>
       </c>
       <c r="P87">
-        <v>-79.90412929999999</v>
+        <v>-81.34842788</v>
       </c>
       <c r="Q87">
-        <v>-72.20412929999999</v>
+        <v>-73.64842788</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3874754093132987</v>
+        <v>0.41188079569282</v>
       </c>
       <c r="T87">
-        <v>6.4814562577984</v>
+        <v>6.944417419069715</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.0523697115315311</v>
+        <v>0.05176076139744353</v>
       </c>
       <c r="W87">
-        <v>0.223451222020865</v>
+        <v>0.2235948124624828</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3491314102102073</v>
+        <v>0.3450717426496235</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.24995485011473</v>
+        <v>0.25185485011473</v>
       </c>
       <c r="C88">
-        <v>-333.4538395861705</v>
+        <v>-342.0702800811381</v>
       </c>
       <c r="D88">
-        <v>152.9621604138295</v>
+        <v>151.5517199188619</v>
       </c>
       <c r="E88">
-        <v>247.616</v>
+        <v>254.822</v>
       </c>
       <c r="F88">
-        <v>619.716</v>
+        <v>626.922</v>
       </c>
       <c r="G88">
         <v>133.3</v>
@@ -8503,37 +8503,37 @@
         <v>50.425</v>
       </c>
       <c r="M88">
-        <v>146.1290328</v>
+        <v>147.8282076</v>
       </c>
       <c r="N88">
-        <v>-95.70403280000001</v>
+        <v>-97.40320760000002</v>
       </c>
       <c r="O88">
-        <v>-14.35560492</v>
+        <v>-14.61048114</v>
       </c>
       <c r="P88">
-        <v>-81.34842788</v>
+        <v>-82.79272646000001</v>
       </c>
       <c r="Q88">
-        <v>-73.64842788</v>
+        <v>-75.09272646000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.41188079569282</v>
+        <v>0.44004085689996</v>
       </c>
       <c r="T88">
-        <v>6.944417419069715</v>
+        <v>7.47860337438277</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05176076139744353</v>
+        <v>0.05116581011701314</v>
       </c>
       <c r="W88">
-        <v>0.2235948124624828</v>
+        <v>0.2237351019744083</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3450717426496235</v>
+        <v>0.3411054007800876</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.25185485011473</v>
+        <v>0.25375485011473</v>
       </c>
       <c r="C89">
-        <v>-342.0702800811381</v>
+        <v>-350.6609473186994</v>
       </c>
       <c r="D89">
-        <v>151.5517199188619</v>
+        <v>150.1670526813006</v>
       </c>
       <c r="E89">
-        <v>254.822</v>
+        <v>262.028</v>
       </c>
       <c r="F89">
-        <v>626.922</v>
+        <v>634.128</v>
       </c>
       <c r="G89">
         <v>133.3</v>
@@ -8585,37 +8585,37 @@
         <v>50.425</v>
       </c>
       <c r="M89">
-        <v>147.8282076</v>
+        <v>149.5273824</v>
       </c>
       <c r="N89">
-        <v>-97.40320760000002</v>
+        <v>-99.10238240000002</v>
       </c>
       <c r="O89">
-        <v>-14.61048114</v>
+        <v>-14.86535736</v>
       </c>
       <c r="P89">
-        <v>-82.79272646000001</v>
+        <v>-84.23702504000002</v>
       </c>
       <c r="Q89">
-        <v>-75.09272646000001</v>
+        <v>-76.53702504000002</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.44004085689996</v>
+        <v>0.4728942616416235</v>
       </c>
       <c r="T89">
-        <v>7.47860337438277</v>
+        <v>8.101820322248003</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.05116581011701314</v>
+        <v>0.05058438045659253</v>
       </c>
       <c r="W89">
-        <v>0.2237351019744083</v>
+        <v>0.2238722030883355</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.3411054007800876</v>
+        <v>0.3372292030439502</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.25375485011473</v>
+        <v>0.25565485011473</v>
       </c>
       <c r="C90">
-        <v>-350.6609473186994</v>
+        <v>-359.2265413425615</v>
       </c>
       <c r="D90">
-        <v>150.1670526813006</v>
+        <v>148.8074586574385</v>
       </c>
       <c r="E90">
-        <v>262.028</v>
+        <v>269.234</v>
       </c>
       <c r="F90">
-        <v>634.128</v>
+        <v>641.3340000000001</v>
       </c>
       <c r="G90">
         <v>133.3</v>
@@ -8667,37 +8667,37 @@
         <v>50.425</v>
       </c>
       <c r="M90">
-        <v>149.5273824</v>
+        <v>151.2265572</v>
       </c>
       <c r="N90">
-        <v>-99.10238240000002</v>
+        <v>-100.8015572</v>
       </c>
       <c r="O90">
-        <v>-14.86535736</v>
+        <v>-15.12023358</v>
       </c>
       <c r="P90">
-        <v>-84.23702504000002</v>
+        <v>-85.68132362000003</v>
       </c>
       <c r="Q90">
-        <v>-76.53702504000002</v>
+        <v>-77.98132362000003</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4728942616416235</v>
+        <v>0.511721012699953</v>
       </c>
       <c r="T90">
-        <v>8.101820322248003</v>
+        <v>8.838349442452367</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05058438045659253</v>
+        <v>0.05001601663123755</v>
       </c>
       <c r="W90">
-        <v>0.2238722030883355</v>
+        <v>0.2240062232783542</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.3372292030439502</v>
+        <v>0.3334401108749171</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.25565485011473</v>
+        <v>0.2575548501147301</v>
       </c>
       <c r="C91">
-        <v>-359.2265413425615</v>
+        <v>-367.7677370714714</v>
       </c>
       <c r="D91">
-        <v>148.8074586574385</v>
+        <v>147.4722629285286</v>
       </c>
       <c r="E91">
-        <v>269.234</v>
+        <v>276.4400000000001</v>
       </c>
       <c r="F91">
-        <v>641.3340000000001</v>
+        <v>648.5400000000001</v>
       </c>
       <c r="G91">
         <v>133.3</v>
@@ -8749,37 +8749,37 @@
         <v>50.425</v>
       </c>
       <c r="M91">
-        <v>151.2265572</v>
+        <v>152.925732</v>
       </c>
       <c r="N91">
-        <v>-100.8015572</v>
+        <v>-102.500732</v>
       </c>
       <c r="O91">
-        <v>-15.12023358</v>
+        <v>-15.3751098</v>
       </c>
       <c r="P91">
-        <v>-85.68132362000003</v>
+        <v>-87.12562220000001</v>
       </c>
       <c r="Q91">
-        <v>-77.98132362000003</v>
+        <v>-79.42562220000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.511721012699953</v>
+        <v>0.5583131139699482</v>
       </c>
       <c r="T91">
-        <v>8.838349442452367</v>
+        <v>9.722184386697604</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.05001601663123755</v>
+        <v>0.0494602831131127</v>
       </c>
       <c r="W91">
-        <v>0.2240062232783542</v>
+        <v>0.224137265241928</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3334401108749171</v>
+        <v>0.3297352207540847</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2575548501147301</v>
+        <v>0.25945485011473</v>
       </c>
       <c r="C92">
-        <v>-367.7677370714714</v>
+        <v>-376.2851854163779</v>
       </c>
       <c r="D92">
-        <v>147.4722629285286</v>
+        <v>146.1608145836222</v>
       </c>
       <c r="E92">
-        <v>276.4400000000001</v>
+        <v>283.6460000000001</v>
       </c>
       <c r="F92">
-        <v>648.5400000000001</v>
+        <v>655.7460000000001</v>
       </c>
       <c r="G92">
         <v>133.3</v>
@@ -8831,37 +8831,37 @@
         <v>50.425</v>
       </c>
       <c r="M92">
-        <v>152.925732</v>
+        <v>154.6249068</v>
       </c>
       <c r="N92">
-        <v>-102.500732</v>
+        <v>-104.1999068</v>
       </c>
       <c r="O92">
-        <v>-15.3751098</v>
+        <v>-15.62998602</v>
       </c>
       <c r="P92">
-        <v>-87.12562220000001</v>
+        <v>-88.56992078000002</v>
       </c>
       <c r="Q92">
-        <v>-79.42562220000001</v>
+        <v>-80.86992078000002</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5583131139699482</v>
+        <v>0.6152590155221647</v>
       </c>
       <c r="T92">
-        <v>9.722184386697604</v>
+        <v>10.80242709633067</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0494602831131127</v>
+        <v>0.04891676351846311</v>
       </c>
       <c r="W92">
-        <v>0.224137265241928</v>
+        <v>0.2242654271623464</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3297352207540847</v>
+        <v>0.3261117567897541</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.25945485011473</v>
+        <v>0.2613548501147301</v>
       </c>
       <c r="C93">
-        <v>-376.2851854163779</v>
+        <v>-384.779514338511</v>
       </c>
       <c r="D93">
-        <v>146.1608145836222</v>
+        <v>144.872485661489</v>
       </c>
       <c r="E93">
-        <v>283.6460000000001</v>
+        <v>290.852</v>
       </c>
       <c r="F93">
-        <v>655.7460000000001</v>
+        <v>662.952</v>
       </c>
       <c r="G93">
         <v>133.3</v>
@@ -8913,37 +8913,37 @@
         <v>50.425</v>
       </c>
       <c r="M93">
-        <v>154.6249068</v>
+        <v>156.3240816</v>
       </c>
       <c r="N93">
-        <v>-104.1999068</v>
+        <v>-105.8990816</v>
       </c>
       <c r="O93">
-        <v>-15.62998602</v>
+        <v>-15.88486224</v>
       </c>
       <c r="P93">
-        <v>-88.56992078000002</v>
+        <v>-90.01421936</v>
       </c>
       <c r="Q93">
-        <v>-80.86992078000002</v>
+        <v>-82.31421936</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6152590155221647</v>
+        <v>0.6864413924624354</v>
       </c>
       <c r="T93">
-        <v>10.80242709633067</v>
+        <v>12.15273048337201</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.04891676351846311</v>
+        <v>0.04838505956717547</v>
       </c>
       <c r="W93">
-        <v>0.2242654271623464</v>
+        <v>0.2243908029540601</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3261117567897541</v>
+        <v>0.3225670637811698</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2613548501147301</v>
+        <v>0.26325485011473</v>
       </c>
       <c r="C94">
-        <v>-384.779514338511</v>
+        <v>-393.2513298519916</v>
       </c>
       <c r="D94">
-        <v>144.872485661489</v>
+        <v>143.6066701480084</v>
       </c>
       <c r="E94">
-        <v>290.852</v>
+        <v>298.058</v>
       </c>
       <c r="F94">
-        <v>662.952</v>
+        <v>670.158</v>
       </c>
       <c r="G94">
         <v>133.3</v>
@@ -8995,37 +8995,37 @@
         <v>50.425</v>
       </c>
       <c r="M94">
-        <v>156.3240816</v>
+        <v>158.0232564</v>
       </c>
       <c r="N94">
-        <v>-105.8990816</v>
+        <v>-107.5982564</v>
       </c>
       <c r="O94">
-        <v>-15.88486224</v>
+        <v>-16.13973846</v>
       </c>
       <c r="P94">
-        <v>-90.01421936</v>
+        <v>-91.45851794000001</v>
       </c>
       <c r="Q94">
-        <v>-82.31421936</v>
+        <v>-83.75851794</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6864413924624354</v>
+        <v>0.7779615913856406</v>
       </c>
       <c r="T94">
-        <v>12.15273048337201</v>
+        <v>13.88883483813944</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.04838505956717547</v>
+        <v>0.04786479010946391</v>
       </c>
       <c r="W94">
-        <v>0.2243908029540601</v>
+        <v>0.2245134824921884</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3225670637811698</v>
+        <v>0.3190986007297594</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.26325485011473</v>
+        <v>0.2651548501147301</v>
       </c>
       <c r="C95">
-        <v>-393.2513298519916</v>
+        <v>-401.7012169743348</v>
       </c>
       <c r="D95">
-        <v>143.6066701480084</v>
+        <v>142.3627830256653</v>
       </c>
       <c r="E95">
-        <v>298.058</v>
+        <v>305.264</v>
       </c>
       <c r="F95">
-        <v>670.158</v>
+        <v>677.364</v>
       </c>
       <c r="G95">
         <v>133.3</v>
@@ -9077,37 +9077,37 @@
         <v>50.425</v>
       </c>
       <c r="M95">
-        <v>158.0232564</v>
+        <v>159.7224312</v>
       </c>
       <c r="N95">
-        <v>-107.5982564</v>
+        <v>-109.2974312</v>
       </c>
       <c r="O95">
-        <v>-16.13973846</v>
+        <v>-16.39461468</v>
       </c>
       <c r="P95">
-        <v>-91.45851794000001</v>
+        <v>-92.90281652000002</v>
       </c>
       <c r="Q95">
-        <v>-83.75851794</v>
+        <v>-85.20281652000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7779615913856406</v>
+        <v>0.8999885232832475</v>
       </c>
       <c r="T95">
-        <v>13.88883483813944</v>
+        <v>16.20364064449602</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.04786479010946391</v>
+        <v>0.04735559021468237</v>
       </c>
       <c r="W95">
-        <v>0.2245134824921884</v>
+        <v>0.2246335518273779</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3190986007297594</v>
+        <v>0.3157039347645492</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2651548501147301</v>
+        <v>0.2670548501147301</v>
       </c>
       <c r="C96">
-        <v>-401.7012169743348</v>
+        <v>-410.129740627979</v>
       </c>
       <c r="D96">
-        <v>142.3627830256653</v>
+        <v>141.140259372021</v>
       </c>
       <c r="E96">
-        <v>305.264</v>
+        <v>312.47</v>
       </c>
       <c r="F96">
-        <v>677.364</v>
+        <v>684.5700000000001</v>
       </c>
       <c r="G96">
         <v>133.3</v>
@@ -9159,37 +9159,37 @@
         <v>50.425</v>
       </c>
       <c r="M96">
-        <v>159.7224312</v>
+        <v>161.421606</v>
       </c>
       <c r="N96">
-        <v>-109.2974312</v>
+        <v>-110.996606</v>
       </c>
       <c r="O96">
-        <v>-16.39461468</v>
+        <v>-16.6494909</v>
       </c>
       <c r="P96">
-        <v>-92.90281652000002</v>
+        <v>-94.34711510000002</v>
       </c>
       <c r="Q96">
-        <v>-85.20281652000001</v>
+        <v>-86.64711510000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8999885232832475</v>
+        <v>1.070826227939898</v>
       </c>
       <c r="T96">
-        <v>16.20364064449602</v>
+        <v>19.44436877339523</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.04735559021468237</v>
+        <v>0.04685711031768572</v>
       </c>
       <c r="W96">
-        <v>0.2246335518273779</v>
+        <v>0.2247510933870897</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3157039347645492</v>
+        <v>0.3123807354512381</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2670548501147301</v>
+        <v>0.2689548501147301</v>
       </c>
       <c r="C97">
-        <v>-410.129740627979</v>
+        <v>-418.5374464957608</v>
       </c>
       <c r="D97">
-        <v>141.140259372021</v>
+        <v>139.9385535042393</v>
       </c>
       <c r="E97">
-        <v>312.47</v>
+        <v>319.676</v>
       </c>
       <c r="F97">
-        <v>684.5700000000001</v>
+        <v>691.7760000000001</v>
       </c>
       <c r="G97">
         <v>133.3</v>
@@ -9241,37 +9241,37 @@
         <v>50.425</v>
       </c>
       <c r="M97">
-        <v>161.421606</v>
+        <v>163.1207808</v>
       </c>
       <c r="N97">
-        <v>-110.996606</v>
+        <v>-112.6957808</v>
       </c>
       <c r="O97">
-        <v>-16.6494909</v>
+        <v>-16.90436712</v>
       </c>
       <c r="P97">
-        <v>-94.34711510000002</v>
+        <v>-95.79141368000003</v>
       </c>
       <c r="Q97">
-        <v>-86.64711510000002</v>
+        <v>-88.09141368000003</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.070826227939898</v>
+        <v>1.327082784924873</v>
       </c>
       <c r="T97">
-        <v>19.44436877339523</v>
+        <v>24.30546096674405</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.04685711031768572</v>
+        <v>0.04636901541854315</v>
       </c>
       <c r="W97">
-        <v>0.2247510933870897</v>
+        <v>0.2248661861643075</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3123807354512381</v>
+        <v>0.3091267694569544</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.26895485011473</v>
+        <v>0.27085485011473</v>
       </c>
       <c r="C98">
-        <v>-418.5374464957606</v>
+        <v>-426.9248618330552</v>
       </c>
       <c r="D98">
-        <v>139.9385535042393</v>
+        <v>138.7571381669448</v>
       </c>
       <c r="E98">
-        <v>319.6759999999999</v>
+        <v>326.8819999999999</v>
       </c>
       <c r="F98">
-        <v>691.776</v>
+        <v>698.982</v>
       </c>
       <c r="G98">
         <v>133.3</v>
@@ -9323,37 +9323,37 @@
         <v>50.425</v>
       </c>
       <c r="M98">
-        <v>163.1207808</v>
+        <v>164.8199556</v>
       </c>
       <c r="N98">
-        <v>-112.6957808</v>
+        <v>-114.3949556</v>
       </c>
       <c r="O98">
-        <v>-16.90436712</v>
+        <v>-17.15924334</v>
       </c>
       <c r="P98">
-        <v>-95.79141368000001</v>
+        <v>-97.23571225999999</v>
       </c>
       <c r="Q98">
-        <v>-88.09141368</v>
+        <v>-89.53571225999998</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.327082784924869</v>
+        <v>1.754177046566492</v>
       </c>
       <c r="T98">
-        <v>24.30546096674398</v>
+        <v>32.40728128899197</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.04636901541854316</v>
+        <v>0.04589098433175406</v>
       </c>
       <c r="W98">
-        <v>0.2248661861643075</v>
+        <v>0.2249789058945724</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3091267694569544</v>
+        <v>0.3059398955450271</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.27085485011473</v>
+        <v>0.27275485011473</v>
       </c>
       <c r="C99">
-        <v>-426.9248618330552</v>
+        <v>-435.2924962391228</v>
       </c>
       <c r="D99">
-        <v>138.7571381669448</v>
+        <v>137.5955037608772</v>
       </c>
       <c r="E99">
-        <v>326.8819999999999</v>
+        <v>334.088</v>
       </c>
       <c r="F99">
-        <v>698.982</v>
+        <v>706.188</v>
       </c>
       <c r="G99">
         <v>133.3</v>
@@ -9405,37 +9405,37 @@
         <v>50.425</v>
       </c>
       <c r="M99">
-        <v>164.8199556</v>
+        <v>166.5191304</v>
       </c>
       <c r="N99">
-        <v>-114.3949556</v>
+        <v>-116.0941304</v>
       </c>
       <c r="O99">
-        <v>-17.15924334</v>
+        <v>-17.41411956</v>
       </c>
       <c r="P99">
-        <v>-97.23571225999999</v>
+        <v>-98.68001083999999</v>
       </c>
       <c r="Q99">
-        <v>-89.53571225999998</v>
+        <v>-90.98001083999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.754177046566492</v>
+        <v>2.608365569849738</v>
       </c>
       <c r="T99">
-        <v>32.40728128899197</v>
+        <v>48.61092193348796</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.04589098433175406</v>
+        <v>0.04542270898143003</v>
       </c>
       <c r="W99">
-        <v>0.2249789058945724</v>
+        <v>0.2250893252221788</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3059398955450271</v>
+        <v>0.3028180598762003</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.27275485011473</v>
+        <v>0.27465485011473</v>
       </c>
       <c r="C100">
-        <v>-435.2924962391228</v>
+        <v>-443.640842390033</v>
       </c>
       <c r="D100">
-        <v>137.5955037608772</v>
+        <v>136.4531576099671</v>
       </c>
       <c r="E100">
-        <v>334.088</v>
+        <v>341.294</v>
       </c>
       <c r="F100">
-        <v>706.188</v>
+        <v>713.394</v>
       </c>
       <c r="G100">
         <v>133.3</v>
@@ -9487,37 +9487,37 @@
         <v>50.425</v>
       </c>
       <c r="M100">
-        <v>166.5191304</v>
+        <v>168.2183052</v>
       </c>
       <c r="N100">
-        <v>-116.0941304</v>
+        <v>-117.7933052</v>
       </c>
       <c r="O100">
-        <v>-17.41411956</v>
+        <v>-17.66899578</v>
       </c>
       <c r="P100">
-        <v>-98.68001083999999</v>
+        <v>-100.12430942</v>
       </c>
       <c r="Q100">
-        <v>-90.98001083999999</v>
+        <v>-92.42430942</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.608365569849738</v>
+        <v>5.170931139699475</v>
       </c>
       <c r="T100">
-        <v>48.61092193348796</v>
+        <v>97.22184386697592</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.04542270898143003</v>
+        <v>0.04496389373919336</v>
       </c>
       <c r="W100">
-        <v>0.2250893252221788</v>
+        <v>0.2251975138562982</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3028180598762003</v>
+        <v>0.2997592915946224</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.27465485011473</v>
-      </c>
-      <c r="C101">
-        <v>-443.640842390033</v>
-      </c>
-      <c r="D101">
-        <v>136.4531576099671</v>
-      </c>
-      <c r="E101">
-        <v>341.294</v>
-      </c>
-      <c r="F101">
-        <v>713.394</v>
-      </c>
-      <c r="G101">
-        <v>133.3</v>
-      </c>
-      <c r="H101">
-        <v>348.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>58.125</v>
-      </c>
-      <c r="K101">
-        <v>7.700000000000003</v>
-      </c>
-      <c r="L101">
-        <v>50.425</v>
-      </c>
-      <c r="M101">
-        <v>168.2183052</v>
-      </c>
-      <c r="N101">
-        <v>-117.7933052</v>
-      </c>
-      <c r="O101">
-        <v>-17.66899578</v>
-      </c>
-      <c r="P101">
-        <v>-100.12430942</v>
-      </c>
-      <c r="Q101">
-        <v>-92.42430942</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.170931139699475</v>
-      </c>
-      <c r="T101">
-        <v>97.22184386697592</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.04496389373919336</v>
-      </c>
-      <c r="W101">
-        <v>0.2251975138562982</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2997592915946224</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
